--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -46,10 +46,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="76">
     <font>
@@ -28867,7 +28868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U189"/>
+  <dimension ref="A1:U187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="17.28515625" bestFit="1" customWidth="1" style="158" min="1" max="1"/>
@@ -29015,11 +29016,11 @@
         </is>
       </c>
       <c r="L5" s="11">
-        <f>SUMIF(H5:H184,K5,G5:G184)</f>
+        <f>SUMIF(H5:H182,K5,G5:G182)</f>
         <v/>
       </c>
       <c r="N5" s="230">
-        <f>D185-F185-T5</f>
+        <f>D183-F183-T5</f>
         <v/>
       </c>
       <c r="P5" s="232">
@@ -29027,11 +29028,11 @@
         <v/>
       </c>
       <c r="R5" s="231">
-        <f>D186</f>
+        <f>D184</f>
         <v/>
       </c>
       <c r="T5" s="212">
-        <f>SUMIF(E5:E184,"Aguardando Pagamento",D5:D184)</f>
+        <f>SUMIF(E5:E182,"Aguardando Pagamento",D5:D182)</f>
         <v/>
       </c>
     </row>
@@ -29069,7 +29070,7 @@
         </is>
       </c>
       <c r="L6" s="14">
-        <f>SUMIF(H5:H184,K6,G5:G184)</f>
+        <f>SUMIF(H5:H182,K6,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29105,7 +29106,7 @@
         </is>
       </c>
       <c r="L7" s="11">
-        <f>SUMIF(H5:H184,K7,G5:G184)</f>
+        <f>SUMIF(H5:H182,K7,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29137,7 +29138,7 @@
         </is>
       </c>
       <c r="L8" s="14">
-        <f>SUMIF(H5:H184,K8,G5:G184)</f>
+        <f>SUMIF(H5:H182,K8,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29173,7 +29174,7 @@
         </is>
       </c>
       <c r="L9" s="11">
-        <f>SUMIF(H5:H184,K9,G5:G184)</f>
+        <f>SUMIF(H5:H182,K9,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29209,7 +29210,7 @@
         </is>
       </c>
       <c r="L10" s="14">
-        <f>SUMIF(H5:H184,K10,G5:G184)</f>
+        <f>SUMIF(H5:H182,K10,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29241,7 +29242,7 @@
         </is>
       </c>
       <c r="L11" s="11">
-        <f>SUMIF(H5:H184,K11,G5:G184)</f>
+        <f>SUMIF(H5:H182,K11,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29273,7 +29274,7 @@
         </is>
       </c>
       <c r="L12" s="14">
-        <f>SUMIF(H5:H184,K12,G5:G184)</f>
+        <f>SUMIF(H5:H182,K12,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29309,7 +29310,7 @@
         </is>
       </c>
       <c r="L13" s="11">
-        <f>SUMIF(H5:H184,K13,G5:G184)</f>
+        <f>SUMIF(H5:H182,K13,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29341,7 +29342,7 @@
         </is>
       </c>
       <c r="L14" s="14">
-        <f>SUMIF(H5:H184,K14,G5:G184)</f>
+        <f>SUMIF(H5:H182,K14,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29373,7 +29374,7 @@
         </is>
       </c>
       <c r="L15" s="11">
-        <f>SUMIF(H5:H184,K15,G5:G184)</f>
+        <f>SUMIF(H5:H182,K15,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29405,7 +29406,7 @@
         </is>
       </c>
       <c r="L16" s="11">
-        <f>SUMIF(H5:H184,K16,G5:G184)</f>
+        <f>SUMIF(H5:H182,K16,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -29441,7 +29442,7 @@
         </is>
       </c>
       <c r="L17">
-        <f>SUMIF(H5:H184,K17,G5:G184)</f>
+        <f>SUMIF(H5:H182,K17,G5:G182)</f>
         <v/>
       </c>
     </row>
@@ -32907,106 +32908,108 @@
       </c>
       <c r="B146" s="46" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Papelaria Castro</t>
         </is>
       </c>
       <c r="C146" s="46" t="inlineStr">
         <is>
-          <t>4x Refil Everest</t>
-        </is>
-      </c>
-      <c r="D146" s="47" t="n">
-        <v>480</v>
+          <t>Refil Pro Life + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D146" s="62" t="n">
+        <v>185</v>
       </c>
       <c r="E146" s="46" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F146" s="48" t="n"/>
-      <c r="G146" s="49" t="n"/>
+      <c r="G146" s="48" t="n"/>
       <c r="H146" s="50" t="n"/>
       <c r="I146" s="46" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="17" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B147" s="18" t="inlineStr">
         <is>
-          <t>Papelaria Castro</t>
+          <t>Cristiane Lima Procopio</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D147" s="27" t="n">
-        <v>185</v>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D147" s="156" t="n">
+        <v>200</v>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F147" s="19" t="n"/>
-      <c r="G147" s="19" t="n"/>
+      <c r="G147" s="20" t="n"/>
       <c r="H147" s="21" t="n"/>
-      <c r="I147" s="18" t="n"/>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 24/08/2026 — pagamento recebido via Pix em 25/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="45" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B148" s="46" t="inlineStr">
         <is>
-          <t>Cristiane Lima Procopio</t>
-        </is>
-      </c>
-      <c r="C148" s="46" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D148" s="47" t="n">
-        <v>200</v>
-      </c>
-      <c r="E148" s="46" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>ICMS Antecipação Parcial</t>
+        </is>
+      </c>
+      <c r="C148" s="46" t="n"/>
+      <c r="D148" s="62" t="n"/>
+      <c r="E148" s="46" t="n"/>
       <c r="F148" s="48" t="n"/>
-      <c r="G148" s="49" t="n"/>
-      <c r="H148" s="50" t="n"/>
-      <c r="I148" s="46" t="inlineStr">
-        <is>
-          <t>Venda de 24/08/2026 — pagamento recebido via Pix em 25/08/2026</t>
-        </is>
-      </c>
+      <c r="G148" s="48" t="n">
+        <v>2135.72</v>
+      </c>
+      <c r="H148" s="50" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I148" s="46" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="158">
       <c r="A149" s="17" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B149" s="18" t="inlineStr">
         <is>
-          <t>ICMS Antecipação Parcial</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="n"/>
-      <c r="D149" s="27" t="n"/>
-      <c r="E149" s="18" t="n"/>
-      <c r="F149" s="19" t="n"/>
-      <c r="G149" s="19" t="n">
-        <v>2135.72</v>
-      </c>
-      <c r="H149" s="21" t="inlineStr">
-        <is>
-          <t>Impostos e Taxas</t>
-        </is>
-      </c>
+          <t>Clinica Sao Lucas (Caém)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Mangueira</t>
+        </is>
+      </c>
+      <c r="D149" s="156" t="n">
+        <v>130</v>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F149" s="19" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G149" s="20" t="n"/>
+      <c r="H149" s="21" t="n"/>
       <c r="I149" s="18" t="n"/>
     </row>
     <row r="150">
@@ -33015,16 +33018,16 @@
       </c>
       <c r="B150" s="46" t="inlineStr">
         <is>
-          <t>Clinica Sao Lucas (Caém)</t>
+          <t>Luciano de Matos Nascimento</t>
         </is>
       </c>
       <c r="C150" s="46" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Mangueira</t>
-        </is>
-      </c>
-      <c r="D150" s="47" t="n">
-        <v>130</v>
+          <t>Purificador Everest Star Prata</t>
+        </is>
+      </c>
+      <c r="D150" s="62" t="n">
+        <v>1486</v>
       </c>
       <c r="E150" s="46" t="inlineStr">
         <is>
@@ -33032,11 +33035,15 @@
         </is>
       </c>
       <c r="F150" s="48" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="G150" s="49" t="n"/>
+        <v>207.89</v>
+      </c>
+      <c r="G150" s="48" t="n"/>
       <c r="H150" s="50" t="n"/>
-      <c r="I150" s="46" t="n"/>
+      <c r="I150" s="46" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="n">
@@ -33044,32 +33051,22 @@
       </c>
       <c r="B151" s="18" t="inlineStr">
         <is>
-          <t>Luciano de Matos Nascimento</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>Purificador Everest Star Prata</t>
-        </is>
-      </c>
-      <c r="D151" s="27" t="n">
-        <v>1486</v>
-      </c>
-      <c r="E151" s="18" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F151" s="19" t="n">
-        <v>207.89</v>
-      </c>
-      <c r="G151" s="19" t="n"/>
-      <c r="H151" s="21" t="n"/>
-      <c r="I151" s="18" t="inlineStr">
-        <is>
-          <t>Crédito em 10x</t>
-        </is>
-      </c>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="n"/>
+      <c r="D151" s="156" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="19" t="n"/>
+      <c r="G151" s="20" t="n">
+        <v>504.34</v>
+      </c>
+      <c r="H151" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="45" t="n">
@@ -33077,72 +33074,76 @@
       </c>
       <c r="B152" s="46" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
+          <t>Fix English School</t>
         </is>
       </c>
       <c r="C152" s="46" t="n"/>
-      <c r="D152" s="47" t="n"/>
+      <c r="D152" s="62" t="n"/>
       <c r="E152" s="46" t="n"/>
       <c r="F152" s="48" t="n"/>
-      <c r="G152" s="49" t="n">
-        <v>504.34</v>
+      <c r="G152" s="48" t="n">
+        <v>137</v>
       </c>
       <c r="H152" s="50" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I152" s="46" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="17" t="n">
-        <v>46259</v>
+        <v>46251</v>
       </c>
       <c r="B153" s="18" t="inlineStr">
         <is>
-          <t>Fix English School</t>
+          <t>Retirada Complementar — Despesas de 17/08</t>
         </is>
       </c>
       <c r="C153" s="18" t="n"/>
-      <c r="D153" s="27" t="n"/>
+      <c r="D153" s="156" t="n"/>
       <c r="E153" s="18" t="n"/>
       <c r="F153" s="19" t="n"/>
-      <c r="G153" s="19" t="n">
-        <v>137</v>
+      <c r="G153" s="20" t="n">
+        <v>250</v>
       </c>
       <c r="H153" s="21" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I153" s="18" t="n"/>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="45" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B154" s="46" t="inlineStr">
         <is>
-          <t>Retirada Complementar — Despesas de 17/08</t>
-        </is>
-      </c>
-      <c r="C154" s="46" t="n"/>
-      <c r="D154" s="47" t="n"/>
-      <c r="E154" s="46" t="n"/>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C154" s="46" t="inlineStr">
+        <is>
+          <t>Refil Carbon Tech 9"</t>
+        </is>
+      </c>
+      <c r="D154" s="62" t="n">
+        <v>80</v>
+      </c>
+      <c r="E154" s="46" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F154" s="48" t="n"/>
-      <c r="G154" s="49" t="n">
-        <v>250</v>
-      </c>
-      <c r="H154" s="50" t="inlineStr">
-        <is>
-          <t>Outras Despesas</t>
-        </is>
-      </c>
-      <c r="I154" s="46" t="inlineStr">
-        <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
-        </is>
-      </c>
+      <c r="G154" s="48" t="n"/>
+      <c r="H154" s="50" t="n"/>
+      <c r="I154" s="46" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="17" t="n">
@@ -33150,43 +33151,43 @@
       </c>
       <c r="B155" s="18" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
+          <t>Luana Mesquita Victoria</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
         <is>
-          <t>Refil Carbon Tech 9"</t>
-        </is>
-      </c>
-      <c r="D155" s="27" t="n">
-        <v>80</v>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D155" s="156" t="n">
+        <v>60</v>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F155" s="19" t="n"/>
-      <c r="G155" s="19" t="n"/>
+      <c r="G155" s="20" t="n"/>
       <c r="H155" s="21" t="n"/>
       <c r="I155" s="18" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="45" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B156" s="46" t="inlineStr">
         <is>
-          <t>Luana Mesquita Victoria</t>
+          <t>Cícero Lima</t>
         </is>
       </c>
       <c r="C156" s="46" t="inlineStr">
         <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D156" s="47" t="n">
-        <v>60</v>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D156" s="62" t="n">
+        <v>140</v>
       </c>
       <c r="E156" s="46" t="inlineStr">
         <is>
@@ -33194,26 +33195,26 @@
         </is>
       </c>
       <c r="F156" s="48" t="n"/>
-      <c r="G156" s="49" t="n"/>
+      <c r="G156" s="48" t="n"/>
       <c r="H156" s="50" t="n"/>
       <c r="I156" s="46" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B157" s="18" t="inlineStr">
         <is>
-          <t>Cícero Lima</t>
+          <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D157" s="27" t="n">
-        <v>140</v>
+          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
+        </is>
+      </c>
+      <c r="D157" s="156" t="n">
+        <v>270</v>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
@@ -33221,9 +33222,13 @@
         </is>
       </c>
       <c r="F157" s="19" t="n"/>
-      <c r="G157" s="19" t="n"/>
+      <c r="G157" s="20" t="n"/>
       <c r="H157" s="21" t="n"/>
-      <c r="I157" s="18" t="n"/>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>Venda única de R$ 470,00 (27/08/2026), paga em 28/08/2026 em duas formas: R$ 270,00 Pix (esta linha) + R$ 200,00 crédito 2x (linha seguinte). Os produtos estão listados só aqui.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="45" t="n">
@@ -33236,58 +33241,50 @@
       </c>
       <c r="C158" s="46" t="inlineStr">
         <is>
-          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
-        </is>
-      </c>
-      <c r="D158" s="47" t="n">
-        <v>270</v>
+          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
+        </is>
+      </c>
+      <c r="D158" s="62" t="n">
+        <v>200</v>
       </c>
       <c r="E158" s="46" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F158" s="48" t="n"/>
-      <c r="G158" s="49" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F158" s="48" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="G158" s="48" t="n"/>
       <c r="H158" s="50" t="n"/>
       <c r="I158" s="46" t="inlineStr">
         <is>
-          <t>Venda única de R$ 470,00 (27/08/2026), paga em 28/08/2026 em duas formas: R$ 270,00 Pix (esta linha) + R$ 200,00 crédito 2x (linha seguinte). Os produtos estão listados só aqui.</t>
+          <t>Parte 2/2 da venda de R$ 470,00 da Promotoria Regional de Jacobina — R$ 200,00 no crédito 2x. NÃO é uma venda nova; os itens já constam na linha anterior.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="17" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B159" s="18" t="inlineStr">
         <is>
-          <t>Promotoria Regional de Jacobina</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
-        </is>
-      </c>
-      <c r="D159" s="27" t="n">
-        <v>200</v>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n"/>
+      <c r="D159" s="156" t="n">
+        <v>1000</v>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F159" s="19" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="G159" s="19" t="n"/>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F159" s="19" t="n"/>
+      <c r="G159" s="20" t="n"/>
       <c r="H159" s="21" t="n"/>
-      <c r="I159" s="18" t="inlineStr">
-        <is>
-          <t>Parte 2/2 da venda de R$ 470,00 da Promotoria Regional de Jacobina — R$ 200,00 no crédito 2x. NÃO é uma venda nova; os itens já constam na linha anterior.</t>
-        </is>
-      </c>
+      <c r="I159" s="18" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="45" t="n">
@@ -33295,22 +33292,26 @@
       </c>
       <c r="B160" s="46" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
+          <t>A E G Calçados LTDA</t>
         </is>
       </c>
       <c r="C160" s="46" t="n"/>
-      <c r="D160" s="47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E160" s="46" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+      <c r="D160" s="62" t="n"/>
+      <c r="E160" s="46" t="n"/>
       <c r="F160" s="48" t="n"/>
-      <c r="G160" s="49" t="n"/>
-      <c r="H160" s="50" t="n"/>
-      <c r="I160" s="46" t="n"/>
+      <c r="G160" s="48" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="H160" s="50" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I160" s="46" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 27/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="17" t="n">
@@ -33318,15 +33319,15 @@
       </c>
       <c r="B161" s="18" t="inlineStr">
         <is>
-          <t>A E G Calçados LTDA</t>
+          <t>Queite Almeida Duarte</t>
         </is>
       </c>
       <c r="C161" s="18" t="n"/>
-      <c r="D161" s="27" t="n"/>
+      <c r="D161" s="156" t="n"/>
       <c r="E161" s="18" t="n"/>
       <c r="F161" s="19" t="n"/>
-      <c r="G161" s="19" t="n">
-        <v>127.42</v>
+      <c r="G161" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="H161" s="21" t="inlineStr">
         <is>
@@ -33341,19 +33342,19 @@
     </row>
     <row r="162">
       <c r="A162" s="45" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B162" s="46" t="inlineStr">
         <is>
-          <t>Queite Almeida Duarte</t>
+          <t>Edilania Almeida Silva Costa Fontes</t>
         </is>
       </c>
       <c r="C162" s="46" t="n"/>
-      <c r="D162" s="47" t="n"/>
+      <c r="D162" s="62" t="n"/>
       <c r="E162" s="46" t="n"/>
       <c r="F162" s="48" t="n"/>
-      <c r="G162" s="49" t="n">
-        <v>100</v>
+      <c r="G162" s="48" t="n">
+        <v>230</v>
       </c>
       <c r="H162" s="50" t="inlineStr">
         <is>
@@ -33362,7 +33363,7 @@
       </c>
       <c r="I162" s="46" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 27/08/2026</t>
+          <t>Extrato Stone — Pix de 26/08/2026</t>
         </is>
       </c>
     </row>
@@ -33372,19 +33373,19 @@
       </c>
       <c r="B163" s="18" t="inlineStr">
         <is>
-          <t>Edilania Almeida Silva Costa Fontes</t>
+          <t>Estacionamento (Pagar.me)</t>
         </is>
       </c>
       <c r="C163" s="18" t="n"/>
-      <c r="D163" s="27" t="n"/>
+      <c r="D163" s="156" t="n"/>
       <c r="E163" s="18" t="n"/>
       <c r="F163" s="19" t="n"/>
-      <c r="G163" s="19" t="n">
-        <v>230</v>
+      <c r="G163" s="20" t="n">
+        <v>1.2</v>
       </c>
       <c r="H163" s="21" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I163" s="18" t="inlineStr">
@@ -33395,11 +33396,11 @@
     </row>
     <row r="164">
       <c r="A164" s="45" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B164" s="46" t="inlineStr">
         <is>
-          <t>Estacionamento (Pagar.me)</t>
+          <t>4x Parafuso</t>
         </is>
       </c>
       <c r="C164" s="46" t="n"/>
@@ -33407,615 +33408,561 @@
       <c r="E164" s="46" t="n"/>
       <c r="F164" s="48" t="n"/>
       <c r="G164" s="49" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="H164" s="50" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I164" s="46" t="inlineStr">
-        <is>
-          <t>Extrato Stone — Pix de 26/08/2026</t>
-        </is>
-      </c>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I164" s="46" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="45" t="n">
+      <c r="A165" s="17" t="n">
         <v>46261</v>
       </c>
-      <c r="B165" s="46" t="inlineStr">
-        <is>
-          <t>4x Parafuso</t>
-        </is>
-      </c>
-      <c r="C165" s="46" t="n"/>
-      <c r="D165" s="47" t="n"/>
-      <c r="E165" s="46" t="n"/>
-      <c r="F165" s="48" t="n"/>
-      <c r="G165" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="H165" s="50" t="inlineStr">
-        <is>
-          <t>Manutenção e Reparos</t>
-        </is>
-      </c>
-      <c r="I165" s="46" t="n"/>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>FG Boa Vista (Recife/PE)</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="D165" s="27" t="n">
+        <v>1008.8</v>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F165" s="19" t="n"/>
+      <c r="G165" s="19" t="n"/>
+      <c r="H165" s="21" t="n"/>
+      <c r="I165" s="18" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — OC SOCECPO00006537 · NF 000.004.280 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026. OC lista R$ 1.040,00 sem aplicar o desconto de 3%; Lorena confirmou que não há problema. · Pago em 27/08/2026 (confirmado via Pix SOCEC no extrato bancário)</t>
+        </is>
+      </c>
+      <c r="K165" s="13" t="n"/>
+      <c r="L165" s="14" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="17" t="n">
+      <c r="A166" s="45" t="n">
         <v>46261</v>
       </c>
-      <c r="B166" s="18" t="inlineStr">
-        <is>
-          <t>FG Boa Vista (Recife/PE)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
+      <c r="B166" s="46" t="inlineStr">
+        <is>
+          <t>UNIFG Guanambi (Guanambi/BA)</t>
+        </is>
+      </c>
+      <c r="C166" s="46" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="D166" s="27" t="n">
-        <v>1008.8</v>
-      </c>
-      <c r="E166" s="18" t="inlineStr">
+      <c r="D166" s="47" t="n">
+        <v>4534.75</v>
+      </c>
+      <c r="E166" s="46" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="F166" s="19" t="n"/>
-      <c r="G166" s="19" t="n"/>
-      <c r="H166" s="21" t="n"/>
-      <c r="I166" s="18" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — OC SOCECPO00006537 · NF 000.004.280 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026. OC lista R$ 1.040,00 sem aplicar o desconto de 3%; Lorena confirmou que não há problema. · Pago em 27/08/2026 (confirmado via Pix SOCEC no extrato bancário)</t>
-        </is>
-      </c>
-      <c r="K166" s="13" t="n"/>
-      <c r="L166" s="14" t="n"/>
+      <c r="F166" s="48" t="n"/>
+      <c r="G166" s="49" t="n"/>
+      <c r="H166" s="50" t="n"/>
+      <c r="I166" s="46" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — OC CESGPO00006036 · NF 000.004.281 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 (desc. 3%) · Pago em 27/08/2026 (confirmado via Pix CESG no extrato bancário)</t>
+        </is>
+      </c>
+      <c r="K166" s="42" t="n"/>
+      <c r="L166" s="8" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="45" t="n">
+      <c r="A167" s="17" t="n">
         <v>46261</v>
       </c>
-      <c r="B167" s="46" t="inlineStr">
-        <is>
-          <t>UNIFG Guanambi (Guanambi/BA)</t>
-        </is>
-      </c>
-      <c r="C167" s="46" t="inlineStr">
+      <c r="B167" s="18" t="inlineStr">
+        <is>
+          <t>UNP Zona Norte (Natal/RN)</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="D167" s="47" t="n">
-        <v>4534.75</v>
-      </c>
-      <c r="E167" s="46" t="inlineStr">
+      <c r="D167" s="27" t="n">
+        <v>870</v>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="F167" s="48" t="n"/>
-      <c r="G167" s="49" t="n"/>
-      <c r="H167" s="50" t="n"/>
-      <c r="I167" s="46" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — OC CESGPO00006036 · NF 000.004.281 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 (desc. 3%) · Pago em 27/08/2026 (confirmado via Pix CESG no extrato bancário)</t>
-        </is>
-      </c>
-      <c r="K167" s="42" t="n"/>
-      <c r="L167" s="8" t="n"/>
+      <c r="F167" s="19" t="n"/>
+      <c r="G167" s="19" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="18" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — OC APECPO00019432 · NF 000.004.282 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 · Pago em 27/08/2026 (confirmado via Pix APEC no extrato bancário)</t>
+        </is>
+      </c>
+      <c r="K167" s="31" t="n"/>
+      <c r="L167" s="31" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="17" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B168" s="18" t="inlineStr">
-        <is>
-          <t>UNP Zona Norte (Natal/RN)</t>
-        </is>
-      </c>
-      <c r="C168" s="18" t="inlineStr">
+      <c r="A168" s="45" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B168" s="46" t="inlineStr">
+        <is>
+          <t>UNP Caicó (Caicó/RN)</t>
+        </is>
+      </c>
+      <c r="C168" s="46" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="D168" s="27" t="n">
-        <v>870</v>
-      </c>
-      <c r="E168" s="18" t="inlineStr">
+      <c r="D168" s="47" t="n">
+        <v>440</v>
+      </c>
+      <c r="E168" s="46" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="F168" s="19" t="n"/>
-      <c r="G168" s="19" t="n"/>
-      <c r="H168" s="21" t="n"/>
-      <c r="I168" s="18" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — OC APECPO00019432 · NF 000.004.282 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 · Pago em 27/08/2026 (confirmado via Pix APEC no extrato bancário)</t>
+      <c r="F168" s="48" t="n"/>
+      <c r="G168" s="49" t="n"/>
+      <c r="H168" s="50" t="n"/>
+      <c r="I168" s="46" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — OC APECPO00019405 · NF 000.004.283 de 28/07/2026 · pago via Pix pela APEC em 27/08/2026 (após o fechamento do relatório do dia)</t>
         </is>
       </c>
       <c r="K168" s="31" t="n"/>
       <c r="L168" s="31" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="45" t="n">
+      <c r="A169" s="17" t="n">
         <v>46262</v>
       </c>
-      <c r="B169" s="46" t="inlineStr">
-        <is>
-          <t>UNP Caicó (Caicó/RN)</t>
-        </is>
-      </c>
-      <c r="C169" s="46" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="D169" s="47" t="n">
-        <v>440</v>
-      </c>
-      <c r="E169" s="46" t="inlineStr">
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>Produtos de Higiene</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="27" t="n"/>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="19" t="n"/>
+      <c r="G169" s="19" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H169" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I169" s="18" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B170" s="46" t="inlineStr">
+        <is>
+          <t>Katiane</t>
+        </is>
+      </c>
+      <c r="C170" s="46" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D170" s="47" t="n">
+        <v>150</v>
+      </c>
+      <c r="E170" s="46" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F170" s="48" t="n"/>
+      <c r="G170" s="49" t="n"/>
+      <c r="H170" s="50" t="n"/>
+      <c r="I170" s="46" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="17" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B171" s="18" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="n"/>
+      <c r="D171" s="27" t="n"/>
+      <c r="E171" s="18" t="n"/>
+      <c r="F171" s="19" t="n"/>
+      <c r="G171" s="19" t="n">
+        <v>878.9299999999999</v>
+      </c>
+      <c r="H171" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I171" s="18" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B172" s="46" t="inlineStr">
+        <is>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C172" s="46" t="inlineStr">
+        <is>
+          <t>Refil E3</t>
+        </is>
+      </c>
+      <c r="D172" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="E172" s="46" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F172" s="48" t="n"/>
+      <c r="G172" s="49" t="n"/>
+      <c r="H172" s="50" t="n"/>
+      <c r="I172" s="46" t="n"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1" s="158">
+      <c r="A173" s="17" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B173" s="18" t="inlineStr">
+        <is>
+          <t>Salário Erick (Estagiário)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="n"/>
+      <c r="D173" s="27" t="n"/>
+      <c r="E173" s="18" t="n"/>
+      <c r="F173" s="19" t="n"/>
+      <c r="G173" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="H173" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I173" s="18" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B174" s="46" t="inlineStr">
+        <is>
+          <t>Marcelo Pioverzan Pinheiro</t>
+        </is>
+      </c>
+      <c r="C174" s="46" t="inlineStr">
+        <is>
+          <t>Bebedouro Industrial 50L + Engate</t>
+        </is>
+      </c>
+      <c r="D174" s="62" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E174" s="46" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="F169" s="48" t="n"/>
-      <c r="G169" s="49" t="n"/>
-      <c r="H169" s="50" t="n"/>
-      <c r="I169" s="46" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — OC APECPO00019405 · NF 000.004.283 de 28/07/2026 · pago via Pix pela APEC em 27/08/2026 (após o fechamento do relatório do dia)</t>
-        </is>
-      </c>
-      <c r="K169" s="31" t="n"/>
-      <c r="L169" s="31" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="17" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B170" s="18" t="inlineStr">
-        <is>
-          <t>Produtos de Higiene</t>
-        </is>
-      </c>
-      <c r="C170" s="18" t="n"/>
-      <c r="D170" s="27" t="n"/>
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="19" t="n"/>
-      <c r="G170" s="19" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H170" s="21" t="inlineStr">
-        <is>
-          <t>Material de Limpeza e Escritório</t>
-        </is>
-      </c>
-      <c r="I170" s="18" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="45" t="n">
+      <c r="F174" s="48" t="n"/>
+      <c r="G174" s="48" t="n"/>
+      <c r="H174" s="50" t="n"/>
+      <c r="I174" s="46" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="17" t="n">
         <v>46265</v>
       </c>
-      <c r="B171" s="46" t="inlineStr">
-        <is>
-          <t>Katiane</t>
-        </is>
-      </c>
-      <c r="C171" s="46" t="inlineStr">
-        <is>
-          <t>Refil Everest + Mangueira</t>
-        </is>
-      </c>
-      <c r="D171" s="47" t="n">
-        <v>150</v>
-      </c>
-      <c r="E171" s="46" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F171" s="48" t="n"/>
-      <c r="G171" s="49" t="n"/>
-      <c r="H171" s="50" t="n"/>
-      <c r="I171" s="46" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="17" t="n">
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>Raiane Melo do Rosario</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D175" s="156" t="n">
+        <v>200</v>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F175" s="19" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="G175" s="20" t="n"/>
+      <c r="H175" s="21" t="n"/>
+      <c r="I175" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1" s="158">
+      <c r="A176" s="45" t="n">
         <v>46265</v>
       </c>
-      <c r="B172" s="18" t="inlineStr">
-        <is>
-          <t>Eversoft</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="n"/>
-      <c r="D172" s="27" t="n"/>
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="19" t="n"/>
-      <c r="G172" s="19" t="n">
-        <v>878.9299999999999</v>
-      </c>
-      <c r="H172" s="21" t="inlineStr">
+      <c r="B176" s="46" t="inlineStr">
+        <is>
+          <t>Salário Wiliam</t>
+        </is>
+      </c>
+      <c r="C176" s="46" t="n"/>
+      <c r="D176" s="62" t="n"/>
+      <c r="E176" s="46" t="n"/>
+      <c r="F176" s="48" t="n"/>
+      <c r="G176" s="48" t="n">
+        <v>1571.32</v>
+      </c>
+      <c r="H176" s="50" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I176" s="46" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="17" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>Tarifa Pacote de Tarifas</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="n"/>
+      <c r="D177" s="156" t="n"/>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="19" t="n"/>
+      <c r="G177" s="20" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H177" s="21" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I177" s="18" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B178" s="46" t="inlineStr">
+        <is>
+          <t>Tarifa Pix (14 lançamentos)</t>
+        </is>
+      </c>
+      <c r="C178" s="46" t="n"/>
+      <c r="D178" s="62" t="n"/>
+      <c r="E178" s="46" t="n"/>
+      <c r="F178" s="48" t="n"/>
+      <c r="G178" s="48" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="H178" s="50" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I178" s="46" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="17" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B179" s="18" t="inlineStr">
+        <is>
+          <t>Pix Pessoal (4 lançamentos)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="n"/>
+      <c r="D179" s="156" t="n"/>
+      <c r="E179" s="18" t="n"/>
+      <c r="F179" s="19" t="n"/>
+      <c r="G179" s="20" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="H179" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I179" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B180" s="46" t="inlineStr">
+        <is>
+          <t>Compras p/Loja (2 lançamentos)</t>
+        </is>
+      </c>
+      <c r="C180" s="46" t="n"/>
+      <c r="D180" s="62" t="n"/>
+      <c r="E180" s="46" t="n"/>
+      <c r="F180" s="48" t="n"/>
+      <c r="G180" s="48" t="n">
+        <v>131.29</v>
+      </c>
+      <c r="H180" s="50" t="inlineStr">
         <is>
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I172" s="18" t="n"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" s="158">
-      <c r="A173" s="45" t="n">
+      <c r="I180" s="46" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="17" t="n">
         <v>46265</v>
       </c>
-      <c r="B173" s="46" t="inlineStr">
-        <is>
-          <t>Cliente Consumidor Final</t>
-        </is>
-      </c>
-      <c r="C173" s="46" t="inlineStr">
-        <is>
-          <t>Refil E3</t>
-        </is>
-      </c>
-      <c r="D173" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="E173" s="46" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F173" s="48" t="n"/>
-      <c r="G173" s="49" t="n"/>
-      <c r="H173" s="50" t="n"/>
-      <c r="I173" s="46" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="17" t="n">
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>Estacionamento (2 lançamentos)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="n"/>
+      <c r="D181" s="156" t="n"/>
+      <c r="E181" s="18" t="n"/>
+      <c r="F181" s="19" t="n"/>
+      <c r="G181" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H181" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I181" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="45" t="n">
         <v>46265</v>
       </c>
-      <c r="B174" s="18" t="inlineStr">
-        <is>
-          <t>Salário Erick (Estagiário)</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="n"/>
-      <c r="D174" s="27" t="n"/>
-      <c r="E174" s="18" t="n"/>
-      <c r="F174" s="19" t="n"/>
-      <c r="G174" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="H174" s="21" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
-      <c r="I174" s="18" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="45" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B175" s="46" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="C175" s="46" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D175" s="47" t="n">
-        <v>160</v>
-      </c>
-      <c r="E175" s="46" t="inlineStr">
-        <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
-      <c r="F175" s="48" t="n"/>
-      <c r="G175" s="49" t="n"/>
-      <c r="H175" s="50" t="n"/>
-      <c r="I175" s="46" t="n"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1" s="158">
-      <c r="A176" s="17" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B176" s="18" t="inlineStr">
-        <is>
-          <t>Marcelo Pioverzan Pinheiro</t>
-        </is>
-      </c>
-      <c r="C176" s="18" t="inlineStr">
-        <is>
-          <t>Bebedouro Industrial 50L + Engate</t>
-        </is>
-      </c>
-      <c r="D176" s="27" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E176" s="18" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F176" s="19" t="n"/>
-      <c r="G176" s="19" t="n"/>
-      <c r="H176" s="21" t="n"/>
-      <c r="I176" s="18" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="45" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B177" s="46" t="inlineStr">
-        <is>
-          <t>Raiane Melo do Rosario</t>
-        </is>
-      </c>
-      <c r="C177" s="46" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D177" s="47" t="n">
-        <v>200</v>
-      </c>
-      <c r="E177" s="46" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F177" s="48" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="G177" s="49" t="n"/>
-      <c r="H177" s="50" t="n"/>
-      <c r="I177" s="46" t="inlineStr">
-        <is>
-          <t>Crédito em 4x</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="17" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B178" s="18" t="inlineStr">
-        <is>
-          <t>Salário Wiliam</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="n"/>
-      <c r="D178" s="27" t="n"/>
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="19" t="n"/>
-      <c r="G178" s="19" t="n">
-        <v>1571.32</v>
-      </c>
-      <c r="H178" s="21" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
-      <c r="I178" s="18" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="45" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B179" s="46" t="inlineStr">
-        <is>
-          <t>Tarifa Pacote de Tarifas</t>
-        </is>
-      </c>
-      <c r="C179" s="46" t="n"/>
-      <c r="D179" s="47" t="n"/>
-      <c r="E179" s="46" t="n"/>
-      <c r="F179" s="48" t="n"/>
-      <c r="G179" s="49" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H179" s="50" t="inlineStr">
-        <is>
-          <t>Tarifas Bancárias e Cartão</t>
-        </is>
-      </c>
-      <c r="I179" s="46" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="17" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B180" s="18" t="inlineStr">
-        <is>
-          <t>Tarifa Pix (14 lançamentos)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="n"/>
-      <c r="D180" s="27" t="n"/>
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="19" t="n"/>
-      <c r="G180" s="19" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="H180" s="21" t="inlineStr">
-        <is>
-          <t>Tarifas Bancárias e Cartão</t>
-        </is>
-      </c>
-      <c r="I180" s="18" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="45" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B181" s="46" t="inlineStr">
-        <is>
-          <t>Pix Pessoal (4 lançamentos)</t>
-        </is>
-      </c>
-      <c r="C181" s="46" t="n"/>
-      <c r="D181" s="47" t="n"/>
-      <c r="E181" s="46" t="n"/>
-      <c r="F181" s="48" t="n"/>
-      <c r="G181" s="49" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="H181" s="50" t="inlineStr">
-        <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I181" s="46" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="17" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B182" s="18" t="inlineStr">
-        <is>
-          <t>Compras p/Loja (2 lançamentos)</t>
-        </is>
-      </c>
-      <c r="C182" s="18" t="n"/>
-      <c r="D182" s="27" t="n"/>
-      <c r="E182" s="18" t="n"/>
-      <c r="F182" s="19" t="n"/>
-      <c r="G182" s="19" t="n">
-        <v>131.29</v>
-      </c>
-      <c r="H182" s="21" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I182" s="18" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
-        </is>
-      </c>
+      <c r="B182" s="46" t="inlineStr">
+        <is>
+          <t>Gasolina</t>
+        </is>
+      </c>
+      <c r="C182" s="46" t="n"/>
+      <c r="D182" s="62" t="n"/>
+      <c r="E182" s="46" t="n"/>
+      <c r="F182" s="48" t="n"/>
+      <c r="G182" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="H182" s="50" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I182" s="46" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="45" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B183" s="46" t="inlineStr">
-        <is>
-          <t>Estacionamento (2 lançamentos)</t>
-        </is>
-      </c>
-      <c r="C183" s="46" t="n"/>
-      <c r="D183" s="47" t="n"/>
-      <c r="E183" s="46" t="n"/>
-      <c r="F183" s="48" t="n"/>
-      <c r="G183" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="H183" s="50" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I183" s="46" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
-        </is>
-      </c>
+      <c r="A183" s="29" t="n"/>
+      <c r="B183" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL DO MÊS</t>
+        </is>
+      </c>
+      <c r="C183" s="161" t="n"/>
+      <c r="D183" s="8">
+        <f>SUM(D5:D182)</f>
+        <v/>
+      </c>
+      <c r="E183" s="8" t="n"/>
+      <c r="F183" s="29">
+        <f>SUM(F5:F182)</f>
+        <v/>
+      </c>
+      <c r="G183" s="8">
+        <f>SUM(G5:G182)</f>
+        <v/>
+      </c>
+      <c r="H183" s="29" t="n"/>
+      <c r="I183" s="29" t="n"/>
+      <c r="K183" s="31" t="n"/>
+      <c r="L183" s="31" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="17" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B184" s="18" t="inlineStr">
-        <is>
-          <t>Gasolina</t>
-        </is>
-      </c>
-      <c r="C184" s="18" t="n"/>
-      <c r="D184" s="27" t="n"/>
-      <c r="E184" s="18" t="n"/>
-      <c r="F184" s="19" t="n"/>
-      <c r="G184" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="H184" s="21" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I184" s="18" t="n"/>
+      <c r="A184" s="30" t="n"/>
+      <c r="B184" s="154" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
+        </is>
+      </c>
+      <c r="D184" s="153">
+        <f>(D183-F183-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F184" s="30" t="n"/>
+      <c r="H184" s="30" t="n"/>
+      <c r="I184" s="30" t="n"/>
+      <c r="K184" s="31" t="n"/>
+      <c r="L184" s="31" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="29" t="n"/>
-      <c r="B185" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL DO MÊS</t>
-        </is>
-      </c>
-      <c r="C185" s="161" t="n"/>
-      <c r="D185" s="8">
-        <f>SUM(D5:D184)</f>
-        <v/>
-      </c>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="29">
-        <f>SUM(F5:F184)</f>
-        <v/>
-      </c>
-      <c r="G185" s="8">
-        <f>SUM(G5:G184)</f>
-        <v/>
-      </c>
-      <c r="H185" s="29" t="n"/>
-      <c r="I185" s="29" t="n"/>
       <c r="K185" s="31" t="n"/>
       <c r="L185" s="31" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="30" t="n"/>
-      <c r="B186" s="154" t="inlineStr">
-        <is>
-          <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
-        </is>
-      </c>
-      <c r="D186" s="153">
-        <f>(D185-F185-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F186" s="30" t="n"/>
-      <c r="H186" s="30" t="n"/>
-      <c r="I186" s="30" t="n"/>
       <c r="K186" s="31" t="n"/>
       <c r="L186" s="31" t="n"/>
     </row>
     <row r="187">
       <c r="K187" s="31" t="n"/>
       <c r="L187" s="31" t="n"/>
-    </row>
-    <row r="188">
-      <c r="K188" s="31" t="n"/>
-      <c r="L188" s="31" t="n"/>
-    </row>
-    <row r="189">
-      <c r="K189" s="31" t="n"/>
-      <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -34054,7 +34001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34185,7 +34132,7 @@
       </c>
       <c r="E5" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F5" s="91" t="n"/>
@@ -34193,7 +34140,7 @@
       <c r="H5" s="90" t="n"/>
       <c r="I5" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEMPPO00004359 · NF 000.004.294 de 05/08/2026 · prazo 30 dias · vencimento 04/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEMPPO00004359 · NF 000.004.294 de 05/08/2026 · prazo 30 dias · vencimento 04/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 04/09/2026</t>
         </is>
       </c>
       <c r="K5" s="90" t="inlineStr">
@@ -34202,11 +34149,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H54,K5,G5:G54)</f>
+        <f>SUMIF(H5:H61,K5,G5:G61)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D55-F55-T5</f>
+        <f>D62-F62-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34214,11 +34161,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D56</f>
+        <f>D63</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E54,"Aguardando Pagamento",D5:D54)</f>
+        <f>SUMIF(E5:E61,"Aguardando Pagamento",D5:D61)</f>
         <v/>
       </c>
     </row>
@@ -34241,7 +34188,7 @@
       </c>
       <c r="E6" s="94" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F6" s="95" t="n"/>
@@ -34249,7 +34196,7 @@
       <c r="H6" s="94" t="n"/>
       <c r="I6" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEMPPO00004358 · NF 000.004.295 de 05/08/2026 · prazo 30 dias · vencimento 04/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEMPPO00004358 · NF 000.004.295 de 05/08/2026 · prazo 30 dias · vencimento 04/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 04/09/2026</t>
         </is>
       </c>
       <c r="K6" s="90" t="inlineStr">
@@ -34258,13 +34205,13 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H54,K6,G5:G54)</f>
+        <f>SUMIF(H5:H61,K6,G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="89" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B7" s="90" t="inlineStr">
         <is>
@@ -34281,7 +34228,7 @@
       </c>
       <c r="E7" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F7" s="91" t="n"/>
@@ -34289,7 +34236,7 @@
       <c r="H7" s="90" t="n"/>
       <c r="I7" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEDPO00004751 · NF 000.004.298 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEDPO00004751 · NF 000.004.298 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
       <c r="K7" s="90" t="inlineStr">
@@ -34298,13 +34245,13 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H54,K7,G5:G54)</f>
+        <f>SUMIF(H5:H61,K7,G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="93" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B8" s="94" t="inlineStr">
         <is>
@@ -34321,7 +34268,7 @@
       </c>
       <c r="E8" s="94" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F8" s="95" t="n"/>
@@ -34329,7 +34276,7 @@
       <c r="H8" s="94" t="n"/>
       <c r="I8" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEDPO00004750 · NF 000.004.299 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEDPO00004750 · NF 000.004.299 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
       <c r="K8" s="90" t="inlineStr">
@@ -34338,13 +34285,13 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H54,K8,G5:G54)</f>
+        <f>SUMIF(H5:H61,K8,G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="89" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B9" s="90" t="inlineStr">
         <is>
@@ -34361,7 +34308,7 @@
       </c>
       <c r="E9" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F9" s="91" t="n"/>
@@ -34369,7 +34316,7 @@
       <c r="H9" s="90" t="n"/>
       <c r="I9" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEDPO00004743 · NF 000.004.300 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEDPO00004743 · NF 000.004.300 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
       <c r="K9" s="90" t="inlineStr">
@@ -34378,13 +34325,13 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H54,K9,G5:G54)</f>
+        <f>SUMIF(H5:H61,K9,G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="93" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B10" s="94" t="inlineStr">
         <is>
@@ -34401,7 +34348,7 @@
       </c>
       <c r="E10" s="94" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F10" s="95" t="n"/>
@@ -34409,7 +34356,7 @@
       <c r="H10" s="94" t="n"/>
       <c r="I10" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEDPO00004749 · NF 000.004.301 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEDPO00004749 · NF 000.004.301 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
       <c r="K10" s="90" t="inlineStr">
@@ -34418,13 +34365,13 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H54,K10,G5:G54)</f>
+        <f>SUMIF(H5:H61,K10,G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="89" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B11" s="90" t="inlineStr">
         <is>
@@ -34441,7 +34388,7 @@
       </c>
       <c r="E11" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F11" s="91" t="n"/>
@@ -34449,7 +34396,7 @@
       <c r="H11" s="90" t="n"/>
       <c r="I11" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC APECPO00019551 · NF 000.004.302 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC APECPO00019551 · NF 000.004.302 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
       <c r="K11" s="90" t="inlineStr">
@@ -34458,7 +34405,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H54,K11,G5:G54)</f>
+        <f>SUMIF(H5:H61,K11,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34498,7 +34445,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H54,K12,G5:G54)</f>
+        <f>SUMIF(H5:H61,K12,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34534,7 +34481,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H54,K13,G5:G54)</f>
+        <f>SUMIF(H5:H61,K13,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34574,7 +34521,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H54,K14,G5:G54)</f>
+        <f>SUMIF(H5:H61,K14,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34610,7 +34557,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H54,K15,G5:G54)</f>
+        <f>SUMIF(H5:H61,K15,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34646,7 +34593,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H54,K16,G5:G54)</f>
+        <f>SUMIF(H5:H61,K16,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -34686,7 +34633,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H54,K17,G5:G54)</f>
+        <f>SUMIF(H5:H61,K17,G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -35628,90 +35575,359 @@
       <c r="I50" s="94" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="89" t="n"/>
-      <c r="B51" s="90" t="n"/>
-      <c r="C51" s="90" t="n"/>
-      <c r="D51" s="91" t="n"/>
-      <c r="E51" s="90" t="n"/>
+      <c r="A51" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B51" s="90" t="inlineStr">
+        <is>
+          <t>Instituto Paulo Leão</t>
+        </is>
+      </c>
+      <c r="C51" s="90" t="inlineStr">
+        <is>
+          <t>Refil E3 + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D51" s="91" t="n">
+        <v>160</v>
+      </c>
+      <c r="E51" s="90" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F51" s="91" t="n"/>
       <c r="G51" s="91" t="n"/>
       <c r="H51" s="90" t="n"/>
-      <c r="I51" s="90" t="n"/>
+      <c r="I51" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 31/08/2026 — pagamento recebido via Pix em 08/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="93" t="n"/>
-      <c r="B52" s="94" t="n"/>
+      <c r="A52" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B52" s="94" t="inlineStr">
+        <is>
+          <t>Crédito Celular da Loja</t>
+        </is>
+      </c>
       <c r="C52" s="94" t="n"/>
       <c r="D52" s="95" t="n"/>
       <c r="E52" s="94" t="n"/>
       <c r="F52" s="95" t="n"/>
-      <c r="G52" s="95" t="n"/>
-      <c r="H52" s="94" t="n"/>
+      <c r="G52" s="95" t="n">
+        <v>25</v>
+      </c>
+      <c r="H52" s="94" t="inlineStr">
+        <is>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
       <c r="I52" s="94" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="89" t="n"/>
-      <c r="B53" s="90" t="n"/>
-      <c r="C53" s="90" t="n"/>
-      <c r="D53" s="91" t="n"/>
-      <c r="E53" s="90" t="n"/>
-      <c r="F53" s="91" t="n"/>
+      <c r="A53" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B53" s="90" t="inlineStr">
+        <is>
+          <t>Edileia Santana Lima</t>
+        </is>
+      </c>
+      <c r="C53" s="90" t="inlineStr">
+        <is>
+          <t>Purificador Everest Fit Branco</t>
+        </is>
+      </c>
+      <c r="D53" s="91" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E53" s="90" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F53" s="91" t="n">
+        <v>199.92</v>
+      </c>
       <c r="G53" s="91" t="n"/>
       <c r="H53" s="90" t="n"/>
-      <c r="I53" s="90" t="n"/>
+      <c r="I53" s="90" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="93" t="n"/>
-      <c r="B54" s="94" t="n"/>
-      <c r="C54" s="94" t="n"/>
-      <c r="D54" s="95" t="n"/>
-      <c r="E54" s="94" t="n"/>
+      <c r="A54" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B54" s="94" t="inlineStr">
+        <is>
+          <t>Luiz Junior</t>
+        </is>
+      </c>
+      <c r="C54" s="94" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D54" s="95" t="n">
+        <v>130</v>
+      </c>
+      <c r="E54" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F54" s="95" t="n"/>
       <c r="G54" s="95" t="n"/>
       <c r="H54" s="94" t="n"/>
       <c r="I54" s="94" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="102" t="n"/>
-      <c r="B55" s="102" t="inlineStr">
+      <c r="A55" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B55" s="90" t="inlineStr">
+        <is>
+          <t>Consultório Dr Vitor Hugo</t>
+        </is>
+      </c>
+      <c r="C55" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D55" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E55" s="90" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F55" s="91" t="n"/>
+      <c r="G55" s="91" t="n"/>
+      <c r="H55" s="90" t="n"/>
+      <c r="I55" s="90" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B56" s="94" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C56" s="94" t="inlineStr">
+        <is>
+          <t>Carcaça 7" + 2x Refil Carbon 7"</t>
+        </is>
+      </c>
+      <c r="D56" s="95" t="n">
+        <v>230</v>
+      </c>
+      <c r="E56" s="94" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F56" s="95" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="G56" s="95" t="n"/>
+      <c r="H56" s="94" t="n"/>
+      <c r="I56" s="94" t="inlineStr">
+        <is>
+          <t>Crédito em 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B57" s="90" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="C57" s="90" t="inlineStr">
+        <is>
+          <t>4x Refil Everest</t>
+        </is>
+      </c>
+      <c r="D57" s="91" t="n">
+        <v>480</v>
+      </c>
+      <c r="E57" s="90" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F57" s="91" t="n"/>
+      <c r="G57" s="91" t="n"/>
+      <c r="H57" s="90" t="n"/>
+      <c r="I57" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 24/08/2026 — pagamento recebido em dinheiro em 08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="94" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="C58" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Refil C+3</t>
+        </is>
+      </c>
+      <c r="D58" s="95" t="n">
+        <v>220</v>
+      </c>
+      <c r="E58" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F58" s="95" t="n"/>
+      <c r="G58" s="95" t="n"/>
+      <c r="H58" s="94" t="n"/>
+      <c r="I58" s="94" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B59" s="90" t="inlineStr">
+        <is>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
+      <c r="C59" s="90" t="n"/>
+      <c r="D59" s="91" t="n"/>
+      <c r="E59" s="90" t="n"/>
+      <c r="F59" s="91" t="n"/>
+      <c r="G59" s="91" t="n">
+        <v>550</v>
+      </c>
+      <c r="H59" s="90" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I59" s="90" t="inlineStr">
+        <is>
+          <t>Comissões da quinzena de 24/08 a 05/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B60" s="94" t="inlineStr">
+        <is>
+          <t>Central do Suplemento</t>
+        </is>
+      </c>
+      <c r="C60" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D60" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E60" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F60" s="95" t="n"/>
+      <c r="G60" s="95" t="n"/>
+      <c r="H60" s="94" t="n"/>
+      <c r="I60" s="94" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B61" s="90" t="inlineStr">
+        <is>
+          <t>Tarifa Pix (Cobrança QR Code)</t>
+        </is>
+      </c>
+      <c r="C61" s="90" t="n"/>
+      <c r="D61" s="91" t="n"/>
+      <c r="E61" s="90" t="n"/>
+      <c r="F61" s="91" t="n"/>
+      <c r="G61" s="91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="90" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I61" s="90" t="inlineStr">
+        <is>
+          <t>DOC 85500035</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="102" t="n"/>
+      <c r="B62" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C55" s="102" t="n"/>
-      <c r="D55" s="103">
-        <f>SUM(D5:D54)</f>
-        <v/>
-      </c>
-      <c r="E55" s="102" t="n"/>
-      <c r="F55" s="103">
-        <f>SUM(F5:F54)</f>
-        <v/>
-      </c>
-      <c r="G55" s="103">
-        <f>SUM(G5:G54)</f>
-        <v/>
-      </c>
-      <c r="H55" s="102" t="n"/>
-      <c r="I55" s="102" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="104" t="n"/>
-      <c r="B56" s="104" t="inlineStr">
+      <c r="C62" s="102" t="n"/>
+      <c r="D62" s="103">
+        <f>SUM(D5:D61)</f>
+        <v/>
+      </c>
+      <c r="E62" s="102" t="n"/>
+      <c r="F62" s="103">
+        <f>SUM(F5:F61)</f>
+        <v/>
+      </c>
+      <c r="G62" s="103">
+        <f>SUM(G5:G61)</f>
+        <v/>
+      </c>
+      <c r="H62" s="102" t="n"/>
+      <c r="I62" s="102" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="104" t="n"/>
+      <c r="B63" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C56" s="104" t="n"/>
-      <c r="D56" s="105">
-        <f>(D55-F55-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E56" s="104" t="n"/>
-      <c r="F56" s="105" t="n"/>
-      <c r="G56" s="105" t="n"/>
-      <c r="H56" s="104" t="n"/>
-      <c r="I56" s="104" t="n"/>
+      <c r="C63" s="104" t="n"/>
+      <c r="D63" s="105">
+        <f>(D62-F62-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E63" s="104" t="n"/>
+      <c r="F63" s="105" t="n"/>
+      <c r="G63" s="105" t="n"/>
+      <c r="H63" s="104" t="n"/>
+      <c r="I63" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -35728,10 +35944,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -34001,7 +34001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U63"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34149,11 +34149,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H61,K5,G5:G61)</f>
+        <f>SUMIF(H5:H63,K5,G5:G63)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D62-F62-T5</f>
+        <f>D64-F64-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34161,11 +34161,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D63</f>
+        <f>D65</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E61,"Aguardando Pagamento",D5:D61)</f>
+        <f>SUMIF(E5:E63,"Aguardando Pagamento",D5:D63)</f>
         <v/>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H61,K6,G5:G61)</f>
+        <f>SUMIF(H5:H63,K6,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H61,K7,G5:G61)</f>
+        <f>SUMIF(H5:H63,K7,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34285,7 +34285,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H61,K8,G5:G61)</f>
+        <f>SUMIF(H5:H63,K8,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34325,7 +34325,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H61,K9,G5:G61)</f>
+        <f>SUMIF(H5:H63,K9,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34365,7 +34365,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H61,K10,G5:G61)</f>
+        <f>SUMIF(H5:H63,K10,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34405,7 +34405,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H61,K11,G5:G61)</f>
+        <f>SUMIF(H5:H63,K11,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34445,7 +34445,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H61,K12,G5:G61)</f>
+        <f>SUMIF(H5:H63,K12,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34481,7 +34481,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H61,K13,G5:G61)</f>
+        <f>SUMIF(H5:H63,K13,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34521,7 +34521,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H61,K14,G5:G61)</f>
+        <f>SUMIF(H5:H63,K14,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34557,7 +34557,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H61,K15,G5:G61)</f>
+        <f>SUMIF(H5:H63,K15,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H61,K16,G5:G61)</f>
+        <f>SUMIF(H5:H63,K16,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -34633,7 +34633,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H61,K17,G5:G61)</f>
+        <f>SUMIF(H5:H63,K17,G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -35888,46 +35888,100 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="102" t="n"/>
-      <c r="B62" s="102" t="inlineStr">
+      <c r="A62" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B62" s="94" t="inlineStr">
+        <is>
+          <t>Conta de Energia Loja</t>
+        </is>
+      </c>
+      <c r="C62" s="94" t="n"/>
+      <c r="D62" s="95" t="n"/>
+      <c r="E62" s="94" t="n"/>
+      <c r="F62" s="95" t="n"/>
+      <c r="G62" s="95" t="n">
+        <v>150.06</v>
+      </c>
+      <c r="H62" s="94" t="inlineStr">
+        <is>
+          <t>Água, Energia e Internet</t>
+        </is>
+      </c>
+      <c r="I62" s="94" t="inlineStr">
+        <is>
+          <t>Neoenergia Coelba — ref. 08/2026, venc. 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="89" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B63" s="90" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
+      <c r="C63" s="90" t="n"/>
+      <c r="D63" s="91" t="n"/>
+      <c r="E63" s="90" t="n"/>
+      <c r="F63" s="91" t="n"/>
+      <c r="G63" s="91" t="n">
+        <v>878.92</v>
+      </c>
+      <c r="H63" s="90" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I63" s="90" t="inlineStr">
+        <is>
+          <t>Boleto doc. 73636 (emissão 10/06/2026) — venc. 08/09/2026. Pago em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="102" t="n"/>
+      <c r="B64" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C62" s="102" t="n"/>
-      <c r="D62" s="103">
-        <f>SUM(D5:D61)</f>
-        <v/>
-      </c>
-      <c r="E62" s="102" t="n"/>
-      <c r="F62" s="103">
-        <f>SUM(F5:F61)</f>
-        <v/>
-      </c>
-      <c r="G62" s="103">
-        <f>SUM(G5:G61)</f>
-        <v/>
-      </c>
-      <c r="H62" s="102" t="n"/>
-      <c r="I62" s="102" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="104" t="n"/>
-      <c r="B63" s="104" t="inlineStr">
+      <c r="C64" s="102" t="n"/>
+      <c r="D64" s="103">
+        <f>SUM(D5:D63)</f>
+        <v/>
+      </c>
+      <c r="E64" s="102" t="n"/>
+      <c r="F64" s="103">
+        <f>SUM(F5:F63)</f>
+        <v/>
+      </c>
+      <c r="G64" s="103">
+        <f>SUM(G5:G63)</f>
+        <v/>
+      </c>
+      <c r="H64" s="102" t="n"/>
+      <c r="I64" s="102" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="104" t="n"/>
+      <c r="B65" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C63" s="104" t="n"/>
-      <c r="D63" s="105">
-        <f>(D62-F62-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E63" s="104" t="n"/>
-      <c r="F63" s="105" t="n"/>
-      <c r="G63" s="105" t="n"/>
-      <c r="H63" s="104" t="n"/>
-      <c r="I63" s="104" t="n"/>
+      <c r="C65" s="104" t="n"/>
+      <c r="D65" s="105">
+        <f>(D64-F64-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E65" s="104" t="n"/>
+      <c r="F65" s="105" t="n"/>
+      <c r="G65" s="105" t="n"/>
+      <c r="H65" s="104" t="n"/>
+      <c r="I65" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -35944,10 +35998,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -40211,7 +40265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -40625,7 +40679,7 @@
       </c>
       <c r="E20" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F20" s="125">
@@ -40634,7 +40688,7 @@
       </c>
       <c r="G20" s="94" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Água, Energia e Internet.</t>
+          <t>Categoria: Água, Energia e Internet. Pago em 08/09/2026 — lançado em Set 2026 como "Conta de Energia Loja".</t>
         </is>
       </c>
     </row>
@@ -40657,7 +40711,7 @@
       </c>
       <c r="E21" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F21" s="124">
@@ -40666,7 +40720,7 @@
       </c>
       <c r="G21" s="90" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7, nosso número 112/24142153-9. Após 1 dia do vencimento: juros R$ 0,29/dia + multa 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/09/2026 — lançado em Set 2026 como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -41208,14 +41262,18 @@
       </c>
       <c r="E48" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F48" s="124">
         <f>IF(OR($E48="Recebido",$C48=""),"",MAX(0,TODAY()-$C48))</f>
         <v/>
       </c>
-      <c r="G48" s="90" t="n"/>
+      <c r="G48" s="90" t="inlineStr">
+        <is>
+          <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="94" t="inlineStr">
@@ -41460,7 +41518,7 @@
       </c>
       <c r="E56" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F56" s="124">
@@ -41469,7 +41527,7 @@
       </c>
       <c r="G56" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.294 de 05/08/2026 · OC AEMPPO00004359 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41492,7 +41550,7 @@
       </c>
       <c r="E57" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F57" s="125">
@@ -41501,7 +41559,7 @@
       </c>
       <c r="G57" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.295 de 05/08/2026 · OC AEMPPO00004358 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41524,7 +41582,7 @@
       </c>
       <c r="E58" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F58" s="124">
@@ -41533,7 +41591,7 @@
       </c>
       <c r="G58" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.298 de 06/08/2026 · OC AEDPO00004751 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41556,7 +41614,7 @@
       </c>
       <c r="E59" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F59" s="125">
@@ -41565,7 +41623,7 @@
       </c>
       <c r="G59" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.299 de 06/08/2026 · OC AEDPO00004750 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41588,7 +41646,7 @@
       </c>
       <c r="E60" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F60" s="124">
@@ -41597,7 +41655,7 @@
       </c>
       <c r="G60" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.300 de 06/08/2026 · OC AEDPO00004743 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41620,7 +41678,7 @@
       </c>
       <c r="E61" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F61" s="125">
@@ -41629,7 +41687,7 @@
       </c>
       <c r="G61" s="94" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.301 de 06/08/2026 · OC AEDPO00004749 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41652,7 +41710,7 @@
       </c>
       <c r="E62" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F62" s="124">
@@ -41661,7 +41719,7 @@
       </c>
       <c r="G62" s="90" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.302 de 06/08/2026 · OC APECPO00019551 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
@@ -41748,14 +41806,18 @@
       </c>
       <c r="E65" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F65" s="125">
         <f>IF(OR($E65="Recebido",$C65=""),"",MAX(0,TODAY()-$C65))</f>
         <v/>
       </c>
-      <c r="G65" s="94" t="inlineStr"/>
+      <c r="G65" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="90" t="inlineStr">
@@ -41974,43 +42036,61 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="98" t="inlineStr">
-        <is>
-          <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
-        </is>
-      </c>
-      <c r="B73" s="98" t="n"/>
-      <c r="C73" s="126" t="n"/>
-      <c r="D73" s="127">
-        <f>SUMIF(E42:E72,"Pendente",D42:D72)</f>
-        <v/>
-      </c>
-      <c r="E73" s="128" t="n"/>
+      <c r="A73" s="90" t="inlineStr">
+        <is>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+        </is>
+      </c>
+      <c r="B73" s="90" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C73" s="89" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D73" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E73" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F73" s="160" t="n"/>
       <c r="G73" s="161" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="129" t="inlineStr">
-        <is>
-          <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
-        </is>
-      </c>
-      <c r="B74" s="130" t="n"/>
-      <c r="C74" s="131" t="n"/>
-      <c r="D74" s="132">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="E74" s="205">
-        <f>IF(ROUND(D73-D74,2)=0,"✔ O detalhe bate com as abas dos meses.","⚠ DIVERGÊNCIA de "&amp;TEXT(D73-D74,"R$ #,##0.00")&amp;" — alguma venda foi paga na aba do mês e não teve o Status atualizado aqui (ou o contrário).")</f>
-        <v/>
-      </c>
+      <c r="A74" s="98" t="inlineStr">
+        <is>
+          <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
+        </is>
+      </c>
+      <c r="B74" s="98" t="n"/>
+      <c r="C74" s="126" t="n"/>
+      <c r="D74" s="127">
+        <f>SUMIF(E42:E73,"Pendente",D42:D73)</f>
+        <v/>
+      </c>
+      <c r="E74" s="128" t="n"/>
       <c r="F74" s="160" t="n"/>
       <c r="G74" s="161" t="n"/>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="200" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="129" t="inlineStr">
+        <is>
+          <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
+        </is>
+      </c>
+      <c r="B75" s="160" t="n"/>
+      <c r="C75" s="160" t="n"/>
+      <c r="D75" s="160" t="n"/>
+      <c r="E75" s="160" t="n"/>
+      <c r="F75" s="160" t="n"/>
+      <c r="G75" s="161" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -42036,7 +42116,7 @@
     <dataValidation sqref="E11:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago"</formula1>
     </dataValidation>
-    <dataValidation sqref="E42:E72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E42:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -46,11 +46,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="76">
     <font>
@@ -34001,7 +34000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U65"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34149,11 +34148,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H63,K5,G5:G63)</f>
+        <f>SUMIF(H5:H75,K5,G5:G75)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D64-F64-T5</f>
+        <f>D76-F76-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34161,11 +34160,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D65</f>
+        <f>D77</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E63,"Aguardando Pagamento",D5:D63)</f>
+        <f>SUMIF(E5:E75,"Aguardando Pagamento",D5:D75)</f>
         <v/>
       </c>
     </row>
@@ -34205,7 +34204,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H63,K6,G5:G63)</f>
+        <f>SUMIF(H5:H75,K6,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34245,7 +34244,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H63,K7,G5:G63)</f>
+        <f>SUMIF(H5:H75,K7,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34285,7 +34284,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H63,K8,G5:G63)</f>
+        <f>SUMIF(H5:H75,K8,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34325,7 +34324,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H63,K9,G5:G63)</f>
+        <f>SUMIF(H5:H75,K9,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34365,7 +34364,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H63,K10,G5:G63)</f>
+        <f>SUMIF(H5:H75,K10,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34405,7 +34404,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H63,K11,G5:G63)</f>
+        <f>SUMIF(H5:H75,K11,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34445,7 +34444,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H63,K12,G5:G63)</f>
+        <f>SUMIF(H5:H75,K12,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34481,7 +34480,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H63,K13,G5:G63)</f>
+        <f>SUMIF(H5:H75,K13,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34521,7 +34520,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H63,K14,G5:G63)</f>
+        <f>SUMIF(H5:H75,K14,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34557,7 +34556,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H63,K15,G5:G63)</f>
+        <f>SUMIF(H5:H75,K15,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34593,7 +34592,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H63,K16,G5:G63)</f>
+        <f>SUMIF(H5:H75,K16,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -34633,7 +34632,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H63,K17,G5:G63)</f>
+        <f>SUMIF(H5:H75,K17,G5:G75)</f>
         <v/>
       </c>
     </row>
@@ -35942,46 +35941,374 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="102" t="n"/>
-      <c r="B64" s="102" t="inlineStr">
+      <c r="A64" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B64" s="94" t="inlineStr">
+        <is>
+          <t>Juliane Rosa de Oliveira</t>
+        </is>
+      </c>
+      <c r="C64" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D64" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E64" s="94" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F64" s="95" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G64" s="95" t="n"/>
+      <c r="H64" s="94" t="n"/>
+      <c r="I64" s="94" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B65" s="90" t="inlineStr">
+        <is>
+          <t>Erika Lopes de Guimaraes</t>
+        </is>
+      </c>
+      <c r="C65" s="90" t="inlineStr">
+        <is>
+          <t>Refil FPA14</t>
+        </is>
+      </c>
+      <c r="D65" s="91" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" s="90" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F65" s="91" t="n"/>
+      <c r="G65" s="91" t="n"/>
+      <c r="H65" s="90" t="n"/>
+      <c r="I65" s="90" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B66" s="94" t="inlineStr">
+        <is>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+        </is>
+      </c>
+      <c r="C66" s="94" t="inlineStr">
+        <is>
+          <t>Refil Plissado + Refil BAG</t>
+        </is>
+      </c>
+      <c r="D66" s="95" t="n">
+        <v>150</v>
+      </c>
+      <c r="E66" s="94" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F66" s="95" t="n"/>
+      <c r="G66" s="95" t="n"/>
+      <c r="H66" s="94" t="n"/>
+      <c r="I66" s="94" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B67" s="90" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C67" s="90" t="n"/>
+      <c r="D67" s="91" t="n"/>
+      <c r="E67" s="90" t="n"/>
+      <c r="F67" s="91" t="n"/>
+      <c r="G67" s="91" t="n">
+        <v>649.83</v>
+      </c>
+      <c r="H67" s="90" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I67" s="90" t="inlineStr">
+        <is>
+          <t>Boleto doc. 133138/1 (emissão 12/08/2026) — venc. 09/09/2026. Pago em 09/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B68" s="94" t="inlineStr">
+        <is>
+          <t>Sindicato dos Empregados no Comércio de Jacobina</t>
+        </is>
+      </c>
+      <c r="C68" s="94" t="n"/>
+      <c r="D68" s="95" t="n"/>
+      <c r="E68" s="94" t="n"/>
+      <c r="F68" s="95" t="n"/>
+      <c r="G68" s="95" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H68" s="94" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I68" s="94" t="inlineStr">
+        <is>
+          <t>Contribuição assistencial — competência junho/2026. Venc. 10/09/2026, pago em 09/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B69" s="90" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="C69" s="90" t="n"/>
+      <c r="D69" s="91" t="n"/>
+      <c r="E69" s="90" t="n"/>
+      <c r="F69" s="91" t="n"/>
+      <c r="G69" s="91" t="n">
+        <v>400</v>
+      </c>
+      <c r="H69" s="90" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I69" s="90" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B70" s="94" t="inlineStr">
+        <is>
+          <t>Antonio Felix dos Santos</t>
+        </is>
+      </c>
+      <c r="C70" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D70" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E70" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F70" s="95" t="n"/>
+      <c r="G70" s="95" t="n"/>
+      <c r="H70" s="94" t="n"/>
+      <c r="I70" s="94" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B71" s="90" t="inlineStr">
+        <is>
+          <t>Arivaldo Teixeira Advocacia</t>
+        </is>
+      </c>
+      <c r="C71" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D71" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E71" s="90" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F71" s="91" t="n"/>
+      <c r="G71" s="91" t="n"/>
+      <c r="H71" s="90" t="n"/>
+      <c r="I71" s="90" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B72" s="94" t="inlineStr">
+        <is>
+          <t>Central do Suplemento</t>
+        </is>
+      </c>
+      <c r="C72" s="94" t="inlineStr">
+        <is>
+          <t>2x Botão do Purificador Everest</t>
+        </is>
+      </c>
+      <c r="D72" s="95" t="n">
+        <v>60</v>
+      </c>
+      <c r="E72" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F72" s="95" t="n"/>
+      <c r="G72" s="95" t="n"/>
+      <c r="H72" s="94" t="n"/>
+      <c r="I72" s="94" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B73" s="90" t="inlineStr">
+        <is>
+          <t>Tereza Cristina Aquino Martins - Escritório</t>
+        </is>
+      </c>
+      <c r="C73" s="90" t="inlineStr">
+        <is>
+          <t>Refil FPA14 + Refil Universal</t>
+        </is>
+      </c>
+      <c r="D73" s="91" t="n">
+        <v>130</v>
+      </c>
+      <c r="E73" s="90" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F73" s="91" t="n"/>
+      <c r="G73" s="91" t="n"/>
+      <c r="H73" s="90" t="n"/>
+      <c r="I73" s="90" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B74" s="94" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C74" s="94" t="inlineStr">
+        <is>
+          <t>Mangueira (11m)</t>
+        </is>
+      </c>
+      <c r="D74" s="95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F74" s="95" t="n"/>
+      <c r="G74" s="95" t="n"/>
+      <c r="H74" s="94" t="n"/>
+      <c r="I74" s="94" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B75" s="90" t="inlineStr">
+        <is>
+          <t>Rebeca Oliveira Soares Avelino</t>
+        </is>
+      </c>
+      <c r="C75" s="90" t="inlineStr">
+        <is>
+          <t>Purificador Everest Fit Branco</t>
+        </is>
+      </c>
+      <c r="D75" s="91" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E75" s="90" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F75" s="91" t="n">
+        <v>181.73</v>
+      </c>
+      <c r="G75" s="91" t="n"/>
+      <c r="H75" s="90" t="n"/>
+      <c r="I75" s="90" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="102" t="n"/>
+      <c r="B76" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C64" s="102" t="n"/>
-      <c r="D64" s="103">
-        <f>SUM(D5:D63)</f>
-        <v/>
-      </c>
-      <c r="E64" s="102" t="n"/>
-      <c r="F64" s="103">
-        <f>SUM(F5:F63)</f>
-        <v/>
-      </c>
-      <c r="G64" s="103">
-        <f>SUM(G5:G63)</f>
-        <v/>
-      </c>
-      <c r="H64" s="102" t="n"/>
-      <c r="I64" s="102" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="104" t="n"/>
-      <c r="B65" s="104" t="inlineStr">
+      <c r="C76" s="102" t="n"/>
+      <c r="D76" s="103">
+        <f>SUM(D5:D75)</f>
+        <v/>
+      </c>
+      <c r="E76" s="102" t="n"/>
+      <c r="F76" s="103">
+        <f>SUM(F5:F75)</f>
+        <v/>
+      </c>
+      <c r="G76" s="103">
+        <f>SUM(G5:G75)</f>
+        <v/>
+      </c>
+      <c r="H76" s="102" t="n"/>
+      <c r="I76" s="102" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="104" t="n"/>
+      <c r="B77" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C65" s="104" t="n"/>
-      <c r="D65" s="105">
-        <f>(D64-F64-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E65" s="104" t="n"/>
-      <c r="F65" s="105" t="n"/>
-      <c r="G65" s="105" t="n"/>
-      <c r="H65" s="104" t="n"/>
-      <c r="I65" s="104" t="n"/>
+      <c r="C77" s="104" t="n"/>
+      <c r="D77" s="105">
+        <f>(D76-F76-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E77" s="104" t="n"/>
+      <c r="F77" s="105" t="n"/>
+      <c r="G77" s="105" t="n"/>
+      <c r="H77" s="104" t="n"/>
+      <c r="I77" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -35998,10 +36325,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -40265,7 +40592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -40743,7 +41070,7 @@
       </c>
       <c r="E22" s="125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F22" s="125">
@@ -40752,7 +41079,7 @@
       </c>
       <c r="G22" s="94" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7, nosso número 109/00257849-8. Após o vencimento: multa 1,9% + juros 0,1% ao dia; protesto no Serasa no 5º dia útil.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7, nosso número 109/00257849-8. Pago em 09/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -40775,7 +41102,7 @@
       </c>
       <c r="E23" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F23" s="124">
@@ -40784,7 +41111,7 @@
       </c>
       <c r="G23" s="90" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas.</t>
+          <t>Categoria: Impostos e Taxas. Pago em 09/09/2026 (antecipado, venc. 10/09) — lançado em "Set 2026" como "Sindicato dos Empregados no Comércio de Jacobina".</t>
         </is>
       </c>
     </row>
@@ -40821,55 +41148,55 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="90" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>Patrus Transportes Ltda</t>
+        </is>
+      </c>
+      <c r="B25" s="94" t="inlineStr">
+        <is>
+          <t>Frete — fatura 26-08-913041 (CT-e 2117850, remetente Eversoft, NF 75472)</t>
+        </is>
+      </c>
+      <c r="C25" s="93" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D25" s="95" t="n">
+        <v>292.68</v>
+      </c>
+      <c r="E25" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F25" s="125">
+        <f>IF(OR($E25="Pago",$C25=""),"",MAX(0,TODAY()-$C25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840262224-4, cedente 6348-/017737-7. Após o vencimento: R$ 0,44 por dia de atraso; protesto a partir do 7º dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="90" t="inlineStr">
         <is>
           <t>FGTS Digital (GFD)</t>
         </is>
       </c>
-      <c r="B25" s="90" t="inlineStr">
+      <c r="B26" s="90" t="inlineStr">
         <is>
           <t>FGTS mensal — competência 08/2026</t>
         </is>
       </c>
-      <c r="C25" s="89" t="n">
+      <c r="C26" s="89" t="n">
         <v>46283</v>
       </c>
-      <c r="D25" s="91" t="n">
+      <c r="D26" s="91" t="n">
         <v>136</v>
       </c>
-      <c r="E25" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F25" s="124">
-        <f>IF(OR($E25="Pago",$C25=""),"",MAX(0,TODAY()-$C25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="90" t="inlineStr">
-        <is>
-          <t>Categoria quando pagar: Impostos e Taxas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="94" t="inlineStr">
-        <is>
-          <t>Receita Federal</t>
-        </is>
-      </c>
-      <c r="B26" s="94" t="inlineStr">
-        <is>
-          <t>DARF / INSS — período de apuração agosto/2026</t>
-        </is>
-      </c>
-      <c r="C26" s="93" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D26" s="95" t="n">
-        <v>306.99</v>
-      </c>
-      <c r="E26" s="125" t="inlineStr">
+      <c r="E26" s="124" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -40878,23 +41205,43 @@
         <f>IF(OR($E26="Pago",$C26=""),"",MAX(0,TODAY()-$C26))</f>
         <v/>
       </c>
-      <c r="G26" s="94" t="inlineStr">
+      <c r="G26" s="90" t="inlineStr">
         <is>
           <t>Categoria quando pagar: Impostos e Taxas.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="90" t="n"/>
-      <c r="B27" s="90" t="n"/>
-      <c r="C27" s="89" t="n"/>
-      <c r="D27" s="91" t="n"/>
-      <c r="E27" s="124" t="n"/>
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>Receita Federal</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>DARF / INSS — período de apuração agosto/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="93" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D27" s="95" t="n">
+        <v>306.99</v>
+      </c>
+      <c r="E27" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F27" s="124">
         <f>IF(OR($E27="Pago",$C27=""),"",MAX(0,TODAY()-$C27))</f>
         <v/>
       </c>
-      <c r="G27" s="90" t="n"/>
+      <c r="G27" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="94" t="n"/>
@@ -42057,40 +42404,81 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F73" s="160" t="n"/>
-      <c r="G73" s="161" t="n"/>
+      <c r="F73" s="124">
+        <f>IF(OR($E73="Recebido",$C73=""),"",MAX(0,TODAY()-$C73))</f>
+        <v/>
+      </c>
+      <c r="G73" s="90" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="98" t="inlineStr">
+      <c r="A74" s="90" t="inlineStr">
+        <is>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+        </is>
+      </c>
+      <c r="B74" s="90" t="inlineStr">
+        <is>
+          <t>Refil Plissado + Refil BAG</t>
+        </is>
+      </c>
+      <c r="C74" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D74" s="91" t="n">
+        <v>150</v>
+      </c>
+      <c r="E74" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F74" s="124">
+        <f>IF(OR($E74="Recebido",$C74=""),"",MAX(0,TODAY()-$C74))</f>
+        <v/>
+      </c>
+      <c r="G74" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B74" s="98" t="n"/>
-      <c r="C74" s="126" t="n"/>
-      <c r="D74" s="127">
-        <f>SUMIF(E42:E73,"Pendente",D42:D73)</f>
-        <v/>
-      </c>
-      <c r="E74" s="128" t="n"/>
-      <c r="F74" s="160" t="n"/>
-      <c r="G74" s="161" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="129" t="inlineStr">
+      <c r="B75" s="98" t="n"/>
+      <c r="C75" s="126" t="n"/>
+      <c r="D75" s="127">
+        <f>SUMIF(E42:E74,"Pendente",D42:D74)</f>
+        <v/>
+      </c>
+      <c r="E75" s="128" t="n"/>
+      <c r="F75" s="128" t="n"/>
+      <c r="G75" s="98" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B75" s="160" t="n"/>
-      <c r="C75" s="160" t="n"/>
-      <c r="D75" s="160" t="n"/>
-      <c r="E75" s="160" t="n"/>
-      <c r="F75" s="160" t="n"/>
-      <c r="G75" s="161" t="n"/>
+      <c r="B76" s="160" t="n"/>
+      <c r="C76" s="160" t="n"/>
+      <c r="D76" s="160" t="n"/>
+      <c r="E76" s="160" t="n"/>
+      <c r="F76" s="160" t="n"/>
+      <c r="G76" s="161" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="200" t="inlineStr">
+      <c r="A77" s="200">
+        <f>IF(ROUND(D75-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D75-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -42104,12 +42492,12 @@
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A77:G77"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
@@ -43170,11 +43558,11 @@
         </is>
       </c>
       <c r="B9" s="121" t="n">
-        <v>17000</v>
+        <v>23500</v>
       </c>
       <c r="C9" s="152" t="inlineStr">
         <is>
-          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00. R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) (ver aba "Capital de Giro (BB)") — mas como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida, em vez de sair dela. Por isso os R$ 17.000,00 inteiros ficam guardados como reserva.</t>
+          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Total guardado: R$ 23.500,00.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -635,7 +635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -794,11 +794,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1330,6 +1374,8 @@
     <xf numFmtId="0" fontId="49" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="31" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="31" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3521,11 +3567,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="158" min="1" max="1"/>
     <col width="15" customWidth="1" style="158" min="2" max="9"/>
+    <col width="13" customWidth="1" style="158" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="158">
@@ -3538,7 +3585,7 @@
     <row r="2">
       <c r="A2" s="219" t="inlineStr">
         <is>
-          <t>Quanto sobra de verdade em cada item vendido. Preencha o custo de aquisição (amarelo) — os preços já vieram das vendas de Ago/2026.</t>
+          <t>Quanto sobra de verdade em cada item vendido. Custo = última compra de 2026 (IPI incluso, Simples não recupera) + 6,4% de frete de entrada nos itens da Everest e Eversoft, que são FOB. Filtros Planeta Água, Culligan e Knox são CIF: frete já vem no preço.</t>
         </is>
       </c>
     </row>
@@ -3568,14 +3615,14 @@
       </c>
       <c r="E4" s="152" t="inlineStr">
         <is>
-          <t>← ajuste conforme sua maquininha e seu regime tributário (confirme com o contador)</t>
+          <t>← taxa dos itens de balcão. Purificadores usam 13,99% (crédito 10x) direto na fórmula; Baby usa 11% (6x).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="221" t="inlineStr">
         <is>
-          <t>⚠ Enquanto a coluna "Custo de Aquisição" estiver em branco, a Margem mostrada é o preço quase cheio — não é a margem real.</t>
+          <t>COMISSÃO: só entra quando o Wiliam faz a troca/instalação. Venda de balcão sem serviço = margem R$ 10 (ou R$ 30) maior. Refis de outras marcas ficam sem comissão porque raramente são trocados por ele.</t>
         </is>
       </c>
     </row>
@@ -3625,6 +3672,11 @@
           <t>Margem (%)</t>
         </is>
       </c>
+      <c r="J6" s="63" t="inlineStr">
+        <is>
+          <t>Taxa aplicada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="64" t="inlineStr">
@@ -3635,12 +3687,14 @@
       <c r="B7" s="67" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="121" t="n"/>
+      <c r="C7" s="121" t="n">
+        <v>46.76</v>
+      </c>
       <c r="D7" s="67" t="n">
         <v>10</v>
       </c>
       <c r="E7" s="67">
-        <f>IF(B7="","",B7*$B$4)</f>
+        <f>IF(B7="","",B7*IF($J7="",$B$4,$J7))</f>
         <v/>
       </c>
       <c r="F7" s="67">
@@ -3659,6 +3713,7 @@
         <f>IF(B7=0,"",H7/B7)</f>
         <v/>
       </c>
+      <c r="J7" s="239" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="66" t="inlineStr">
@@ -3669,12 +3724,14 @@
       <c r="B8" s="69" t="n">
         <v>140</v>
       </c>
-      <c r="C8" s="121" t="n"/>
+      <c r="C8" s="121" t="n">
+        <v>26.89</v>
+      </c>
       <c r="D8" s="69" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="69">
-        <f>IF(B8="","",B8*$B$4)</f>
+        <f>IF(B8="","",B8*IF($J8="",$B$4,$J8))</f>
         <v/>
       </c>
       <c r="F8" s="69">
@@ -3693,6 +3750,7 @@
         <f>IF(B8=0,"",H8/B8)</f>
         <v/>
       </c>
+      <c r="J8" s="240" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="64" t="inlineStr">
@@ -3703,12 +3761,14 @@
       <c r="B9" s="67" t="n">
         <v>90</v>
       </c>
-      <c r="C9" s="121" t="n"/>
+      <c r="C9" s="121" t="n">
+        <v>32.48</v>
+      </c>
       <c r="D9" s="67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" s="67">
-        <f>IF(B9="","",B9*$B$4)</f>
+        <f>IF(B9="","",B9*IF($J9="",$B$4,$J9))</f>
         <v/>
       </c>
       <c r="F9" s="67">
@@ -3727,6 +3787,7 @@
         <f>IF(B9=0,"",H9/B9)</f>
         <v/>
       </c>
+      <c r="J9" s="239" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="66" t="inlineStr">
@@ -3737,12 +3798,14 @@
       <c r="B10" s="69" t="n">
         <v>60</v>
       </c>
-      <c r="C10" s="121" t="n"/>
+      <c r="C10" s="121" t="n">
+        <v>38.23</v>
+      </c>
       <c r="D10" s="69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" s="69">
-        <f>IF(B10="","",B10*$B$4)</f>
+        <f>IF(B10="","",B10*IF($J10="",$B$4,$J10))</f>
         <v/>
       </c>
       <c r="F10" s="69">
@@ -3761,6 +3824,7 @@
         <f>IF(B10=0,"",H10/B10)</f>
         <v/>
       </c>
+      <c r="J10" s="240" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="64" t="inlineStr">
@@ -3771,12 +3835,14 @@
       <c r="B11" s="67" t="n">
         <v>110</v>
       </c>
-      <c r="C11" s="121" t="n"/>
+      <c r="C11" s="121" t="n">
+        <v>20.17</v>
+      </c>
       <c r="D11" s="67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E11" s="67">
-        <f>IF(B11="","",B11*$B$4)</f>
+        <f>IF(B11="","",B11*IF($J11="",$B$4,$J11))</f>
         <v/>
       </c>
       <c r="F11" s="67">
@@ -3795,6 +3861,7 @@
         <f>IF(B11=0,"",H11/B11)</f>
         <v/>
       </c>
+      <c r="J11" s="239" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="66" t="inlineStr">
@@ -3805,12 +3872,14 @@
       <c r="B12" s="69" t="n">
         <v>90</v>
       </c>
-      <c r="C12" s="121" t="n"/>
+      <c r="C12" s="121" t="n">
+        <v>18.23</v>
+      </c>
       <c r="D12" s="69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E12" s="69">
-        <f>IF(B12="","",B12*$B$4)</f>
+        <f>IF(B12="","",B12*IF($J12="",$B$4,$J12))</f>
         <v/>
       </c>
       <c r="F12" s="69">
@@ -3829,6 +3898,7 @@
         <f>IF(B12=0,"",H12/B12)</f>
         <v/>
       </c>
+      <c r="J12" s="240" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="64" t="inlineStr">
@@ -3839,12 +3909,14 @@
       <c r="B13" s="67" t="n">
         <v>115</v>
       </c>
-      <c r="C13" s="121" t="n"/>
+      <c r="C13" s="121" t="n">
+        <v>24</v>
+      </c>
       <c r="D13" s="67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E13" s="67">
-        <f>IF(B13="","",B13*$B$4)</f>
+        <f>IF(B13="","",B13*IF($J13="",$B$4,$J13))</f>
         <v/>
       </c>
       <c r="F13" s="67">
@@ -3863,6 +3935,7 @@
         <f>IF(B13=0,"",H13/B13)</f>
         <v/>
       </c>
+      <c r="J13" s="239" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="66" t="inlineStr">
@@ -3873,12 +3946,14 @@
       <c r="B14" s="69" t="n">
         <v>60</v>
       </c>
-      <c r="C14" s="121" t="n"/>
+      <c r="C14" s="121" t="n">
+        <v>10.84</v>
+      </c>
       <c r="D14" s="69" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="69">
-        <f>IF(B14="","",B14*$B$4)</f>
+        <f>IF(B14="","",B14*IF($J14="",$B$4,$J14))</f>
         <v/>
       </c>
       <c r="F14" s="69">
@@ -3897,22 +3972,25 @@
         <f>IF(B14=0,"",H14/B14)</f>
         <v/>
       </c>
+      <c r="J14" s="240" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="64" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Mangueira (2 m)</t>
         </is>
       </c>
       <c r="B15" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="C15" s="121" t="n"/>
+      <c r="C15" s="121" t="n">
+        <v>3.44</v>
+      </c>
       <c r="D15" s="67" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="67">
-        <f>IF(B15="","",B15*$B$4)</f>
+        <f>IF(B15="","",B15*IF($J15="",$B$4,$J15))</f>
         <v/>
       </c>
       <c r="F15" s="67">
@@ -3931,6 +4009,7 @@
         <f>IF(B15=0,"",H15/B15)</f>
         <v/>
       </c>
+      <c r="J15" s="239" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
@@ -3941,12 +4020,14 @@
       <c r="B16" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="C16" s="121" t="n"/>
+      <c r="C16" s="121" t="n">
+        <v>5.19</v>
+      </c>
       <c r="D16" s="69" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="69">
-        <f>IF(B16="","",B16*$B$4)</f>
+        <f>IF(B16="","",B16*IF($J16="",$B$4,$J16))</f>
         <v/>
       </c>
       <c r="F16" s="69">
@@ -3965,6 +4046,7 @@
         <f>IF(B16=0,"",H16/B16)</f>
         <v/>
       </c>
+      <c r="J16" s="240" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="64" t="inlineStr">
@@ -3980,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="67">
-        <f>IF(B17="","",B17*$B$4)</f>
+        <f>IF(B17="","",B17*IF($J17="",$B$4,$J17))</f>
         <v/>
       </c>
       <c r="F17" s="67">
@@ -3999,6 +4081,7 @@
         <f>IF(B17=0,"",H17/B17)</f>
         <v/>
       </c>
+      <c r="J17" s="239" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
@@ -4009,12 +4092,14 @@
       <c r="B18" s="69" t="n">
         <v>40</v>
       </c>
-      <c r="C18" s="121" t="n"/>
+      <c r="C18" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="D18" s="69" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="69">
-        <f>IF(B18="","",B18*$B$4)</f>
+        <f>IF(B18="","",B18*IF($J18="",$B$4,$J18))</f>
         <v/>
       </c>
       <c r="F18" s="69">
@@ -4033,6 +4118,7 @@
         <f>IF(B18=0,"",H18/B18)</f>
         <v/>
       </c>
+      <c r="J18" s="240" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="64" t="inlineStr">
@@ -4043,12 +4129,14 @@
       <c r="B19" s="67" t="n">
         <v>100</v>
       </c>
-      <c r="C19" s="121" t="n"/>
+      <c r="C19" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="D19" s="67" t="n">
         <v>30</v>
       </c>
       <c r="E19" s="67">
-        <f>IF(B19="","",B19*$B$4)</f>
+        <f>IF(B19="","",B19*IF($J19="",$B$4,$J19))</f>
         <v/>
       </c>
       <c r="F19" s="67">
@@ -4067,6 +4155,7 @@
         <f>IF(B19=0,"",H19/B19)</f>
         <v/>
       </c>
+      <c r="J19" s="239" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
@@ -4075,14 +4164,16 @@
         </is>
       </c>
       <c r="B20" s="69" t="n">
-        <v>1324</v>
-      </c>
-      <c r="C20" s="121" t="n"/>
+        <v>1429</v>
+      </c>
+      <c r="C20" s="121" t="n">
+        <v>715.02</v>
+      </c>
       <c r="D20" s="69" t="n">
         <v>30</v>
       </c>
       <c r="E20" s="69">
-        <f>IF(B20="","",B20*$B$4)</f>
+        <f>IF(B20="","",B20*IF($J20="",$B$4,$J20))</f>
         <v/>
       </c>
       <c r="F20" s="69">
@@ -4101,6 +4192,9 @@
         <f>IF(B20=0,"",H20/B20)</f>
         <v/>
       </c>
+      <c r="J20" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="64" t="inlineStr">
@@ -4109,14 +4203,16 @@
         </is>
       </c>
       <c r="B21" s="67" t="n">
-        <v>1415</v>
-      </c>
-      <c r="C21" s="121" t="n"/>
+        <v>1486</v>
+      </c>
+      <c r="C21" s="121" t="n">
+        <v>784.97</v>
+      </c>
       <c r="D21" s="67" t="n">
         <v>30</v>
       </c>
       <c r="E21" s="67">
-        <f>IF(B21="","",B21*$B$4)</f>
+        <f>IF(B21="","",B21*IF($J21="",$B$4,$J21))</f>
         <v/>
       </c>
       <c r="F21" s="67">
@@ -4135,6 +4231,9 @@
         <f>IF(B21=0,"",H21/B21)</f>
         <v/>
       </c>
+      <c r="J21" s="239" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
@@ -4143,14 +4242,16 @@
         </is>
       </c>
       <c r="B22" s="69" t="n">
-        <v>1332</v>
-      </c>
-      <c r="C22" s="121" t="n"/>
+        <v>1429</v>
+      </c>
+      <c r="C22" s="121" t="n">
+        <v>756.73</v>
+      </c>
       <c r="D22" s="69" t="n">
         <v>30</v>
       </c>
       <c r="E22" s="69">
-        <f>IF(B22="","",B22*$B$4)</f>
+        <f>IF(B22="","",B22*IF($J22="",$B$4,$J22))</f>
         <v/>
       </c>
       <c r="F22" s="69">
@@ -4169,6 +4270,9 @@
         <f>IF(B22=0,"",H22/B22)</f>
         <v/>
       </c>
+      <c r="J22" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="64" t="inlineStr">
@@ -4177,14 +4281,16 @@
         </is>
       </c>
       <c r="B23" s="67" t="n">
-        <v>1499</v>
-      </c>
-      <c r="C23" s="121" t="n"/>
+        <v>1529</v>
+      </c>
+      <c r="C23" s="121" t="n">
+        <v>820.73</v>
+      </c>
       <c r="D23" s="67" t="n">
         <v>30</v>
       </c>
       <c r="E23" s="67">
-        <f>IF(B23="","",B23*$B$4)</f>
+        <f>IF(B23="","",B23*IF($J23="",$B$4,$J23))</f>
         <v/>
       </c>
       <c r="F23" s="67">
@@ -4203,6 +4309,9 @@
         <f>IF(B23=0,"",H23/B23)</f>
         <v/>
       </c>
+      <c r="J23" s="239" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
@@ -4211,14 +4320,16 @@
         </is>
       </c>
       <c r="B24" s="69" t="n">
-        <v>1460</v>
-      </c>
-      <c r="C24" s="121" t="n"/>
+        <v>1569</v>
+      </c>
+      <c r="C24" s="121" t="n">
+        <v>906.9299999999999</v>
+      </c>
       <c r="D24" s="69" t="n">
         <v>30</v>
       </c>
       <c r="E24" s="69">
-        <f>IF(B24="","",B24*$B$4)</f>
+        <f>IF(B24="","",B24*IF($J24="",$B$4,$J24))</f>
         <v/>
       </c>
       <c r="F24" s="69">
@@ -4237,6 +4348,9 @@
         <f>IF(B24=0,"",H24/B24)</f>
         <v/>
       </c>
+      <c r="J24" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="64" t="inlineStr">
@@ -4245,14 +4359,16 @@
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>1324</v>
-      </c>
-      <c r="C25" s="121" t="n"/>
+        <v>1429</v>
+      </c>
+      <c r="C25" s="121" t="n">
+        <v>756.73</v>
+      </c>
       <c r="D25" s="67" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="67">
-        <f>IF(B25="","",B25*$B$4)</f>
+        <f>IF(B25="","",B25*IF($J25="",$B$4,$J25))</f>
         <v/>
       </c>
       <c r="F25" s="67">
@@ -4271,6 +4387,9 @@
         <f>IF(B25=0,"",H25/B25)</f>
         <v/>
       </c>
+      <c r="J25" s="239" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="66" t="inlineStr">
@@ -4279,14 +4398,16 @@
         </is>
       </c>
       <c r="B26" s="69" t="n">
-        <v>1449</v>
-      </c>
-      <c r="C26" s="121" t="n"/>
+        <v>1486</v>
+      </c>
+      <c r="C26" s="121" t="n">
+        <v>784.96</v>
+      </c>
       <c r="D26" s="69" t="n">
         <v>30</v>
       </c>
       <c r="E26" s="69">
-        <f>IF(B26="","",B26*$B$4)</f>
+        <f>IF(B26="","",B26*IF($J26="",$B$4,$J26))</f>
         <v/>
       </c>
       <c r="F26" s="69">
@@ -4305,6 +4426,9 @@
         <f>IF(B26=0,"",H26/B26)</f>
         <v/>
       </c>
+      <c r="J26" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
@@ -4313,14 +4437,16 @@
         </is>
       </c>
       <c r="B27" s="67" t="n">
-        <v>1366</v>
-      </c>
-      <c r="C27" s="121" t="n"/>
+        <v>1486</v>
+      </c>
+      <c r="C27" s="121" t="n">
+        <v>739.37</v>
+      </c>
       <c r="D27" s="67" t="n">
         <v>30</v>
       </c>
       <c r="E27" s="67">
-        <f>IF(B27="","",B27*$B$4)</f>
+        <f>IF(B27="","",B27*IF($J27="",$B$4,$J27))</f>
         <v/>
       </c>
       <c r="F27" s="67">
@@ -4339,20 +4465,27 @@
         <f>IF(B27=0,"",H27/B27)</f>
         <v/>
       </c>
+      <c r="J27" s="239" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Baby</t>
-        </is>
-      </c>
-      <c r="B28" s="77" t="n"/>
-      <c r="C28" s="121" t="n"/>
+          <t>Purificador Everest Star Preto</t>
+        </is>
+      </c>
+      <c r="B28" s="77" t="n">
+        <v>1486</v>
+      </c>
+      <c r="C28" s="121" t="n">
+        <v>784.96</v>
+      </c>
       <c r="D28" s="69" t="n">
         <v>30</v>
       </c>
       <c r="E28" s="69">
-        <f>IF(B28="","",B28*$B$4)</f>
+        <f>IF(B28="","",B28*IF($J28="",$B$4,$J28))</f>
         <v/>
       </c>
       <c r="F28" s="69">
@@ -4371,28 +4504,156 @@
         <f>IF(B28=0,"",H28/B28)</f>
         <v/>
       </c>
+      <c r="J28" s="240" t="n">
+        <v>0.1399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="66" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Branco</t>
+        </is>
+      </c>
+      <c r="B29" s="77" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C29" s="121" t="n">
+        <v>767.95</v>
+      </c>
+      <c r="D29" s="69" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" s="69">
+        <f>IF(B29="","",B29*IF($J29="",$B$4,$J29))</f>
+        <v/>
+      </c>
+      <c r="F29" s="69">
+        <f>IF(B29="","",B29*$D$4)</f>
+        <v/>
+      </c>
+      <c r="G29" s="69">
+        <f>IF(B29="","",SUM(C29:F29))</f>
+        <v/>
+      </c>
+      <c r="H29" s="69">
+        <f>IF(B29="","",B29-G29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="76">
+        <f>IF(B29=0,"",H29/B29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="220" t="inlineStr">
-        <is>
-          <t>Preços = média praticada em Ago/2026 (purificadores: média de Jan–Jul). Comissões: R$ 10 por troca de refil e R$ 30 por instalação, conforme combinado com Wiliam.</t>
-        </is>
+      <c r="A30" s="66" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Cinza/Grafite</t>
+        </is>
+      </c>
+      <c r="B30" s="77" t="n">
+        <v>1689</v>
+      </c>
+      <c r="C30" s="121" t="n">
+        <v>819.5700000000001</v>
+      </c>
+      <c r="D30" s="69" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" s="69">
+        <f>IF(B30="","",B30*IF($J30="",$B$4,$J30))</f>
+        <v/>
+      </c>
+      <c r="F30" s="69">
+        <f>IF(B30="","",B30*$D$4)</f>
+        <v/>
+      </c>
+      <c r="G30" s="69">
+        <f>IF(B30="","",SUM(C30:F30))</f>
+        <v/>
+      </c>
+      <c r="H30" s="69">
+        <f>IF(B30="","",B30-G30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="76">
+        <f>IF(B30=0,"",H30/B30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="240" t="n">
+        <v>0.1399</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="220" t="inlineStr">
-        <is>
-          <t>Enquanto o Custo de Aquisição estiver vazio, a Margem mostra o preço cheio — só fica correta depois de preencher o custo de compra de cada item.</t>
+      <c r="A31" s="66" t="inlineStr">
+        <is>
+          <t>Purificador Everest Baby (todas as cores)</t>
+        </is>
+      </c>
+      <c r="B31" s="77" t="n">
+        <v>420</v>
+      </c>
+      <c r="C31" s="121" t="n">
+        <v>150.13</v>
+      </c>
+      <c r="D31" s="69" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="69">
+        <f>IF(B31="","",B31*IF($J31="",$B$4,$J31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="69">
+        <f>IF(B31="","",B31*$D$4)</f>
+        <v/>
+      </c>
+      <c r="G31" s="69">
+        <f>IF(B31="","",SUM(C31:F31))</f>
+        <v/>
+      </c>
+      <c r="H31" s="69">
+        <f>IF(B31="","",B31-G31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="76">
+        <f>IF(B31=0,"",H31/B31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="240" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="220" t="inlineStr">
+        <is>
+          <t>PREÇOS: purificadores conforme o Catálogo de Purificadores (pasta Catálogos) — valor total do parcelamento em 10x, que é como as vendas entram na planilha. À vista sai mais barato: Residencial branco R$ 1.329, demais cores R$ 1.376; Plus branco R$ 1.429, demais R$ 1.476; Foz branco R$ 1.489, cinza/grafite R$ 1.589; Baby R$ 379.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="220" t="inlineStr">
+        <is>
+          <t>TAXAS REAIS DA MAQUININHA (medidas em Ago-Set/2026): débito 1,45% · crédito à vista 3,51% · crédito 2-3x 6,99% · 4x 7,99% · 5x 9,99% · 10x 13,99%. Dinheiro e Pix não têm taxa. A coluna "Taxa aplicada" (J) manda: em branco usa os 7% de B4 (itens de balcão); preenchida, vale o que estiver lá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CUSTOS: Refil Everest e Pré-Filtro = Eversoft (26/08). Pro Life, Carbon Tech, E3, Plissado = Filtros Planeta Água. C+3 = Culligan (22/04). Registro = Everest (19/05). Purificadores = Everest, última nota de cada modelo. Mangueira = R$ 1,72/m (rolo 50 m por R$ 86,01). Termostato: sem compra em 2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" location="'Início'!A1" display="← Início"/>
@@ -34000,7 +34261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U77"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34148,11 +34409,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H75,K5,G5:G75)</f>
+        <f>SUMIF(H5:H79,K5,G5:G79)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D76-F76-T5</f>
+        <f>D80-F80-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34160,11 +34421,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D77</f>
+        <f>D81</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E75,"Aguardando Pagamento",D5:D75)</f>
+        <f>SUMIF(E5:E79,"Aguardando Pagamento",D5:D79)</f>
         <v/>
       </c>
     </row>
@@ -34204,7 +34465,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H75,K6,G5:G75)</f>
+        <f>SUMIF(H5:H79,K6,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34244,7 +34505,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H75,K7,G5:G75)</f>
+        <f>SUMIF(H5:H79,K7,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34284,7 +34545,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H75,K8,G5:G75)</f>
+        <f>SUMIF(H5:H79,K8,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34324,7 +34585,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H75,K9,G5:G75)</f>
+        <f>SUMIF(H5:H79,K9,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34364,7 +34625,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H75,K10,G5:G75)</f>
+        <f>SUMIF(H5:H79,K10,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34404,7 +34665,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H75,K11,G5:G75)</f>
+        <f>SUMIF(H5:H79,K11,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34444,7 +34705,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H75,K12,G5:G75)</f>
+        <f>SUMIF(H5:H79,K12,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34480,7 +34741,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H75,K13,G5:G75)</f>
+        <f>SUMIF(H5:H79,K13,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34520,13 +34781,13 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H75,K14,G5:G75)</f>
+        <f>SUMIF(H5:H79,K14,G5:G79)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="89" t="n">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B15" s="90" t="inlineStr">
         <is>
@@ -34543,20 +34804,24 @@
       </c>
       <c r="E15" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F15" s="91" t="n"/>
       <c r="G15" s="91" t="n"/>
       <c r="H15" s="90" t="n"/>
-      <c r="I15" s="90" t="n"/>
+      <c r="I15" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 01/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
+        </is>
+      </c>
       <c r="K15" s="90" t="inlineStr">
         <is>
           <t>Estornos de Vendas (Cancelamentos)</t>
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H75,K15,G5:G75)</f>
+        <f>SUMIF(H5:H79,K15,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34592,7 +34857,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H75,K16,G5:G75)</f>
+        <f>SUMIF(H5:H79,K16,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34632,7 +34897,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H75,K17,G5:G75)</f>
+        <f>SUMIF(H5:H79,K17,G5:G79)</f>
         <v/>
       </c>
     </row>
@@ -34903,7 +35168,7 @@
     </row>
     <row r="27">
       <c r="A27" s="89" t="n">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="B27" s="90" t="inlineStr">
         <is>
@@ -34920,13 +35185,17 @@
       </c>
       <c r="E27" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F27" s="91" t="n"/>
       <c r="G27" s="91" t="n"/>
       <c r="H27" s="90" t="n"/>
-      <c r="I27" s="90" t="n"/>
+      <c r="I27" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 02/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="93" t="n">
@@ -36269,46 +36538,146 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="102" t="n"/>
-      <c r="B76" s="102" t="inlineStr">
+      <c r="A76" s="93" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B76" s="94" t="inlineStr">
+        <is>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C76" s="94" t="n"/>
+      <c r="D76" s="95" t="n">
+        <v>700</v>
+      </c>
+      <c r="E76" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F76" s="95" t="n"/>
+      <c r="G76" s="95" t="n"/>
+      <c r="H76" s="94" t="n"/>
+      <c r="I76" s="94" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="89" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B77" s="90" t="inlineStr">
+        <is>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C77" s="90" t="n"/>
+      <c r="D77" s="91" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="90" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F77" s="91" t="n"/>
+      <c r="G77" s="91" t="n"/>
+      <c r="H77" s="90" t="n"/>
+      <c r="I77" s="90" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="93" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B78" s="94" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C78" s="94" t="inlineStr">
+        <is>
+          <t>Mangueira (2m)</t>
+        </is>
+      </c>
+      <c r="D78" s="95" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F78" s="95" t="n"/>
+      <c r="G78" s="95" t="n"/>
+      <c r="H78" s="94" t="n"/>
+      <c r="I78" s="94" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="89" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B79" s="90" t="inlineStr">
+        <is>
+          <t>Compra na Shopee - Ferramentas, Velas e Tinta</t>
+        </is>
+      </c>
+      <c r="C79" s="90" t="n"/>
+      <c r="D79" s="91" t="n"/>
+      <c r="E79" s="90" t="n"/>
+      <c r="F79" s="91" t="n"/>
+      <c r="G79" s="91" t="n">
+        <v>139.59</v>
+      </c>
+      <c r="H79" s="90" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I79" s="90" t="inlineStr">
+        <is>
+          <t>Pix de 10/09/2026 11:56 para Shpp Brasil Instituição de Pagamento (CNPJ 38.372.267/0001-82) — ferramentas e tinta para a loja + velas de carvão ativado para revenda. ID E07237373202609101455 8N7SUEN9VKQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="102" t="n"/>
+      <c r="B80" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C76" s="102" t="n"/>
-      <c r="D76" s="103">
-        <f>SUM(D5:D75)</f>
-        <v/>
-      </c>
-      <c r="E76" s="102" t="n"/>
-      <c r="F76" s="103">
-        <f>SUM(F5:F75)</f>
-        <v/>
-      </c>
-      <c r="G76" s="103">
-        <f>SUM(G5:G75)</f>
-        <v/>
-      </c>
-      <c r="H76" s="102" t="n"/>
-      <c r="I76" s="102" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="104" t="n"/>
-      <c r="B77" s="104" t="inlineStr">
+      <c r="C80" s="102" t="n"/>
+      <c r="D80" s="103">
+        <f>SUM(D5:D79)</f>
+        <v/>
+      </c>
+      <c r="E80" s="102" t="n"/>
+      <c r="F80" s="103">
+        <f>SUM(F5:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="103">
+        <f>SUM(G5:G79)</f>
+        <v/>
+      </c>
+      <c r="H80" s="102" t="n"/>
+      <c r="I80" s="102" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="104" t="n"/>
+      <c r="B81" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C77" s="104" t="n"/>
-      <c r="D77" s="105">
-        <f>(D76-F76-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E77" s="104" t="n"/>
-      <c r="F77" s="105" t="n"/>
-      <c r="G77" s="105" t="n"/>
-      <c r="H77" s="104" t="n"/>
-      <c r="I77" s="104" t="n"/>
+      <c r="C81" s="104" t="n"/>
+      <c r="D81" s="105">
+        <f>(D80-F80-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E81" s="104" t="n"/>
+      <c r="F81" s="105" t="n"/>
+      <c r="G81" s="105" t="n"/>
+      <c r="H81" s="104" t="n"/>
+      <c r="I81" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -36325,10 +36694,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51,7 +51,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="78">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -512,8 +512,21 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FFB7791F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FFB7791F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -632,6 +645,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6B46C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -842,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1376,6 +1394,26 @@
     </xf>
     <xf numFmtId="10" fontId="31" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="31" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="23" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="76" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="76" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="23" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="77" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -40961,7 +40999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -41012,7 +41050,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D36</f>
+        <f>D68</f>
         <v/>
       </c>
       <c r="C5" s="203">
@@ -41517,23 +41555,23 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="inlineStr">
+      <c r="A25" s="90" t="inlineStr">
         <is>
           <t>Patrus Transportes Ltda</t>
         </is>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="90" t="inlineStr">
         <is>
           <t>Frete — fatura 26-08-913041 (CT-e 2117850, remetente Eversoft, NF 75472)</t>
         </is>
       </c>
-      <c r="C25" s="93" t="n">
+      <c r="C25" s="89" t="n">
         <v>46281</v>
       </c>
-      <c r="D25" s="95" t="n">
+      <c r="D25" s="91" t="n">
         <v>292.68</v>
       </c>
-      <c r="E25" s="125" t="inlineStr">
+      <c r="E25" s="124" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -41542,30 +41580,30 @@
         <f>IF(OR($E25="Pago",$C25=""),"",MAX(0,TODAY()-$C25))</f>
         <v/>
       </c>
-      <c r="G25" s="94" t="inlineStr">
+      <c r="G25" s="90" t="inlineStr">
         <is>
           <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840262224-4, cedente 6348-/017737-7. Após o vencimento: R$ 0,44 por dia de atraso; protesto a partir do 7º dia.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="90" t="inlineStr">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>FGTS Digital (GFD)</t>
         </is>
       </c>
-      <c r="B26" s="90" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>FGTS mensal — competência 08/2026</t>
         </is>
       </c>
-      <c r="C26" s="89" t="n">
+      <c r="C26" s="93" t="n">
         <v>46283</v>
       </c>
-      <c r="D26" s="91" t="n">
+      <c r="D26" s="95" t="n">
         <v>136</v>
       </c>
-      <c r="E26" s="124" t="inlineStr">
+      <c r="E26" s="125" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -41574,30 +41612,30 @@
         <f>IF(OR($E26="Pago",$C26=""),"",MAX(0,TODAY()-$C26))</f>
         <v/>
       </c>
-      <c r="G26" s="90" t="inlineStr">
+      <c r="G26" s="94" t="inlineStr">
         <is>
           <t>Categoria quando pagar: Impostos e Taxas.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="94" t="inlineStr">
+      <c r="A27" s="90" t="inlineStr">
         <is>
           <t>Receita Federal</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="90" t="inlineStr">
         <is>
           <t>DARF / INSS — período de apuração agosto/2026</t>
         </is>
       </c>
-      <c r="C27" s="93" t="n">
+      <c r="C27" s="89" t="n">
         <v>46283</v>
       </c>
-      <c r="D27" s="95" t="n">
+      <c r="D27" s="91" t="n">
         <v>306.99</v>
       </c>
-      <c r="E27" s="125" t="inlineStr">
+      <c r="E27" s="124" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -41606,1195 +41644,1159 @@
         <f>IF(OR($E27="Pago",$C27=""),"",MAX(0,TODAY()-$C27))</f>
         <v/>
       </c>
-      <c r="G27" s="94" t="inlineStr">
+      <c r="G27" s="90" t="inlineStr">
         <is>
           <t>Categoria quando pagar: Impostos e Taxas.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="n"/>
-      <c r="B28" s="94" t="n"/>
-      <c r="C28" s="93" t="n"/>
-      <c r="D28" s="95" t="n"/>
-      <c r="E28" s="125" t="n"/>
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B28" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 74454 (emissão 17/07/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C28" s="93" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D28" s="95" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="E28" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F28" s="125">
         <f>IF(OR($E28="Pago",$C28=""),"",MAX(0,TODAY()-$C28))</f>
         <v/>
       </c>
-      <c r="G28" s="94" t="n"/>
+      <c r="G28" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638767-8. Linha digitável 34191.12283 63876.780303 55679.010003 5 15700000098083. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="90" t="n"/>
-      <c r="B29" s="90" t="n"/>
-      <c r="C29" s="89" t="n"/>
-      <c r="D29" s="91" t="n"/>
-      <c r="E29" s="124" t="n"/>
+      <c r="A29" s="90" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B29" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 75472 (emissão 26/08/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C29" s="89" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D29" s="91" t="n">
+        <v>940.0599999999999</v>
+      </c>
+      <c r="E29" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F29" s="124">
         <f>IF(OR($E29="Pago",$C29=""),"",MAX(0,TODAY()-$C29))</f>
         <v/>
       </c>
-      <c r="G29" s="90" t="n"/>
+      <c r="G29" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604587-0. Linha digitável 34191.12333 60458.700303 55679.010003 3 15800000094006. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="n"/>
-      <c r="B30" s="94" t="n"/>
-      <c r="C30" s="93" t="n"/>
-      <c r="D30" s="95" t="n"/>
-      <c r="E30" s="125" t="n"/>
+      <c r="A30" s="94" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B30" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 72869 (emissão 07/05/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C30" s="93" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D30" s="95" t="n">
+        <v>980.8099999999999</v>
+      </c>
+      <c r="E30" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F30" s="125">
         <f>IF(OR($E30="Pago",$C30=""),"",MAX(0,TODAY()-$C30))</f>
         <v/>
       </c>
-      <c r="G30" s="94" t="n"/>
+      <c r="G30" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="90" t="n"/>
-      <c r="B31" s="90" t="n"/>
-      <c r="C31" s="89" t="n"/>
-      <c r="D31" s="91" t="n"/>
-      <c r="E31" s="124" t="n"/>
+      <c r="A31" s="90" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B31" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 73636 (emissão 10/06/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C31" s="89" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D31" s="91" t="n">
+        <v>878.92</v>
+      </c>
+      <c r="E31" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F31" s="124">
         <f>IF(OR($E31="Pago",$C31=""),"",MAX(0,TODAY()-$C31))</f>
         <v/>
       </c>
-      <c r="G31" s="90" t="n"/>
+      <c r="G31" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="n"/>
-      <c r="B32" s="94" t="n"/>
-      <c r="C32" s="93" t="n"/>
-      <c r="D32" s="95" t="n"/>
-      <c r="E32" s="125" t="n"/>
+      <c r="A32" s="94" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B32" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 74454 (emissão 17/07/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C32" s="93" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D32" s="95" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="E32" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F32" s="125">
         <f>IF(OR($E32="Pago",$C32=""),"",MAX(0,TODAY()-$C32))</f>
         <v/>
       </c>
-      <c r="G32" s="94" t="n"/>
+      <c r="G32" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="90" t="n"/>
-      <c r="B33" s="90" t="n"/>
-      <c r="C33" s="89" t="n"/>
-      <c r="D33" s="91" t="n"/>
-      <c r="E33" s="124" t="n"/>
+      <c r="A33" s="90" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B33" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 75472 (emissão 26/08/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C33" s="89" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D33" s="91" t="n">
+        <v>940.0599999999999</v>
+      </c>
+      <c r="E33" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F33" s="124">
         <f>IF(OR($E33="Pago",$C33=""),"",MAX(0,TODAY()-$C33))</f>
         <v/>
       </c>
-      <c r="G33" s="90" t="n"/>
+      <c r="G33" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604663-9. Linha digitável 34191.12333 60466.390303 55679.010003 1 16100000094006. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="n"/>
-      <c r="B34" s="94" t="n"/>
-      <c r="C34" s="93" t="n"/>
-      <c r="D34" s="95" t="n"/>
-      <c r="E34" s="125" t="n"/>
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B34" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 73636 (emissão 10/06/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C34" s="93" t="n">
+        <v>46333</v>
+      </c>
+      <c r="D34" s="95" t="n">
+        <v>878.9299999999999</v>
+      </c>
+      <c r="E34" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F34" s="125">
         <f>IF(OR($E34="Pago",$C34=""),"",MAX(0,TODAY()-$C34))</f>
         <v/>
       </c>
-      <c r="G34" s="94" t="n"/>
+      <c r="G34" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142177-8. Linha digitável 34191.12242 14217.780304 55679.010003 4 16230000087893. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="90" t="n"/>
-      <c r="B35" s="90" t="n"/>
-      <c r="C35" s="89" t="n"/>
-      <c r="D35" s="91" t="n"/>
-      <c r="E35" s="124" t="n"/>
+      <c r="A35" s="90" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B35" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 381554 (emissão 17/07/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C35" s="89" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D35" s="91" t="n">
+        <v>892.3</v>
+      </c>
+      <c r="E35" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F35" s="124">
         <f>IF(OR($E35="Pago",$C35=""),"",MAX(0,TODAY()-$C35))</f>
         <v/>
       </c>
-      <c r="G35" s="90" t="n"/>
+      <c r="G35" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28638136-6. Linha digitável 34191.12283 63813.660303 52238.850003 1 15700000089230. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="98" t="inlineStr">
-        <is>
-          <t>TOTAL EM ABERTO A PAGAR</t>
-        </is>
-      </c>
-      <c r="B36" s="98" t="n"/>
-      <c r="C36" s="126" t="n"/>
-      <c r="D36" s="127">
-        <f>SUMIF(E11:E35,"Pendente",D11:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="128" t="n"/>
-      <c r="F36" s="128" t="n"/>
-      <c r="G36" s="98" t="n"/>
+      <c r="A36" s="94" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B36" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377737 (emissão 19/05/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C36" s="93" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D36" s="95" t="n">
+        <v>139.31</v>
+      </c>
+      <c r="E36" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F36" s="125">
+        <f>IF(OR($E36="Pago",$C36=""),"",MAX(0,TODAY()-$C36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336084-8. Linha digitável 34191.12218 33608.480308 52238.850003 9 15710000013931. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="90" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B37" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377738 (emissão 19/05/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C37" s="89" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D37" s="91" t="n">
+        <v>865.5</v>
+      </c>
+      <c r="E37" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F37" s="124">
+        <f>IF(OR($E37="Pago",$C37=""),"",MAX(0,TODAY()-$C37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336022-8. Linha digitável 34191.12218 33602.280308 52238.850003 5 15710000086550. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="94" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B38" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377739 (emissão 19/05/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C38" s="93" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D38" s="95" t="n">
+        <v>856.35</v>
+      </c>
+      <c r="E38" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F38" s="125">
+        <f>IF(OR($E38="Pago",$C38=""),"",MAX(0,TODAY()-$C38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336008-7. Linha digitável 34191.12218 33600.870308 52238.850003 9 15710000085635. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="21.95" customHeight="1" s="158">
-      <c r="A39" s="202" t="inlineStr">
+      <c r="A39" s="90" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B39" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 379826 (emissão 22/06/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C39" s="89" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D39" s="91" t="n">
+        <v>874.6799999999999</v>
+      </c>
+      <c r="E39" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F39" s="124">
+        <f>IF(OR($E39="Pago",$C39=""),"",MAX(0,TODAY()-$C39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528668-7. Linha digitável 34191.12259 52866.870307 52238.850003 7 15750000087468. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="94" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B40" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 381554 (emissão 17/07/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C40" s="93" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D40" s="95" t="n">
+        <v>892.3</v>
+      </c>
+      <c r="E40" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F40" s="125">
+        <f>IF(OR($E40="Pago",$C40=""),"",MAX(0,TODAY()-$C40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26.1" customHeight="1" s="158">
+      <c r="A41" s="90" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B41" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377737 (emissão 19/05/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C41" s="89" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D41" s="91" t="n">
+        <v>139.32</v>
+      </c>
+      <c r="E41" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F41" s="124">
+        <f>IF(OR($E41="Pago",$C41=""),"",MAX(0,TODAY()-$C41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="94" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377738 (emissão 19/05/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C42" s="93" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D42" s="95" t="n">
+        <v>865.52</v>
+      </c>
+      <c r="E42" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F42" s="125">
+        <f>IF(OR($E42="Pago",$C42=""),"",MAX(0,TODAY()-$C42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="90" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B43" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 377739 (emissão 19/05/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C43" s="89" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D43" s="91" t="n">
+        <v>856.34</v>
+      </c>
+      <c r="E43" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F43" s="124">
+        <f>IF(OR($E43="Pago",$C43=""),"",MAX(0,TODAY()-$C43))</f>
+        <v/>
+      </c>
+      <c r="G43" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="94" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B44" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 379826 (emissão 22/06/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C44" s="93" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D44" s="95" t="n">
+        <v>874.6799999999999</v>
+      </c>
+      <c r="E44" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F44" s="125">
+        <f>IF(OR($E44="Pago",$C44=""),"",MAX(0,TODAY()-$C44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="241" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B45" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 74454 (emissão 17/07/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C45" s="242" t="n">
+        <v>46340</v>
+      </c>
+      <c r="D45" s="243" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="E45" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F45" s="245">
+        <f>IF(OR($E45="Pago",$C45=""),"",MAX(0,TODAY()-$C45))</f>
+        <v/>
+      </c>
+      <c r="G45" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="241" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B46" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 381554 (emissão 17/07/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C46" s="242" t="n">
+        <v>46340</v>
+      </c>
+      <c r="D46" s="243" t="n">
+        <v>892.3</v>
+      </c>
+      <c r="E46" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F46" s="245">
+        <f>IF(OR($E46="Pago",$C46=""),"",MAX(0,TODAY()-$C46))</f>
+        <v/>
+      </c>
+      <c r="G46" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="241" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B47" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 379826 (emissão 22/06/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C47" s="242" t="n">
+        <v>46345</v>
+      </c>
+      <c r="D47" s="243" t="n">
+        <v>874.6799999999999</v>
+      </c>
+      <c r="E47" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F47" s="245">
+        <f>IF(OR($E47="Pago",$C47=""),"",MAX(0,TODAY()-$C47))</f>
+        <v/>
+      </c>
+      <c r="G47" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="241" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B48" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 75472 (emissão 26/08/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C48" s="242" t="n">
+        <v>46350</v>
+      </c>
+      <c r="D48" s="243" t="n">
+        <v>940.0599999999999</v>
+      </c>
+      <c r="E48" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F48" s="245">
+        <f>IF(OR($E48="Pago",$C48=""),"",MAX(0,TODAY()-$C48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="241" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B49" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 381554 (emissão 17/07/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C49" s="242" t="n">
+        <v>46370</v>
+      </c>
+      <c r="D49" s="243" t="n">
+        <v>892.29</v>
+      </c>
+      <c r="E49" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F49" s="245">
+        <f>IF(OR($E49="Pago",$C49=""),"",MAX(0,TODAY()-$C49))</f>
+        <v/>
+      </c>
+      <c r="G49" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="241" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B50" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 74454 (emissão 17/07/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C50" s="242" t="n">
+        <v>46370</v>
+      </c>
+      <c r="D50" s="243" t="n">
+        <v>980.8099999999999</v>
+      </c>
+      <c r="E50" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F50" s="245">
+        <f>IF(OR($E50="Pago",$C50=""),"",MAX(0,TODAY()-$C50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="241" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B51" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 75472 (emissão 26/08/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C51" s="242" t="n">
+        <v>46380</v>
+      </c>
+      <c r="D51" s="243" t="n">
+        <v>940.0599999999999</v>
+      </c>
+      <c r="E51" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F51" s="245">
+        <f>IF(OR($E51="Pago",$C51=""),"",MAX(0,TODAY()-$C51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="241" t="inlineStr">
+        <is>
+          <t>Eversoft Ind e Com de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="B52" s="241" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 75472 (emissão 26/08/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C52" s="242" t="n">
+        <v>46410</v>
+      </c>
+      <c r="D52" s="243" t="n">
+        <v>940.08</v>
+      </c>
+      <c r="E52" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F52" s="245">
+        <f>IF(OR($E52="Pago",$C52=""),"",MAX(0,TODAY()-$C52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="90" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B53" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 131997/4 (emissão 08/07/2026) · parcela 4/4 (última)</t>
+        </is>
+      </c>
+      <c r="C53" s="89" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D53" s="91" t="n">
+        <v>1385.85</v>
+      </c>
+      <c r="E53" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F53" s="124">
+        <f>IF(OR($E53="Pago",$C53=""),"",MAX(0,TODAY()-$C53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00255359-0. Linha digitável 34191.09008 25535.901430 81531.550002 9 15710000138585. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="94" t="inlineStr">
+        <is>
+          <t>Instituto Euvaldo Lodi — Núcleo Regional da Bahia</t>
+        </is>
+      </c>
+      <c r="B54" s="94" t="inlineStr">
+        <is>
+          <t>Contribuição do contrato de estágio — doc. A 000007329</t>
+        </is>
+      </c>
+      <c r="C54" s="93" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D54" s="95" t="n">
+        <v>75</v>
+      </c>
+      <c r="E54" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F54" s="125">
+        <f>IF(OR($E54="Pago",$C54=""),"",MAX(0,TODAY()-$C54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Salários, Comissões e Encargos. Boleto Banco do Brasil 001-0, nosso número 32190990000160501. Linha digitável 00190.00009 03219.099003 00160.501177 1 15700000007500. Após o vencimento: juros de 0,5% ao mês; não receber após 35 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="90" t="inlineStr">
+        <is>
+          <t>Proxxima Telecomunicacoes S.A.</t>
+        </is>
+      </c>
+      <c r="B55" s="90" t="inlineStr">
+        <is>
+          <t>Internet da loja — plano Turbinados 700 MB, contrato 578646</t>
+        </is>
+      </c>
+      <c r="C55" s="89" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D55" s="91" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="E55" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F55" s="124">
+        <f>IF(OR($E55="Pago",$C55=""),"",MAX(0,TODAY()-$C55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Água, Energia e Internet. Fatura FAT26081721473042, boleto Bradesco 237. Linha digitável 23790.49303 90000.413329 63025.103001 5 15700000006999. A fatura sai em nome do sócio, mas o serviço é da loja. Após o vencimento: multa de 2% + mora de 1,2% ao mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="94" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B56" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133138/2 (emissão 12/08/2026) · parcela 2/4</t>
+        </is>
+      </c>
+      <c r="C56" s="93" t="n">
+        <v>46288</v>
+      </c>
+      <c r="D56" s="95" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="E56" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F56" s="125">
+        <f>IF(OR($E56="Pago",$C56=""),"",MAX(0,TODAY()-$C56))</f>
+        <v/>
+      </c>
+      <c r="G56" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257850-6. Linha digitável 34191.09008 25785.061430 81531.550002 4 15780000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="90" t="inlineStr">
+        <is>
+          <t>Empresa Baiana de Aguas e Saneamento SA (Embasa)</t>
+        </is>
+      </c>
+      <c r="B57" s="90" t="inlineStr">
+        <is>
+          <t>Conta de água — despesa pessoal do dono (não é da loja) — ref. 10/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="89" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D57" s="91" t="n">
+        <v>91</v>
+      </c>
+      <c r="E57" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F57" s="124">
+        <f>IF(OR($E57="Pago",$C57=""),"",MAX(0,TODAY()-$C57))</f>
+        <v/>
+      </c>
+      <c r="G57" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Pro Labore Edilânia. Fatura em nome pessoal do sócio, matrícula 0531718-70. Pagável via Pix no QR Code da conta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="94" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B58" s="94" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133138/3 (emissão 12/08/2026) · parcela 3/4</t>
+        </is>
+      </c>
+      <c r="C58" s="93" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D58" s="95" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="E58" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F58" s="125">
+        <f>IF(OR($E58="Pago",$C58=""),"",MAX(0,TODAY()-$C58))</f>
+        <v/>
+      </c>
+      <c r="G58" s="94" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="90" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B59" s="90" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133138/4 (emissão 12/08/2026) · parcela 4/4 (última)</t>
+        </is>
+      </c>
+      <c r="C59" s="89" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D59" s="91" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="E59" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F59" s="124">
+        <f>IF(OR($E59="Pago",$C59=""),"",MAX(0,TODAY()-$C59))</f>
+        <v/>
+      </c>
+      <c r="G59" s="90" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="98" t="inlineStr">
+        <is>
+          <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
+        </is>
+      </c>
+      <c r="B66" s="98" t="n"/>
+      <c r="C66" s="126" t="n"/>
+      <c r="D66" s="127">
+        <f>SUMIF(E11:E65,"Pendente",D11:D65)</f>
+        <v/>
+      </c>
+      <c r="E66" s="128" t="n"/>
+      <c r="F66" s="128" t="n"/>
+      <c r="G66" s="98" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="246" t="inlineStr">
+        <is>
+          <t>PREVISTO — parcelas das notas, boleto ainda não emitido</t>
+        </is>
+      </c>
+      <c r="B67" s="246" t="n"/>
+      <c r="C67" s="247" t="n"/>
+      <c r="D67" s="248">
+        <f>SUMIF(E11:E65,"Previsto",D11:D65)</f>
+        <v/>
+      </c>
+      <c r="E67" s="244" t="n"/>
+      <c r="F67" s="244" t="n"/>
+      <c r="G67" s="246" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="98" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
+        </is>
+      </c>
+      <c r="B68" s="98" t="n"/>
+      <c r="C68" s="126" t="n"/>
+      <c r="D68" s="127">
+        <f>D66+D67</f>
+        <v/>
+      </c>
+      <c r="E68" s="128" t="n"/>
+      <c r="F68" s="128" t="n"/>
+      <c r="G68" s="98" t="n"/>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="202" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="194" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26.1" customHeight="1" s="158">
-      <c r="A41" s="123" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="123" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B41" s="123" t="inlineStr">
+      <c r="B73" s="123" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C41" s="123" t="inlineStr">
+      <c r="C73" s="123" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D41" s="123" t="inlineStr">
+      <c r="D73" s="123" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E41" s="123" t="inlineStr">
+      <c r="E73" s="123" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F41" s="123" t="inlineStr">
+      <c r="F73" s="123" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G41" s="123" t="inlineStr">
+      <c r="G73" s="123" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="90" t="inlineStr">
-        <is>
-          <t>Centro de Especialidades Odontomédicas</t>
-        </is>
-      </c>
-      <c r="B42" s="90" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C42" s="89" t="n">
-        <v>46239</v>
-      </c>
-      <c r="D42" s="91" t="n">
-        <v>140</v>
-      </c>
-      <c r="E42" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F42" s="124">
-        <f>IF(OR($E42="Recebido",$C42=""),"",MAX(0,TODAY()-$C42))</f>
-        <v/>
-      </c>
-      <c r="G42" s="90" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>Supermercado Brasil</t>
-        </is>
-      </c>
-      <c r="B43" s="94" t="inlineStr">
-        <is>
-          <t>2x Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C43" s="93" t="n">
-        <v>46239</v>
-      </c>
-      <c r="D43" s="95" t="n">
-        <v>280</v>
-      </c>
-      <c r="E43" s="125" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F43" s="125">
-        <f>IF(OR($E43="Recebido",$C43=""),"",MAX(0,TODAY()-$C43))</f>
-        <v/>
-      </c>
-      <c r="G43" s="94" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="90" t="inlineStr">
-        <is>
-          <t>Tropical Motos LTDA</t>
-        </is>
-      </c>
-      <c r="B44" s="90" t="inlineStr">
-        <is>
-          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
-        </is>
-      </c>
-      <c r="C44" s="89" t="n">
-        <v>46245</v>
-      </c>
-      <c r="D44" s="91" t="n">
-        <v>820</v>
-      </c>
-      <c r="E44" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F44" s="124">
-        <f>IF(OR($E44="Recebido",$C44=""),"",MAX(0,TODAY()-$C44))</f>
-        <v/>
-      </c>
-      <c r="G44" s="90" t="inlineStr">
-        <is>
-          <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="94" t="inlineStr">
-        <is>
-          <t>Free Way</t>
-        </is>
-      </c>
-      <c r="B45" s="94" t="inlineStr">
-        <is>
-          <t>5x Refil Everest</t>
-        </is>
-      </c>
-      <c r="C45" s="93" t="n">
-        <v>46251</v>
-      </c>
-      <c r="D45" s="95" t="n">
-        <v>700</v>
-      </c>
-      <c r="E45" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F45" s="125">
-        <f>IF(OR($E45="Recebido",$C45=""),"",MAX(0,TODAY()-$C45))</f>
-        <v/>
-      </c>
-      <c r="G45" s="94" t="inlineStr">
-        <is>
-          <t>Recebido via TED em 02/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="90" t="inlineStr">
-        <is>
-          <t>Neli Sena Rego</t>
-        </is>
-      </c>
-      <c r="B46" s="90" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C46" s="89" t="n">
-        <v>46254</v>
-      </c>
-      <c r="D46" s="91" t="n">
-        <v>140</v>
-      </c>
-      <c r="E46" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F46" s="124">
-        <f>IF(OR($E46="Recebido",$C46=""),"",MAX(0,TODAY()-$C46))</f>
-        <v/>
-      </c>
-      <c r="G46" s="90" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="94" t="inlineStr">
-        <is>
-          <t>Neli Sena Rego</t>
-        </is>
-      </c>
-      <c r="B47" s="94" t="inlineStr">
-        <is>
-          <t>Conexão + Mangueira</t>
-        </is>
-      </c>
-      <c r="C47" s="93" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D47" s="95" t="n">
-        <v>40</v>
-      </c>
-      <c r="E47" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F47" s="125">
-        <f>IF(OR($E47="Recebido",$C47=""),"",MAX(0,TODAY()-$C47))</f>
-        <v/>
-      </c>
-      <c r="G47" s="94" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="90" t="inlineStr">
-        <is>
-          <t>Lapec</t>
-        </is>
-      </c>
-      <c r="B48" s="90" t="inlineStr">
-        <is>
-          <t>4x Refil Everest</t>
-        </is>
-      </c>
-      <c r="C48" s="89" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D48" s="91" t="n">
-        <v>480</v>
-      </c>
-      <c r="E48" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F48" s="124">
-        <f>IF(OR($E48="Recebido",$C48=""),"",MAX(0,TODAY()-$C48))</f>
-        <v/>
-      </c>
-      <c r="G48" s="90" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="94" t="inlineStr">
-        <is>
-          <t>Cícero Lima</t>
-        </is>
-      </c>
-      <c r="B49" s="94" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C49" s="93" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D49" s="95" t="n">
-        <v>140</v>
-      </c>
-      <c r="E49" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F49" s="125">
-        <f>IF(OR($E49="Recebido",$C49=""),"",MAX(0,TODAY()-$C49))</f>
-        <v/>
-      </c>
-      <c r="G49" s="94" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 27/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="90" t="inlineStr">
-        <is>
-          <t>Promotoria Regional de Jacobina</t>
-        </is>
-      </c>
-      <c r="B50" s="90" t="inlineStr">
-        <is>
-          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
-        </is>
-      </c>
-      <c r="C50" s="89" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D50" s="91" t="n">
-        <v>470</v>
-      </c>
-      <c r="E50" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F50" s="124">
-        <f>IF(OR($E50="Recebido",$C50=""),"",MAX(0,TODAY()-$C50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="90" t="inlineStr">
-        <is>
-          <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="94" t="inlineStr">
-        <is>
-          <t>Lucas Souza</t>
-        </is>
-      </c>
-      <c r="B51" s="94" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C51" s="93" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D51" s="95" t="n">
-        <v>200</v>
-      </c>
-      <c r="E51" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F51" s="125">
-        <f>IF(OR($E51="Recebido",$C51=""),"",MAX(0,TODAY()-$C51))</f>
-        <v/>
-      </c>
-      <c r="G51" s="94" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="90" t="inlineStr">
-        <is>
-          <t>FG Boa Vista (Recife/PE)</t>
-        </is>
-      </c>
-      <c r="B52" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="89" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D52" s="91" t="n">
-        <v>1008.8</v>
-      </c>
-      <c r="E52" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F52" s="124">
-        <f>IF(OR($E52="Recebido",$C52=""),"",MAX(0,TODAY()-$C52))</f>
-        <v/>
-      </c>
-      <c r="G52" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="94" t="inlineStr">
-        <is>
-          <t>UNIFG Guanambi (Guanambi/BA)</t>
-        </is>
-      </c>
-      <c r="B53" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C53" s="93" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D53" s="95" t="n">
-        <v>4534.75</v>
-      </c>
-      <c r="E53" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F53" s="125">
-        <f>IF(OR($E53="Recebido",$C53=""),"",MAX(0,TODAY()-$C53))</f>
-        <v/>
-      </c>
-      <c r="G53" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="90" t="inlineStr">
-        <is>
-          <t>UNP Zona Norte (Natal/RN)</t>
-        </is>
-      </c>
-      <c r="B54" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C54" s="89" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D54" s="91" t="n">
-        <v>870</v>
-      </c>
-      <c r="E54" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F54" s="124">
-        <f>IF(OR($E54="Recebido",$C54=""),"",MAX(0,TODAY()-$C54))</f>
-        <v/>
-      </c>
-      <c r="G54" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="94" t="inlineStr">
-        <is>
-          <t>UNP Caicó (Caicó/RN)</t>
-        </is>
-      </c>
-      <c r="B55" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C55" s="93" t="n">
-        <v>46261</v>
-      </c>
-      <c r="D55" s="95" t="n">
-        <v>440</v>
-      </c>
-      <c r="E55" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F55" s="125">
-        <f>IF(OR($E55="Recebido",$C55=""),"",MAX(0,TODAY()-$C55))</f>
-        <v/>
-      </c>
-      <c r="G55" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="90" t="inlineStr">
-        <is>
-          <t>AGES Irecê (Irecê/BA)</t>
-        </is>
-      </c>
-      <c r="B56" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C56" s="89" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D56" s="91" t="n">
-        <v>1338.6</v>
-      </c>
-      <c r="E56" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F56" s="124">
-        <f>IF(OR($E56="Recebido",$C56=""),"",MAX(0,TODAY()-$C56))</f>
-        <v/>
-      </c>
-      <c r="G56" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="94" t="inlineStr">
-        <is>
-          <t>CIS Irecê (Irecê/BA)</t>
-        </is>
-      </c>
-      <c r="B57" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C57" s="93" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D57" s="95" t="n">
-        <v>1358</v>
-      </c>
-      <c r="E57" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F57" s="125">
-        <f>IF(OR($E57="Recebido",$C57=""),"",MAX(0,TODAY()-$C57))</f>
-        <v/>
-      </c>
-      <c r="G57" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="90" t="inlineStr">
-        <is>
-          <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
-        </is>
-      </c>
-      <c r="B58" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="89" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D58" s="91" t="n">
-        <v>649.9</v>
-      </c>
-      <c r="E58" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F58" s="124">
-        <f>IF(OR($E58="Recebido",$C58=""),"",MAX(0,TODAY()-$C58))</f>
-        <v/>
-      </c>
-      <c r="G58" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="94" t="inlineStr">
-        <is>
-          <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
-        </is>
-      </c>
-      <c r="B59" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C59" s="93" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D59" s="95" t="n">
-        <v>562.6</v>
-      </c>
-      <c r="E59" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F59" s="125">
-        <f>IF(OR($E59="Recebido",$C59=""),"",MAX(0,TODAY()-$C59))</f>
-        <v/>
-      </c>
-      <c r="G59" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="90" t="inlineStr">
-        <is>
-          <t>AGES Paripiranga (Paripiranga/BA)</t>
-        </is>
-      </c>
-      <c r="B60" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C60" s="89" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D60" s="91" t="n">
-        <v>1086.4</v>
-      </c>
-      <c r="E60" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F60" s="124">
-        <f>IF(OR($E60="Recebido",$C60=""),"",MAX(0,TODAY()-$C60))</f>
-        <v/>
-      </c>
-      <c r="G60" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="94" t="inlineStr">
-        <is>
-          <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
-        </is>
-      </c>
-      <c r="B61" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C61" s="93" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D61" s="95" t="n">
-        <v>1265.85</v>
-      </c>
-      <c r="E61" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F61" s="125">
-        <f>IF(OR($E61="Recebido",$C61=""),"",MAX(0,TODAY()-$C61))</f>
-        <v/>
-      </c>
-      <c r="G61" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="90" t="inlineStr">
-        <is>
-          <t>UNP Mossoró (Mossoró/RN)</t>
-        </is>
-      </c>
-      <c r="B62" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C62" s="89" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D62" s="91" t="n">
-        <v>1867.25</v>
-      </c>
-      <c r="E62" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F62" s="124">
-        <f>IF(OR($E62="Recebido",$C62=""),"",MAX(0,TODAY()-$C62))</f>
-        <v/>
-      </c>
-      <c r="G62" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="94" t="inlineStr">
-        <is>
-          <t>CIS Jacobina (Jacobina/BA)</t>
-        </is>
-      </c>
-      <c r="B63" s="94" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C63" s="93" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D63" s="95" t="n">
-        <v>2095.2</v>
-      </c>
-      <c r="E63" s="125" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F63" s="125">
-        <f>IF(OR($E63="Recebido",$C63=""),"",MAX(0,TODAY()-$C63))</f>
-        <v/>
-      </c>
-      <c r="G63" s="94" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="90" t="inlineStr">
-        <is>
-          <t>AGES Jacobina (Jacobina/BA)</t>
-        </is>
-      </c>
-      <c r="B64" s="90" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C64" s="89" t="n">
-        <v>46305</v>
-      </c>
-      <c r="D64" s="91" t="n">
-        <v>1188.25</v>
-      </c>
-      <c r="E64" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F64" s="124">
-        <f>IF(OR($E64="Recebido",$C64=""),"",MAX(0,TODAY()-$C64))</f>
-        <v/>
-      </c>
-      <c r="G64" s="90" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="94" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="B65" s="94" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C65" s="93" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D65" s="95" t="n">
-        <v>160</v>
-      </c>
-      <c r="E65" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F65" s="125">
-        <f>IF(OR($E65="Recebido",$C65=""),"",MAX(0,TODAY()-$C65))</f>
-        <v/>
-      </c>
-      <c r="G65" s="94" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="90" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B66" s="90" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C66" s="89" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D66" s="91" t="n">
-        <v>60</v>
-      </c>
-      <c r="E66" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F66" s="124">
-        <f>IF(OR($E66="Recebido",$C66=""),"",MAX(0,TODAY()-$C66))</f>
-        <v/>
-      </c>
-      <c r="G66" s="90" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="94" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B67" s="94" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C67" s="93" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D67" s="95" t="n">
-        <v>150</v>
-      </c>
-      <c r="E67" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F67" s="125">
-        <f>IF(OR($E67="Recebido",$C67=""),"",MAX(0,TODAY()-$C67))</f>
-        <v/>
-      </c>
-      <c r="G67" s="94" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="90" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B68" s="90" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C68" s="89" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D68" s="91" t="n">
-        <v>225</v>
-      </c>
-      <c r="E68" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F68" s="124">
-        <f>IF(OR($E68="Recebido",$C68=""),"",MAX(0,TODAY()-$C68))</f>
-        <v/>
-      </c>
-      <c r="G68" s="90" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="94" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B69" s="94" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C69" s="93" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D69" s="95" t="n">
-        <v>140</v>
-      </c>
-      <c r="E69" s="125" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F69" s="125">
-        <f>IF(OR($E69="Recebido",$C69=""),"",MAX(0,TODAY()-$C69))</f>
-        <v/>
-      </c>
-      <c r="G69" s="94" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="94" t="inlineStr">
-        <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
-        </is>
-      </c>
-      <c r="B70" s="94" t="inlineStr">
-        <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C70" s="93" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D70" s="95" t="n">
-        <v>540</v>
-      </c>
-      <c r="E70" s="125" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F70" s="125">
-        <f>IF(OR($E70="Recebido",$C70=""),"",MAX(0,TODAY()-$C70))</f>
-        <v/>
-      </c>
-      <c r="G70" s="94" t="inlineStr">
-        <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="90" t="inlineStr">
-        <is>
-          <t>Cecilio Mota Junior</t>
-        </is>
-      </c>
-      <c r="B71" s="90" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C71" s="89" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D71" s="91" t="n">
-        <v>140</v>
-      </c>
-      <c r="E71" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F71" s="124">
-        <f>IF(OR($E71="Recebido",$C71=""),"",MAX(0,TODAY()-$C71))</f>
-        <v/>
-      </c>
-      <c r="G71" s="90" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="90" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B72" s="90" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C72" s="89" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D72" s="91" t="n">
-        <v>200</v>
-      </c>
-      <c r="E72" s="124" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F72" s="124">
-        <f>IF(OR($E72="Recebido",$C72=""),"",MAX(0,TODAY()-$C72))</f>
-        <v/>
-      </c>
-      <c r="G72" s="90" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="90" t="inlineStr">
-        <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
-        </is>
-      </c>
-      <c r="B73" s="90" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C73" s="89" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D73" s="91" t="n">
-        <v>140</v>
-      </c>
-      <c r="E73" s="124" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F73" s="124">
-        <f>IF(OR($E73="Recebido",$C73=""),"",MAX(0,TODAY()-$C73))</f>
-        <v/>
-      </c>
-      <c r="G73" s="90" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="90" t="inlineStr">
         <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B74" s="90" t="inlineStr">
         <is>
-          <t>Refil Plissado + Refil BAG</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C74" s="89" t="n">
-        <v>46274</v>
+        <v>46239</v>
       </c>
       <c r="D74" s="91" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E74" s="124" t="inlineStr">
         <is>
@@ -42805,49 +42807,1053 @@
         <f>IF(OR($E74="Recebido",$C74=""),"",MAX(0,TODAY()-$C74))</f>
         <v/>
       </c>
-      <c r="G74" s="90" t="inlineStr">
+      <c r="G74" s="90" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="inlineStr">
+        <is>
+          <t>Supermercado Brasil</t>
+        </is>
+      </c>
+      <c r="B75" s="94" t="inlineStr">
+        <is>
+          <t>2x Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C75" s="93" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D75" s="95" t="n">
+        <v>280</v>
+      </c>
+      <c r="E75" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F75" s="125">
+        <f>IF(OR($E75="Recebido",$C75=""),"",MAX(0,TODAY()-$C75))</f>
+        <v/>
+      </c>
+      <c r="G75" s="94" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="90" t="inlineStr">
+        <is>
+          <t>Tropical Motos LTDA</t>
+        </is>
+      </c>
+      <c r="B76" s="90" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
+        </is>
+      </c>
+      <c r="C76" s="89" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D76" s="91" t="n">
+        <v>820</v>
+      </c>
+      <c r="E76" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F76" s="124">
+        <f>IF(OR($E76="Recebido",$C76=""),"",MAX(0,TODAY()-$C76))</f>
+        <v/>
+      </c>
+      <c r="G76" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="94" t="inlineStr">
+        <is>
+          <t>Free Way</t>
+        </is>
+      </c>
+      <c r="B77" s="94" t="inlineStr">
+        <is>
+          <t>5x Refil Everest</t>
+        </is>
+      </c>
+      <c r="C77" s="93" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D77" s="95" t="n">
+        <v>700</v>
+      </c>
+      <c r="E77" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F77" s="125">
+        <f>IF(OR($E77="Recebido",$C77=""),"",MAX(0,TODAY()-$C77))</f>
+        <v/>
+      </c>
+      <c r="G77" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via TED em 02/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="90" t="inlineStr">
+        <is>
+          <t>Neli Sena Rego</t>
+        </is>
+      </c>
+      <c r="B78" s="90" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C78" s="89" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D78" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E78" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F78" s="124">
+        <f>IF(OR($E78="Recebido",$C78=""),"",MAX(0,TODAY()-$C78))</f>
+        <v/>
+      </c>
+      <c r="G78" s="90" t="inlineStr">
+        <is>
+          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="94" t="inlineStr">
+        <is>
+          <t>Neli Sena Rego</t>
+        </is>
+      </c>
+      <c r="B79" s="94" t="inlineStr">
+        <is>
+          <t>Conexão + Mangueira</t>
+        </is>
+      </c>
+      <c r="C79" s="93" t="n">
+        <v>46255</v>
+      </c>
+      <c r="D79" s="95" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F79" s="125">
+        <f>IF(OR($E79="Recebido",$C79=""),"",MAX(0,TODAY()-$C79))</f>
+        <v/>
+      </c>
+      <c r="G79" s="94" t="inlineStr">
+        <is>
+          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="90" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="B80" s="90" t="inlineStr">
+        <is>
+          <t>4x Refil Everest</t>
+        </is>
+      </c>
+      <c r="C80" s="89" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D80" s="91" t="n">
+        <v>480</v>
+      </c>
+      <c r="E80" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F80" s="124">
+        <f>IF(OR($E80="Recebido",$C80=""),"",MAX(0,TODAY()-$C80))</f>
+        <v/>
+      </c>
+      <c r="G80" s="90" t="inlineStr">
+        <is>
+          <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="94" t="inlineStr">
+        <is>
+          <t>Cícero Lima</t>
+        </is>
+      </c>
+      <c r="B81" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C81" s="93" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D81" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E81" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F81" s="125">
+        <f>IF(OR($E81="Recebido",$C81=""),"",MAX(0,TODAY()-$C81))</f>
+        <v/>
+      </c>
+      <c r="G81" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 27/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="90" t="inlineStr">
+        <is>
+          <t>Promotoria Regional de Jacobina</t>
+        </is>
+      </c>
+      <c r="B82" s="90" t="inlineStr">
+        <is>
+          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
+        </is>
+      </c>
+      <c r="C82" s="89" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D82" s="91" t="n">
+        <v>470</v>
+      </c>
+      <c r="E82" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F82" s="124">
+        <f>IF(OR($E82="Recebido",$C82=""),"",MAX(0,TODAY()-$C82))</f>
+        <v/>
+      </c>
+      <c r="G82" s="90" t="inlineStr">
+        <is>
+          <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="94" t="inlineStr">
+        <is>
+          <t>Lucas Souza</t>
+        </is>
+      </c>
+      <c r="B83" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C83" s="93" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D83" s="95" t="n">
+        <v>200</v>
+      </c>
+      <c r="E83" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F83" s="125">
+        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
+        <v/>
+      </c>
+      <c r="G83" s="94" t="inlineStr">
+        <is>
+          <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="90" t="inlineStr">
+        <is>
+          <t>FG Boa Vista (Recife/PE)</t>
+        </is>
+      </c>
+      <c r="B84" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="89" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D84" s="91" t="n">
+        <v>1008.8</v>
+      </c>
+      <c r="E84" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F84" s="124">
+        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
+        <v/>
+      </c>
+      <c r="G84" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="94" t="inlineStr">
+        <is>
+          <t>UNIFG Guanambi (Guanambi/BA)</t>
+        </is>
+      </c>
+      <c r="B85" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="93" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D85" s="95" t="n">
+        <v>4534.75</v>
+      </c>
+      <c r="E85" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F85" s="125">
+        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
+        <v/>
+      </c>
+      <c r="G85" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="90" t="inlineStr">
+        <is>
+          <t>UNP Zona Norte (Natal/RN)</t>
+        </is>
+      </c>
+      <c r="B86" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="89" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D86" s="91" t="n">
+        <v>870</v>
+      </c>
+      <c r="E86" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F86" s="124">
+        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
+        <v/>
+      </c>
+      <c r="G86" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="94" t="inlineStr">
+        <is>
+          <t>UNP Caicó (Caicó/RN)</t>
+        </is>
+      </c>
+      <c r="B87" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="93" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D87" s="95" t="n">
+        <v>440</v>
+      </c>
+      <c r="E87" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F87" s="125">
+        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
+        <v/>
+      </c>
+      <c r="G87" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="90" t="inlineStr">
+        <is>
+          <t>AGES Irecê (Irecê/BA)</t>
+        </is>
+      </c>
+      <c r="B88" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="89" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D88" s="91" t="n">
+        <v>1338.6</v>
+      </c>
+      <c r="E88" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F88" s="124">
+        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="94" t="inlineStr">
+        <is>
+          <t>CIS Irecê (Irecê/BA)</t>
+        </is>
+      </c>
+      <c r="B89" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="93" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D89" s="95" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E89" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F89" s="125">
+        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="90" t="inlineStr">
+        <is>
+          <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
+        </is>
+      </c>
+      <c r="B90" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D90" s="91" t="n">
+        <v>649.9</v>
+      </c>
+      <c r="E90" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F90" s="124">
+        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="94" t="inlineStr">
+        <is>
+          <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
+        </is>
+      </c>
+      <c r="B91" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="93" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D91" s="95" t="n">
+        <v>562.6</v>
+      </c>
+      <c r="E91" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F91" s="125">
+        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="90" t="inlineStr">
+        <is>
+          <t>AGES Paripiranga (Paripiranga/BA)</t>
+        </is>
+      </c>
+      <c r="B92" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D92" s="91" t="n">
+        <v>1086.4</v>
+      </c>
+      <c r="E92" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F92" s="124">
+        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="94" t="inlineStr">
+        <is>
+          <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
+        </is>
+      </c>
+      <c r="B93" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="93" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D93" s="95" t="n">
+        <v>1265.85</v>
+      </c>
+      <c r="E93" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F93" s="125">
+        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="90" t="inlineStr">
+        <is>
+          <t>UNP Mossoró (Mossoró/RN)</t>
+        </is>
+      </c>
+      <c r="B94" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D94" s="91" t="n">
+        <v>1867.25</v>
+      </c>
+      <c r="E94" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F94" s="124">
+        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>CIS Jacobina (Jacobina/BA)</t>
+        </is>
+      </c>
+      <c r="B95" s="94" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="93" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D95" s="95" t="n">
+        <v>2095.2</v>
+      </c>
+      <c r="E95" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F95" s="125">
+        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="94" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="90" t="inlineStr">
+        <is>
+          <t>AGES Jacobina (Jacobina/BA)</t>
+        </is>
+      </c>
+      <c r="B96" s="90" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="89" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D96" s="91" t="n">
+        <v>1188.25</v>
+      </c>
+      <c r="E96" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F96" s="124">
+        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="90" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="94" t="inlineStr">
+        <is>
+          <t>Instituto Paulo Leão</t>
+        </is>
+      </c>
+      <c r="B97" s="94" t="inlineStr">
+        <is>
+          <t>Refil E3 + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C97" s="93" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D97" s="95" t="n">
+        <v>160</v>
+      </c>
+      <c r="E97" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F97" s="125">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="90" t="inlineStr">
+        <is>
+          <t>Eletronic Segurança Eletronica</t>
+        </is>
+      </c>
+      <c r="B98" s="90" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C98" s="89" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D98" s="91" t="n">
+        <v>60</v>
+      </c>
+      <c r="E98" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F98" s="124">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 03/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="94" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B99" s="94" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C99" s="93" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D99" s="95" t="n">
+        <v>150</v>
+      </c>
+      <c r="E99" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F99" s="125">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="90" t="inlineStr">
+        <is>
+          <t>Armazem Cecilio Mota</t>
+        </is>
+      </c>
+      <c r="B100" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest + Refil Carbon 9"</t>
+        </is>
+      </c>
+      <c r="C100" s="89" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D100" s="91" t="n">
+        <v>225</v>
+      </c>
+      <c r="E100" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F100" s="124">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="90" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="94" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B101" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C101" s="93" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D101" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E101" s="125" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F101" s="125">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="94" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="94" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B102" s="94" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C102" s="93" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D102" s="95" t="n">
+        <v>540</v>
+      </c>
+      <c r="E102" s="125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F102" s="125">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="94" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="90" t="inlineStr">
+        <is>
+          <t>Cecilio Mota Junior</t>
+        </is>
+      </c>
+      <c r="B103" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C103" s="89" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D103" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E103" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F103" s="124">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="90" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="90" t="inlineStr">
+        <is>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
+        </is>
+      </c>
+      <c r="B104" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C104" s="89" t="n">
+        <v>46268</v>
+      </c>
+      <c r="D104" s="91" t="n">
+        <v>200</v>
+      </c>
+      <c r="E104" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F104" s="124">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 04/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="90" t="inlineStr">
+        <is>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+        </is>
+      </c>
+      <c r="B105" s="90" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C105" s="89" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D105" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E105" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F105" s="124">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="90" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="90" t="inlineStr">
+        <is>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+        </is>
+      </c>
+      <c r="B106" s="90" t="inlineStr">
+        <is>
+          <t>Refil Plissado + Refil BAG</t>
+        </is>
+      </c>
+      <c r="C106" s="89" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D106" s="91" t="n">
+        <v>150</v>
+      </c>
+      <c r="E106" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F106" s="124">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="90" t="inlineStr">
         <is>
           <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="98" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B75" s="98" t="n"/>
-      <c r="C75" s="126" t="n"/>
-      <c r="D75" s="127">
-        <f>SUMIF(E42:E74,"Pendente",D42:D74)</f>
-        <v/>
-      </c>
-      <c r="E75" s="128" t="n"/>
-      <c r="F75" s="128" t="n"/>
-      <c r="G75" s="98" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="129" t="inlineStr">
+      <c r="B107" s="98" t="n"/>
+      <c r="C107" s="126" t="n"/>
+      <c r="D107" s="127">
+        <f>SUMIF(E74:E106,"Pendente",D74:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="128" t="n"/>
+      <c r="F107" s="128" t="n"/>
+      <c r="G107" s="98" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B76" s="160" t="n"/>
-      <c r="C76" s="160" t="n"/>
-      <c r="D76" s="160" t="n"/>
-      <c r="E76" s="160" t="n"/>
-      <c r="F76" s="160" t="n"/>
-      <c r="G76" s="161" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="200">
-        <f>IF(ROUND(D75-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D75-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="200" t="inlineStr">
+      <c r="B108" s="160" t="n"/>
+      <c r="C108" s="160" t="n"/>
+      <c r="D108" s="160" t="n"/>
+      <c r="E108" s="160" t="n"/>
+      <c r="F108" s="160" t="n"/>
+      <c r="G108" s="161" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="200">
+        <f>IF(ROUND(D107-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D107-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -42858,22 +43864,22 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A109:G109"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A108:G108"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pendente,Pago"</formula1>
+    <dataValidation sqref="E11:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E42:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E74:E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -42674,12 +42674,70 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
+    <row r="60">
+      <c r="A60" s="241" t="inlineStr">
+        <is>
+          <t>Wiliam Pinto Bispo</t>
+        </is>
+      </c>
+      <c r="B60" s="241" t="inlineStr">
+        <is>
+          <t>Salário mensal — competência setembro/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="242" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D60" s="243" t="n">
+        <v>1571.32</v>
+      </c>
+      <c r="E60" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F60" s="245">
+        <f>IF(OR($E60="Pago",$C60=""),"",MAX(0,TODAY()-$C60))</f>
+        <v/>
+      </c>
+      <c r="G60" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="241" t="inlineStr">
+        <is>
+          <t>Wiliam Pinto Bispo</t>
+        </is>
+      </c>
+      <c r="B61" s="241" t="inlineStr">
+        <is>
+          <t>Salário mensal — competência outubro/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="242" t="n">
+        <v>46327</v>
+      </c>
+      <c r="D61" s="243" t="n">
+        <v>1571.32</v>
+      </c>
+      <c r="E61" s="244" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F61" s="245">
+        <f>IF(OR($E61="Pago",$C61=""),"",MAX(0,TODAY()-$C61))</f>
+        <v/>
+      </c>
+      <c r="G61" s="241" t="inlineStr">
+        <is>
+          <t>PREVISÃO — salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
       <c r="A66" s="98" t="inlineStr">
         <is>
@@ -42699,7 +42757,7 @@
     <row r="67">
       <c r="A67" s="246" t="inlineStr">
         <is>
-          <t>PREVISTO — parcelas das notas, boleto ainda não emitido</t>
+          <t>PREVISTO — compromisso certo, sem boleto/documento em mãos</t>
         </is>
       </c>
       <c r="B67" s="246" t="n"/>
@@ -42728,8 +42786,6 @@
       <c r="F68" s="128" t="n"/>
       <c r="G68" s="98" t="n"/>
     </row>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="202" t="inlineStr">
         <is>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="158" min="1" max="1"/>
@@ -3660,7 +3660,7 @@
     <row r="5">
       <c r="A5" s="221" t="inlineStr">
         <is>
-          <t>COMISSÃO: só entra quando o Wiliam faz a troca/instalação. Venda de balcão sem serviço = margem R$ 10 (ou R$ 30) maior. Refis de outras marcas ficam sem comissão porque raramente são trocados por ele.</t>
+          <t>COMISSÃO: só entra quando o Wiliam faz a troca/instalação. Venda de balcão sem serviço = margem R$ 10 (ou R$ 30) maior. Refis de outras marcas ficam sem comissão porque raramente são trocados por ele. A tabela lista só o que é comprado e revendido — serviços avulsos (instalação por fora, limpeza de refil) saíram daqui em 10/09/2026 por serem raros.</t>
         </is>
       </c>
     </row>
@@ -4124,17 +4124,17 @@
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>Limpeza de Refil</t>
+          <t>Purificador Everest Slim Branco</t>
         </is>
       </c>
       <c r="B18" s="69" t="n">
-        <v>40</v>
+        <v>1429</v>
       </c>
       <c r="C18" s="121" t="n">
-        <v>0</v>
+        <v>715.02</v>
       </c>
       <c r="D18" s="69" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E18" s="69">
         <f>IF(B18="","",B18*IF($J18="",$B$4,$J18))</f>
@@ -4156,19 +4156,21 @@
         <f>IF(B18=0,"",H18/B18)</f>
         <v/>
       </c>
-      <c r="J18" s="240" t="n"/>
+      <c r="J18" s="240" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="64" t="inlineStr">
         <is>
-          <t>Instalação de Purificador</t>
+          <t>Purificador Everest Slim Prata</t>
         </is>
       </c>
       <c r="B19" s="67" t="n">
-        <v>100</v>
+        <v>1486</v>
       </c>
       <c r="C19" s="121" t="n">
-        <v>0</v>
+        <v>784.97</v>
       </c>
       <c r="D19" s="67" t="n">
         <v>30</v>
@@ -4193,19 +4195,21 @@
         <f>IF(B19=0,"",H19/B19)</f>
         <v/>
       </c>
-      <c r="J19" s="239" t="n"/>
+      <c r="J19" s="239" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Slim Branco</t>
+          <t>Purificador Everest Star Branco</t>
         </is>
       </c>
       <c r="B20" s="69" t="n">
         <v>1429</v>
       </c>
       <c r="C20" s="121" t="n">
-        <v>715.02</v>
+        <v>756.73</v>
       </c>
       <c r="D20" s="69" t="n">
         <v>30</v>
@@ -4237,14 +4241,14 @@
     <row r="21">
       <c r="A21" s="64" t="inlineStr">
         <is>
-          <t>Purificador Everest Slim Prata</t>
+          <t>Purificador Everest Plus Branco</t>
         </is>
       </c>
       <c r="B21" s="67" t="n">
-        <v>1486</v>
+        <v>1529</v>
       </c>
       <c r="C21" s="121" t="n">
-        <v>784.97</v>
+        <v>820.73</v>
       </c>
       <c r="D21" s="67" t="n">
         <v>30</v>
@@ -4276,14 +4280,14 @@
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Star Branco</t>
+          <t>Purificador Everest Plus Prata</t>
         </is>
       </c>
       <c r="B22" s="69" t="n">
-        <v>1429</v>
+        <v>1569</v>
       </c>
       <c r="C22" s="121" t="n">
-        <v>756.73</v>
+        <v>906.9299999999999</v>
       </c>
       <c r="D22" s="69" t="n">
         <v>30</v>
@@ -4315,14 +4319,14 @@
     <row r="23">
       <c r="A23" s="64" t="inlineStr">
         <is>
-          <t>Purificador Everest Plus Branco</t>
+          <t>Purificador Everest Fit Branco</t>
         </is>
       </c>
       <c r="B23" s="67" t="n">
-        <v>1529</v>
+        <v>1429</v>
       </c>
       <c r="C23" s="121" t="n">
-        <v>820.73</v>
+        <v>756.73</v>
       </c>
       <c r="D23" s="67" t="n">
         <v>30</v>
@@ -4354,14 +4358,14 @@
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Plus Prata</t>
+          <t>Purificador Everest Fit Preto</t>
         </is>
       </c>
       <c r="B24" s="69" t="n">
-        <v>1569</v>
+        <v>1486</v>
       </c>
       <c r="C24" s="121" t="n">
-        <v>906.9299999999999</v>
+        <v>784.96</v>
       </c>
       <c r="D24" s="69" t="n">
         <v>30</v>
@@ -4393,14 +4397,14 @@
     <row r="25">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>Purificador Everest Fit Branco</t>
+          <t>Purificador Everest Fit Prata</t>
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>1429</v>
+        <v>1486</v>
       </c>
       <c r="C25" s="121" t="n">
-        <v>756.73</v>
+        <v>739.37</v>
       </c>
       <c r="D25" s="67" t="n">
         <v>30</v>
@@ -4432,10 +4436,10 @@
     <row r="26">
       <c r="A26" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Fit Preto</t>
-        </is>
-      </c>
-      <c r="B26" s="69" t="n">
+          <t>Purificador Everest Star Preto</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="n">
         <v>1486</v>
       </c>
       <c r="C26" s="121" t="n">
@@ -4469,55 +4473,55 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
-        <is>
-          <t>Purificador Everest Fit Prata</t>
-        </is>
-      </c>
-      <c r="B27" s="67" t="n">
-        <v>1486</v>
+      <c r="A27" s="66" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Branco</t>
+        </is>
+      </c>
+      <c r="B27" s="77" t="n">
+        <v>1589</v>
       </c>
       <c r="C27" s="121" t="n">
-        <v>739.37</v>
-      </c>
-      <c r="D27" s="67" t="n">
+        <v>767.95</v>
+      </c>
+      <c r="D27" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E27" s="67">
+      <c r="E27" s="69">
         <f>IF(B27="","",B27*IF($J27="",$B$4,$J27))</f>
         <v/>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="69">
         <f>IF(B27="","",B27*$D$4)</f>
         <v/>
       </c>
-      <c r="G27" s="67">
+      <c r="G27" s="69">
         <f>IF(B27="","",SUM(C27:F27))</f>
         <v/>
       </c>
-      <c r="H27" s="67">
+      <c r="H27" s="69">
         <f>IF(B27="","",B27-G27)</f>
         <v/>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="76">
         <f>IF(B27=0,"",H27/B27)</f>
         <v/>
       </c>
-      <c r="J27" s="239" t="n">
+      <c r="J27" s="240" t="n">
         <v>0.1399</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Star Preto</t>
+          <t>Purificador Everest Foz Cinza/Grafite</t>
         </is>
       </c>
       <c r="B28" s="77" t="n">
-        <v>1486</v>
+        <v>1689</v>
       </c>
       <c r="C28" s="121" t="n">
-        <v>784.96</v>
+        <v>819.5700000000001</v>
       </c>
       <c r="D28" s="69" t="n">
         <v>30</v>
@@ -4549,14 +4553,14 @@
     <row r="29">
       <c r="A29" s="66" t="inlineStr">
         <is>
-          <t>Purificador Everest Foz Branco</t>
+          <t>Purificador Everest Baby (todas as cores)</t>
         </is>
       </c>
       <c r="B29" s="77" t="n">
-        <v>1589</v>
+        <v>420</v>
       </c>
       <c r="C29" s="121" t="n">
-        <v>767.95</v>
+        <v>150.13</v>
       </c>
       <c r="D29" s="69" t="n">
         <v>30</v>
@@ -4582,103 +4586,25 @@
         <v/>
       </c>
       <c r="J29" s="240" t="n">
-        <v>0.1399</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="66" t="inlineStr">
-        <is>
-          <t>Purificador Everest Foz Cinza/Grafite</t>
-        </is>
-      </c>
-      <c r="B30" s="77" t="n">
-        <v>1689</v>
-      </c>
-      <c r="C30" s="121" t="n">
-        <v>819.5700000000001</v>
-      </c>
-      <c r="D30" s="69" t="n">
-        <v>30</v>
-      </c>
-      <c r="E30" s="69">
-        <f>IF(B30="","",B30*IF($J30="",$B$4,$J30))</f>
-        <v/>
-      </c>
-      <c r="F30" s="69">
-        <f>IF(B30="","",B30*$D$4)</f>
-        <v/>
-      </c>
-      <c r="G30" s="69">
-        <f>IF(B30="","",SUM(C30:F30))</f>
-        <v/>
-      </c>
-      <c r="H30" s="69">
-        <f>IF(B30="","",B30-G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="76">
-        <f>IF(B30=0,"",H30/B30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="240" t="n">
-        <v>0.1399</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="66" t="inlineStr">
-        <is>
-          <t>Purificador Everest Baby (todas as cores)</t>
-        </is>
-      </c>
-      <c r="B31" s="77" t="n">
-        <v>420</v>
-      </c>
-      <c r="C31" s="121" t="n">
-        <v>150.13</v>
-      </c>
-      <c r="D31" s="69" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="69">
-        <f>IF(B31="","",B31*IF($J31="",$B$4,$J31))</f>
-        <v/>
-      </c>
-      <c r="F31" s="69">
-        <f>IF(B31="","",B31*$D$4)</f>
-        <v/>
-      </c>
-      <c r="G31" s="69">
-        <f>IF(B31="","",SUM(C31:F31))</f>
-        <v/>
-      </c>
-      <c r="H31" s="69">
-        <f>IF(B31="","",B31-G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="76">
-        <f>IF(B31=0,"",H31/B31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="240" t="n">
-        <v>0.11</v>
+      <c r="A31" s="220" t="inlineStr">
+        <is>
+          <t>PREÇOS: purificadores conforme o Catálogo de Purificadores (pasta Catálogos) — valor total do parcelamento em 10x, que é como as vendas entram na planilha. À vista sai mais barato: Residencial branco R$ 1.329, demais cores R$ 1.376; Plus branco R$ 1.429, demais R$ 1.476; Foz branco R$ 1.489, cinza/grafite R$ 1.589; Baby R$ 379.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="220" t="inlineStr">
+        <is>
+          <t>TAXAS REAIS DA MAQUININHA (medidas em Ago-Set/2026): débito 1,45% · crédito à vista 3,51% · crédito 2-3x 6,99% · 4x 7,99% · 5x 9,99% · 10x 13,99%. Dinheiro e Pix não têm taxa. A coluna "Taxa aplicada" (J) manda: em branco usa os 7% de B4 (itens de balcão); preenchida, vale o que estiver lá.</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="220" t="inlineStr">
-        <is>
-          <t>PREÇOS: purificadores conforme o Catálogo de Purificadores (pasta Catálogos) — valor total do parcelamento em 10x, que é como as vendas entram na planilha. À vista sai mais barato: Residencial branco R$ 1.329, demais cores R$ 1.376; Plus branco R$ 1.429, demais R$ 1.476; Foz branco R$ 1.489, cinza/grafite R$ 1.589; Baby R$ 379.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="220" t="inlineStr">
-        <is>
-          <t>TAXAS REAIS DA MAQUININHA (medidas em Ago-Set/2026): débito 1,45% · crédito à vista 3,51% · crédito 2-3x 6,99% · 4x 7,99% · 5x 9,99% · 10x 13,99%. Dinheiro e Pix não têm taxa. A coluna "Taxa aplicada" (J) manda: em branco usa os 7% de B4 (itens de balcão); preenchida, vale o que estiver lá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A33" s="216" t="inlineStr">
         <is>
           <t>CUSTOS: Refil Everest e Pré-Filtro = Eversoft (26/08). Pro Life, Carbon Tech, E3, Plissado = Filtros Planeta Água. C+3 = Culligan (22/04). Registro = Everest (19/05). Purificadores = Everest, última nota de cada modelo. Mangueira = R$ 1,72/m (rolo 50 m por R$ 86,01). Termostato: sem compra em 2026.</t>
         </is>
@@ -4689,9 +4615,9 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A31:I31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" location="'Início'!A1" display="← Início"/>
@@ -42222,7 +42148,7 @@
       </c>
       <c r="G45" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42254,7 +42180,7 @@
       </c>
       <c r="G46" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42286,7 +42212,7 @@
       </c>
       <c r="G47" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42318,7 +42244,7 @@
       </c>
       <c r="G48" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42350,7 +42276,7 @@
       </c>
       <c r="G49" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42382,7 +42308,7 @@
       </c>
       <c r="G50" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42414,7 +42340,7 @@
       </c>
       <c r="G51" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42446,7 +42372,7 @@
       </c>
       <c r="G52" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — boleto ainda NÃO recebido do fornecedor. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
         </is>
       </c>
     </row>
@@ -42702,7 +42628,7 @@
       </c>
       <c r="G60" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
+          <t>PREVISÃO (fixo mensal) — despesa recorrente que NUNCA tem boleto: é pagamento direto ao funcionário. Salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
         </is>
       </c>
     </row>
@@ -42734,10 +42660,14 @@
       </c>
       <c r="G61" s="241" t="inlineStr">
         <is>
-          <t>PREVISÃO — salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
-        </is>
-      </c>
-    </row>
+          <t>PREVISÃO (fixo mensal) — despesa recorrente que NUNCA tem boleto: é pagamento direto ao funcionário. Salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="98" t="inlineStr">
         <is>
@@ -42757,7 +42687,7 @@
     <row r="67">
       <c r="A67" s="246" t="inlineStr">
         <is>
-          <t>PREVISTO — compromisso certo, sem boleto/documento em mãos</t>
+          <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
       <c r="B67" s="246" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -34225,7 +34225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34373,11 +34373,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H79,K5,G5:G79)</f>
+        <f>SUMIF(H5:H82,K5,G5:G82)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D80-F80-T5</f>
+        <f>D83-F83-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34385,11 +34385,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D81</f>
+        <f>D84</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E79,"Aguardando Pagamento",D5:D79)</f>
+        <f>SUMIF(E5:E82,"Aguardando Pagamento",D5:D82)</f>
         <v/>
       </c>
     </row>
@@ -34429,7 +34429,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H79,K6,G5:G79)</f>
+        <f>SUMIF(H5:H82,K6,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34469,7 +34469,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H79,K7,G5:G79)</f>
+        <f>SUMIF(H5:H82,K7,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34509,7 +34509,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H79,K8,G5:G79)</f>
+        <f>SUMIF(H5:H82,K8,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34549,7 +34549,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H79,K9,G5:G79)</f>
+        <f>SUMIF(H5:H82,K9,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34589,7 +34589,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H79,K10,G5:G79)</f>
+        <f>SUMIF(H5:H82,K10,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H79,K11,G5:G79)</f>
+        <f>SUMIF(H5:H82,K11,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34669,7 +34669,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H79,K12,G5:G79)</f>
+        <f>SUMIF(H5:H82,K12,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34705,7 +34705,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H79,K13,G5:G79)</f>
+        <f>SUMIF(H5:H82,K13,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H79,K14,G5:G79)</f>
+        <f>SUMIF(H5:H82,K14,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34785,7 +34785,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H79,K15,G5:G79)</f>
+        <f>SUMIF(H5:H82,K15,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H79,K16,G5:G79)</f>
+        <f>SUMIF(H5:H82,K16,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -34861,7 +34861,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H79,K17,G5:G79)</f>
+        <f>SUMIF(H5:H82,K17,G5:G82)</f>
         <v/>
       </c>
     </row>
@@ -36602,46 +36602,135 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="102" t="n"/>
-      <c r="B80" s="102" t="inlineStr">
+      <c r="A80" s="93" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B80" s="94" t="inlineStr">
+        <is>
+          <t>Pamella Rodrigues Ribeiro de Oliveira</t>
+        </is>
+      </c>
+      <c r="C80" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D80" s="95" t="n">
+        <v>150</v>
+      </c>
+      <c r="E80" s="94" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F80" s="95" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="G80" s="95" t="n"/>
+      <c r="H80" s="94" t="n"/>
+      <c r="I80" s="94" t="inlineStr">
+        <is>
+          <t>Crédito em 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="89" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B81" s="90" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C81" s="90" t="inlineStr">
+        <is>
+          <t>Refil BAG</t>
+        </is>
+      </c>
+      <c r="D81" s="91" t="n">
+        <v>50</v>
+      </c>
+      <c r="E81" s="90" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F81" s="91" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G81" s="91" t="n"/>
+      <c r="H81" s="90" t="n"/>
+      <c r="I81" s="90" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="93" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B82" s="94" t="inlineStr">
+        <is>
+          <t>Adriadne (Hotel Jovem Jota)</t>
+        </is>
+      </c>
+      <c r="C82" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D82" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E82" s="94" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F82" s="95" t="n"/>
+      <c r="G82" s="95" t="n"/>
+      <c r="H82" s="94" t="n"/>
+      <c r="I82" s="94" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="102" t="n"/>
+      <c r="B83" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C80" s="102" t="n"/>
-      <c r="D80" s="103">
-        <f>SUM(D5:D79)</f>
-        <v/>
-      </c>
-      <c r="E80" s="102" t="n"/>
-      <c r="F80" s="103">
-        <f>SUM(F5:F79)</f>
-        <v/>
-      </c>
-      <c r="G80" s="103">
-        <f>SUM(G5:G79)</f>
-        <v/>
-      </c>
-      <c r="H80" s="102" t="n"/>
-      <c r="I80" s="102" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="104" t="n"/>
-      <c r="B81" s="104" t="inlineStr">
+      <c r="C83" s="102" t="n"/>
+      <c r="D83" s="103">
+        <f>SUM(D5:D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="102" t="n"/>
+      <c r="F83" s="103">
+        <f>SUM(F5:F82)</f>
+        <v/>
+      </c>
+      <c r="G83" s="103">
+        <f>SUM(G5:G82)</f>
+        <v/>
+      </c>
+      <c r="H83" s="102" t="n"/>
+      <c r="I83" s="102" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="104" t="n"/>
+      <c r="B84" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C81" s="104" t="n"/>
-      <c r="D81" s="105">
-        <f>(D80-F80-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E81" s="104" t="n"/>
-      <c r="F81" s="105" t="n"/>
-      <c r="G81" s="105" t="n"/>
-      <c r="H81" s="104" t="n"/>
-      <c r="I81" s="104" t="n"/>
+      <c r="C84" s="104" t="n"/>
+      <c r="D84" s="105">
+        <f>(D83-F83-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E84" s="104" t="n"/>
+      <c r="F84" s="105" t="n"/>
+      <c r="G84" s="105" t="n"/>
+      <c r="H84" s="104" t="n"/>
+      <c r="I84" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -36658,10 +36747,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -40925,7 +41014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -42664,10 +42753,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="98" t="inlineStr">
         <is>
@@ -43610,14 +43695,18 @@
       </c>
       <c r="E100" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F100" s="124">
         <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
         <v/>
       </c>
-      <c r="G100" s="90" t="n"/>
+      <c r="G100" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="94" t="inlineStr">
@@ -43702,14 +43791,18 @@
       </c>
       <c r="E103" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F103" s="124">
         <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
         <v/>
       </c>
-      <c r="G103" s="90" t="n"/>
+      <c r="G103" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="90" t="inlineStr">
@@ -43804,42 +43897,74 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="98" t="inlineStr">
+      <c r="A107" s="90" t="inlineStr">
+        <is>
+          <t>Adriadne (Hotel Jovem Jota)</t>
+        </is>
+      </c>
+      <c r="B107" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C107" s="89" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D107" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E107" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F107" s="124">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 10/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B107" s="98" t="n"/>
-      <c r="C107" s="126" t="n"/>
-      <c r="D107" s="127">
-        <f>SUMIF(E74:E106,"Pendente",D74:D106)</f>
-        <v/>
-      </c>
-      <c r="E107" s="128" t="n"/>
-      <c r="F107" s="128" t="n"/>
-      <c r="G107" s="98" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="129" t="inlineStr">
+      <c r="B108" s="98" t="n"/>
+      <c r="C108" s="126" t="n"/>
+      <c r="D108" s="127">
+        <f>SUMIF(E74:E107,"Pendente",D74:D107)</f>
+        <v/>
+      </c>
+      <c r="E108" s="128" t="n"/>
+      <c r="F108" s="128" t="n"/>
+      <c r="G108" s="98" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B108" s="160" t="n"/>
-      <c r="C108" s="160" t="n"/>
-      <c r="D108" s="160" t="n"/>
-      <c r="E108" s="160" t="n"/>
-      <c r="F108" s="160" t="n"/>
-      <c r="G108" s="161" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="200">
-        <f>IF(ROUND(D107-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D107-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B109" s="160" t="n"/>
+      <c r="C109" s="160" t="n"/>
+      <c r="D109" s="160" t="n"/>
+      <c r="E109" s="160" t="n"/>
+      <c r="F109" s="160" t="n"/>
+      <c r="G109" s="161" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="200" t="inlineStr">
+      <c r="A110" s="200">
+        <f>IF(ROUND(D108-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D108-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -43851,6 +43976,7 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A110:G110"/>
     <mergeCell ref="A109:G109"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
@@ -43858,14 +43984,13 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A72:G72"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A108:G108"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E74:E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E74:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -34225,7 +34225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U84"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34373,11 +34373,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H82,K5,G5:G82)</f>
+        <f>SUMIF(H5:H83,K5,G5:G83)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D83-F83-T5</f>
+        <f>D84-F84-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34385,11 +34385,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D84</f>
+        <f>D85</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E82,"Aguardando Pagamento",D5:D82)</f>
+        <f>SUMIF(E5:E83,"Aguardando Pagamento",D5:D83)</f>
         <v/>
       </c>
     </row>
@@ -34429,7 +34429,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H82,K6,G5:G82)</f>
+        <f>SUMIF(H5:H83,K6,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34469,7 +34469,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H82,K7,G5:G82)</f>
+        <f>SUMIF(H5:H83,K7,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34509,7 +34509,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H82,K8,G5:G82)</f>
+        <f>SUMIF(H5:H83,K8,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34549,7 +34549,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H82,K9,G5:G82)</f>
+        <f>SUMIF(H5:H83,K9,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34589,7 +34589,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H82,K10,G5:G82)</f>
+        <f>SUMIF(H5:H83,K10,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H82,K11,G5:G82)</f>
+        <f>SUMIF(H5:H83,K11,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34669,7 +34669,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H82,K12,G5:G82)</f>
+        <f>SUMIF(H5:H83,K12,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34705,7 +34705,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H82,K13,G5:G82)</f>
+        <f>SUMIF(H5:H83,K13,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H82,K14,G5:G82)</f>
+        <f>SUMIF(H5:H83,K14,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34785,7 +34785,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H82,K15,G5:G82)</f>
+        <f>SUMIF(H5:H83,K15,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H82,K16,G5:G82)</f>
+        <f>SUMIF(H5:H83,K16,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -34861,7 +34861,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H82,K17,G5:G82)</f>
+        <f>SUMIF(H5:H83,K17,G5:G83)</f>
         <v/>
       </c>
     </row>
@@ -36691,46 +36691,73 @@
       <c r="I82" s="94" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="102" t="n"/>
-      <c r="B83" s="102" t="inlineStr">
+      <c r="A83" s="93" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B83" s="94" t="inlineStr">
+        <is>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+        </is>
+      </c>
+      <c r="C83" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D83" s="95" t="n">
+        <v>200</v>
+      </c>
+      <c r="E83" s="94" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F83" s="95" t="n"/>
+      <c r="G83" s="95" t="n"/>
+      <c r="H83" s="94" t="n"/>
+      <c r="I83" s="94" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="102" t="n"/>
+      <c r="B84" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C83" s="102" t="n"/>
-      <c r="D83" s="103">
-        <f>SUM(D5:D82)</f>
-        <v/>
-      </c>
-      <c r="E83" s="102" t="n"/>
-      <c r="F83" s="103">
-        <f>SUM(F5:F82)</f>
-        <v/>
-      </c>
-      <c r="G83" s="103">
-        <f>SUM(G5:G82)</f>
-        <v/>
-      </c>
-      <c r="H83" s="102" t="n"/>
-      <c r="I83" s="102" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="104" t="n"/>
-      <c r="B84" s="104" t="inlineStr">
+      <c r="C84" s="102" t="n"/>
+      <c r="D84" s="103">
+        <f>SUM(D5:D83)</f>
+        <v/>
+      </c>
+      <c r="E84" s="102" t="n"/>
+      <c r="F84" s="103">
+        <f>SUM(F5:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="103">
+        <f>SUM(G5:G83)</f>
+        <v/>
+      </c>
+      <c r="H84" s="102" t="n"/>
+      <c r="I84" s="102" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="104" t="n"/>
+      <c r="B85" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C84" s="104" t="n"/>
-      <c r="D84" s="105">
-        <f>(D83-F83-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E84" s="104" t="n"/>
-      <c r="F84" s="105" t="n"/>
-      <c r="G84" s="105" t="n"/>
-      <c r="H84" s="104" t="n"/>
-      <c r="I84" s="104" t="n"/>
+      <c r="C85" s="104" t="n"/>
+      <c r="D85" s="105">
+        <f>(D84-F84-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E85" s="104" t="n"/>
+      <c r="F85" s="105" t="n"/>
+      <c r="G85" s="105" t="n"/>
+      <c r="H85" s="104" t="n"/>
+      <c r="I85" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -36747,10 +36774,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -41014,7 +41041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -43929,42 +43956,74 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="98" t="inlineStr">
+      <c r="A108" s="90" t="inlineStr">
+        <is>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+        </is>
+      </c>
+      <c r="B108" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C108" s="89" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D108" s="91" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F108" s="124">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 10/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B108" s="98" t="n"/>
-      <c r="C108" s="126" t="n"/>
-      <c r="D108" s="127">
-        <f>SUMIF(E74:E107,"Pendente",D74:D107)</f>
-        <v/>
-      </c>
-      <c r="E108" s="128" t="n"/>
-      <c r="F108" s="128" t="n"/>
-      <c r="G108" s="98" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="129" t="inlineStr">
+      <c r="B109" s="98" t="n"/>
+      <c r="C109" s="126" t="n"/>
+      <c r="D109" s="127">
+        <f>SUMIF(E74:E108,"Pendente",D74:D108)</f>
+        <v/>
+      </c>
+      <c r="E109" s="128" t="n"/>
+      <c r="F109" s="128" t="n"/>
+      <c r="G109" s="98" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B109" s="160" t="n"/>
-      <c r="C109" s="160" t="n"/>
-      <c r="D109" s="160" t="n"/>
-      <c r="E109" s="160" t="n"/>
-      <c r="F109" s="160" t="n"/>
-      <c r="G109" s="161" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="200">
-        <f>IF(ROUND(D108-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D108-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B110" s="160" t="n"/>
+      <c r="C110" s="160" t="n"/>
+      <c r="D110" s="160" t="n"/>
+      <c r="E110" s="160" t="n"/>
+      <c r="F110" s="160" t="n"/>
+      <c r="G110" s="161" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="200" t="inlineStr">
+      <c r="A111" s="200">
+        <f>IF(ROUND(D109-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D109-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -43973,11 +44032,11 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A111:G111"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A110:G110"/>
-    <mergeCell ref="A109:G109"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
@@ -43990,7 +44049,7 @@
     <dataValidation sqref="E11:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E74:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E74:E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -46,10 +46,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="78">
     <font>
@@ -34225,7 +34226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34373,11 +34374,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H83,K5,G5:G83)</f>
+        <f>SUMIF(H5:H85,K5,G5:G85)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D84-F84-T5</f>
+        <f>D86-F86-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34385,11 +34386,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D85</f>
+        <f>D87</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E83,"Aguardando Pagamento",D5:D83)</f>
+        <f>SUMIF(E5:E85,"Aguardando Pagamento",D5:D85)</f>
         <v/>
       </c>
     </row>
@@ -34429,7 +34430,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H83,K6,G5:G83)</f>
+        <f>SUMIF(H5:H85,K6,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34469,7 +34470,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H83,K7,G5:G83)</f>
+        <f>SUMIF(H5:H85,K7,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34509,7 +34510,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H83,K8,G5:G83)</f>
+        <f>SUMIF(H5:H85,K8,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34549,7 +34550,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H83,K9,G5:G83)</f>
+        <f>SUMIF(H5:H85,K9,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34589,7 +34590,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H83,K10,G5:G83)</f>
+        <f>SUMIF(H5:H85,K10,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34629,7 +34630,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H83,K11,G5:G83)</f>
+        <f>SUMIF(H5:H85,K11,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34669,7 +34670,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H83,K12,G5:G83)</f>
+        <f>SUMIF(H5:H85,K12,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34705,7 +34706,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H83,K13,G5:G83)</f>
+        <f>SUMIF(H5:H85,K13,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34745,7 +34746,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H83,K14,G5:G83)</f>
+        <f>SUMIF(H5:H85,K14,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34785,7 +34786,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H83,K15,G5:G83)</f>
+        <f>SUMIF(H5:H85,K15,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34821,7 +34822,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H83,K16,G5:G83)</f>
+        <f>SUMIF(H5:H85,K16,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -34861,7 +34862,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H83,K17,G5:G83)</f>
+        <f>SUMIF(H5:H85,K17,G5:G85)</f>
         <v/>
       </c>
     </row>
@@ -35717,7 +35718,7 @@
       </c>
       <c r="E47" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F47" s="91" t="n"/>
@@ -36691,73 +36692,127 @@
       <c r="I82" s="94" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="93" t="n">
+      <c r="A83" s="89" t="n">
         <v>46275</v>
       </c>
-      <c r="B83" s="94" t="inlineStr">
+      <c r="B83" s="90" t="inlineStr">
         <is>
           <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
-      <c r="C83" s="94" t="inlineStr">
+      <c r="C83" s="90" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="D83" s="95" t="n">
+      <c r="D83" s="91" t="n">
         <v>200</v>
       </c>
-      <c r="E83" s="94" t="inlineStr">
+      <c r="E83" s="90" t="inlineStr">
         <is>
           <t>Aguardando Pagamento</t>
         </is>
       </c>
-      <c r="F83" s="95" t="n"/>
-      <c r="G83" s="95" t="n"/>
-      <c r="H83" s="94" t="n"/>
-      <c r="I83" s="94" t="n"/>
+      <c r="F83" s="91" t="n"/>
+      <c r="G83" s="91" t="n"/>
+      <c r="H83" s="90" t="n"/>
+      <c r="I83" s="90" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="102" t="n"/>
-      <c r="B84" s="102" t="inlineStr">
+      <c r="A84" s="93" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B84" s="94" t="inlineStr">
+        <is>
+          <t>Topvel Tropical Veiculos e Pecas</t>
+        </is>
+      </c>
+      <c r="C84" s="94" t="inlineStr">
+        <is>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D84" s="95" t="n">
+        <v>370</v>
+      </c>
+      <c r="E84" s="94" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F84" s="95" t="n"/>
+      <c r="G84" s="95" t="n"/>
+      <c r="H84" s="94" t="n"/>
+      <c r="I84" s="94" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B85" s="90" t="inlineStr">
+        <is>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
+        </is>
+      </c>
+      <c r="C85" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D85" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E85" s="90" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F85" s="91" t="n"/>
+      <c r="G85" s="91" t="n"/>
+      <c r="H85" s="90" t="n"/>
+      <c r="I85" s="90" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="102" t="n"/>
+      <c r="B86" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C84" s="102" t="n"/>
-      <c r="D84" s="103">
-        <f>SUM(D5:D83)</f>
-        <v/>
-      </c>
-      <c r="E84" s="102" t="n"/>
-      <c r="F84" s="103">
-        <f>SUM(F5:F83)</f>
-        <v/>
-      </c>
-      <c r="G84" s="103">
-        <f>SUM(G5:G83)</f>
-        <v/>
-      </c>
-      <c r="H84" s="102" t="n"/>
-      <c r="I84" s="102" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="104" t="n"/>
-      <c r="B85" s="104" t="inlineStr">
+      <c r="C86" s="102" t="n"/>
+      <c r="D86" s="103">
+        <f>SUM(D5:D85)</f>
+        <v/>
+      </c>
+      <c r="E86" s="102" t="n"/>
+      <c r="F86" s="103">
+        <f>SUM(F5:F85)</f>
+        <v/>
+      </c>
+      <c r="G86" s="103">
+        <f>SUM(G5:G85)</f>
+        <v/>
+      </c>
+      <c r="H86" s="102" t="n"/>
+      <c r="I86" s="102" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="104" t="n"/>
+      <c r="B87" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C85" s="104" t="n"/>
-      <c r="D85" s="105">
-        <f>(D84-F84-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E85" s="104" t="n"/>
-      <c r="F85" s="105" t="n"/>
-      <c r="G85" s="105" t="n"/>
-      <c r="H85" s="104" t="n"/>
-      <c r="I85" s="104" t="n"/>
+      <c r="C87" s="104" t="n"/>
+      <c r="D87" s="105">
+        <f>(D86-F86-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E87" s="104" t="n"/>
+      <c r="F87" s="105" t="n"/>
+      <c r="G87" s="105" t="n"/>
+      <c r="H87" s="104" t="n"/>
+      <c r="I87" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -36774,10 +36829,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -41041,7 +41096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -43882,14 +43937,18 @@
       </c>
       <c r="E105" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F105" s="124">
         <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
         <v/>
       </c>
-      <c r="G105" s="90" t="n"/>
+      <c r="G105" s="90" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="90" t="inlineStr">
@@ -43988,42 +44047,106 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="98" t="inlineStr">
+      <c r="A109" s="90" t="inlineStr">
+        <is>
+          <t>Topvel Tropical Veiculos e Pecas</t>
+        </is>
+      </c>
+      <c r="B109" s="90" t="inlineStr">
+        <is>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C109" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D109" s="91" t="n">
+        <v>370</v>
+      </c>
+      <c r="E109" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F109" s="124">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="90" t="inlineStr">
+        <is>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
+        </is>
+      </c>
+      <c r="B110" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C110" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D110" s="91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E110" s="124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F110" s="124">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 11/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B109" s="98" t="n"/>
-      <c r="C109" s="126" t="n"/>
-      <c r="D109" s="127">
-        <f>SUMIF(E74:E108,"Pendente",D74:D108)</f>
-        <v/>
-      </c>
-      <c r="E109" s="128" t="n"/>
-      <c r="F109" s="128" t="n"/>
-      <c r="G109" s="98" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="129" t="inlineStr">
+      <c r="B111" s="98" t="n"/>
+      <c r="C111" s="126" t="n"/>
+      <c r="D111" s="127">
+        <f>SUMIF(E74:E110,"Pendente",D74:D110)</f>
+        <v/>
+      </c>
+      <c r="E111" s="128" t="n"/>
+      <c r="F111" s="128" t="n"/>
+      <c r="G111" s="98" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B110" s="160" t="n"/>
-      <c r="C110" s="160" t="n"/>
-      <c r="D110" s="160" t="n"/>
-      <c r="E110" s="160" t="n"/>
-      <c r="F110" s="160" t="n"/>
-      <c r="G110" s="161" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="200">
-        <f>IF(ROUND(D109-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D109-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="200" t="inlineStr">
+      <c r="B112" s="160" t="n"/>
+      <c r="C112" s="160" t="n"/>
+      <c r="D112" s="160" t="n"/>
+      <c r="E112" s="160" t="n"/>
+      <c r="F112" s="160" t="n"/>
+      <c r="G112" s="161" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="200">
+        <f>IF(ROUND(D111-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D111-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -44032,16 +44155,16 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A111:G111"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A110:G110"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="A113:G113"/>
     <mergeCell ref="A71:G71"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -44049,7 +44172,7 @@
     <dataValidation sqref="E11:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E74:E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E74:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -46,11 +46,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="78">
     <font>
@@ -34226,7 +34225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U87"/>
+  <dimension ref="A1:U94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34374,11 +34373,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H85,K5,G5:G85)</f>
+        <f>SUMIF(H5:H92,K5,G5:G92)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D86-F86-T5</f>
+        <f>D93-F93-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34386,11 +34385,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D87</f>
+        <f>D94</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E85,"Aguardando Pagamento",D5:D85)</f>
+        <f>SUMIF(E5:E92,"Aguardando Pagamento",D5:D92)</f>
         <v/>
       </c>
     </row>
@@ -34430,7 +34429,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H85,K6,G5:G85)</f>
+        <f>SUMIF(H5:H92,K6,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34470,7 +34469,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H85,K7,G5:G85)</f>
+        <f>SUMIF(H5:H92,K7,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34510,7 +34509,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H85,K8,G5:G85)</f>
+        <f>SUMIF(H5:H92,K8,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34550,7 +34549,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H85,K9,G5:G85)</f>
+        <f>SUMIF(H5:H92,K9,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34590,7 +34589,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H85,K10,G5:G85)</f>
+        <f>SUMIF(H5:H92,K10,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34630,7 +34629,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H85,K11,G5:G85)</f>
+        <f>SUMIF(H5:H92,K11,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34670,7 +34669,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H85,K12,G5:G85)</f>
+        <f>SUMIF(H5:H92,K12,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34706,7 +34705,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H85,K13,G5:G85)</f>
+        <f>SUMIF(H5:H92,K13,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34746,7 +34745,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H85,K14,G5:G85)</f>
+        <f>SUMIF(H5:H92,K14,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34786,7 +34785,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H85,K15,G5:G85)</f>
+        <f>SUMIF(H5:H92,K15,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34822,7 +34821,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H85,K16,G5:G85)</f>
+        <f>SUMIF(H5:H92,K16,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -34862,7 +34861,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H85,K17,G5:G85)</f>
+        <f>SUMIF(H5:H92,K17,G5:G92)</f>
         <v/>
       </c>
     </row>
@@ -35701,7 +35700,7 @@
     </row>
     <row r="47">
       <c r="A47" s="89" t="n">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="B47" s="90" t="inlineStr">
         <is>
@@ -35724,7 +35723,11 @@
       <c r="F47" s="91" t="n"/>
       <c r="G47" s="91" t="n"/>
       <c r="H47" s="90" t="n"/>
-      <c r="I47" s="90" t="n"/>
+      <c r="I47" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 04/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="93" t="n">
@@ -36666,7 +36669,7 @@
     </row>
     <row r="82">
       <c r="A82" s="93" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B82" s="94" t="inlineStr">
         <is>
@@ -36683,17 +36686,21 @@
       </c>
       <c r="E82" s="94" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F82" s="95" t="n"/>
       <c r="G82" s="95" t="n"/>
       <c r="H82" s="94" t="n"/>
-      <c r="I82" s="94" t="n"/>
+      <c r="I82" s="94" t="inlineStr">
+        <is>
+          <t>Venda de 10/09/2026 — pagamento recebido via Pix em 11/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="89" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B83" s="90" t="inlineStr">
         <is>
@@ -36710,13 +36717,17 @@
       </c>
       <c r="E83" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F83" s="91" t="n"/>
       <c r="G83" s="91" t="n"/>
       <c r="H83" s="90" t="n"/>
-      <c r="I83" s="90" t="n"/>
+      <c r="I83" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 10/09/2026 — pagamento recebido via Pix em 11/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="93" t="n">
@@ -36773,46 +36784,223 @@
       <c r="I85" s="90" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="102" t="n"/>
-      <c r="B86" s="102" t="inlineStr">
+      <c r="A86" s="93" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B86" s="94" t="inlineStr">
+        <is>
+          <t>Loja D Leles</t>
+        </is>
+      </c>
+      <c r="C86" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D86" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="E86" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F86" s="95" t="n"/>
+      <c r="G86" s="95" t="n"/>
+      <c r="H86" s="94" t="n"/>
+      <c r="I86" s="94" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B87" s="90" t="inlineStr">
+        <is>
+          <t>Atacadão da Limpeza</t>
+        </is>
+      </c>
+      <c r="C87" s="90" t="n"/>
+      <c r="D87" s="91" t="n"/>
+      <c r="E87" s="90" t="n"/>
+      <c r="F87" s="91" t="n"/>
+      <c r="G87" s="91" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="90" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I87" s="90" t="inlineStr">
+        <is>
+          <t>Luva vinil G + saco de lixo 60L — venda nº 00021207 (total R$ 46,98, desconto R$ 0,98). Pago em dinheiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="93" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B88" s="94" t="inlineStr">
+        <is>
+          <t>Faca Feira Supermercado</t>
+        </is>
+      </c>
+      <c r="C88" s="94" t="n"/>
+      <c r="D88" s="95" t="n"/>
+      <c r="E88" s="94" t="n"/>
+      <c r="F88" s="95" t="n"/>
+      <c r="G88" s="95" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="H88" s="94" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I88" s="94" t="inlineStr">
+        <is>
+          <t>Copo descartável 200 ml — NFC-e nº 208441. Pago em dinheiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B89" s="90" t="inlineStr">
+        <is>
+          <t>Conserto do Controle do Alarme da Loja</t>
+        </is>
+      </c>
+      <c r="C89" s="90" t="n"/>
+      <c r="D89" s="91" t="n"/>
+      <c r="E89" s="90" t="n"/>
+      <c r="F89" s="91" t="n"/>
+      <c r="G89" s="91" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" s="90" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I89" s="90" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="93" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B90" s="94" t="inlineStr">
+        <is>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
+      <c r="C90" s="94" t="n"/>
+      <c r="D90" s="95" t="n"/>
+      <c r="E90" s="94" t="n"/>
+      <c r="F90" s="95" t="n"/>
+      <c r="G90" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="94" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I90" s="94" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="89" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B91" s="90" t="inlineStr">
+        <is>
+          <t>L K Abade Ltda</t>
+        </is>
+      </c>
+      <c r="C91" s="90" t="n"/>
+      <c r="D91" s="91" t="n"/>
+      <c r="E91" s="90" t="n"/>
+      <c r="F91" s="91" t="n"/>
+      <c r="G91" s="91" t="n">
+        <v>70</v>
+      </c>
+      <c r="H91" s="90" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I91" s="90" t="inlineStr">
+        <is>
+          <t>4 caixas organizadoras rattan 28L + 2 panos multiuso + 1 forma descartável para air fryer — pedido nº 48303.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="93" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B92" s="94" t="inlineStr">
+        <is>
+          <t>Moto Táxi</t>
+        </is>
+      </c>
+      <c r="C92" s="94" t="n"/>
+      <c r="D92" s="95" t="n"/>
+      <c r="E92" s="94" t="n"/>
+      <c r="F92" s="95" t="n"/>
+      <c r="G92" s="95" t="n">
+        <v>16</v>
+      </c>
+      <c r="H92" s="94" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I92" s="94" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="102" t="n"/>
+      <c r="B93" s="102" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C86" s="102" t="n"/>
-      <c r="D86" s="103">
-        <f>SUM(D5:D85)</f>
-        <v/>
-      </c>
-      <c r="E86" s="102" t="n"/>
-      <c r="F86" s="103">
-        <f>SUM(F5:F85)</f>
-        <v/>
-      </c>
-      <c r="G86" s="103">
-        <f>SUM(G5:G85)</f>
-        <v/>
-      </c>
-      <c r="H86" s="102" t="n"/>
-      <c r="I86" s="102" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="104" t="n"/>
-      <c r="B87" s="104" t="inlineStr">
+      <c r="C93" s="102" t="n"/>
+      <c r="D93" s="103">
+        <f>SUM(D5:D92)</f>
+        <v/>
+      </c>
+      <c r="E93" s="102" t="n"/>
+      <c r="F93" s="103">
+        <f>SUM(F5:F92)</f>
+        <v/>
+      </c>
+      <c r="G93" s="103">
+        <f>SUM(G5:G92)</f>
+        <v/>
+      </c>
+      <c r="H93" s="102" t="n"/>
+      <c r="I93" s="102" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="104" t="n"/>
+      <c r="B94" s="104" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C87" s="104" t="n"/>
-      <c r="D87" s="105">
-        <f>(D86-F86-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E87" s="104" t="n"/>
-      <c r="F87" s="105" t="n"/>
-      <c r="G87" s="105" t="n"/>
-      <c r="H87" s="104" t="n"/>
-      <c r="I87" s="104" t="n"/>
+      <c r="C94" s="104" t="n"/>
+      <c r="D94" s="105">
+        <f>(D93-F93-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="E94" s="104" t="n"/>
+      <c r="F94" s="105" t="n"/>
+      <c r="G94" s="105" t="n"/>
+      <c r="H94" s="104" t="n"/>
+      <c r="I94" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -36829,10 +37017,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -44001,7 +44189,7 @@
       </c>
       <c r="E107" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F107" s="124">
@@ -44010,7 +44198,7 @@
       </c>
       <c r="G107" s="90" t="inlineStr">
         <is>
-          <t>Troca do dia 10/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
@@ -44033,7 +44221,7 @@
       </c>
       <c r="E108" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F108" s="124">
@@ -44042,7 +44230,7 @@
       </c>
       <c r="G108" s="90" t="inlineStr">
         <is>
-          <t>Troca do dia 10/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
